--- a/data/TWL.MI.xlsx
+++ b/data/TWL.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>540</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>24</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>23.6000003814697</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>23.6000003814697</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>24</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TWL.MI.xlsx
+++ b/data/TWL.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>156</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>24.3999996185303</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>24</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>24</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>24.3999996185303</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TWL.MI.xlsx
+++ b/data/TWL.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>208</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>24.6000003814697</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>24.3999996185303</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>24.3999996185303</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>24.6000003814697</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TWL.MI.xlsx
+++ b/data/TWL.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>408</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>24.6000003814697</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>23.6000003814697</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>24.2000007629395</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>24.6000003814697</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TWL.MI.xlsx
+++ b/data/TWL.MI.xlsx
@@ -62796,10 +62796,10 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C2715" t="n">
         <v>23.6000003814697</v>
@@ -62819,7 +62819,7 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
         <v>0</v>
@@ -62842,10 +62842,10 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="C2717" t="n">
         <v>23.6000003814697</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>28</v>
+        <v>300</v>
       </c>
       <c r="C2718" t="n">
-        <v>23.7999992370605</v>
+        <v>23.6000003814697</v>
       </c>
       <c r="D2718" t="n">
-        <v>23.2000007629395</v>
+        <v>23.6000003814697</v>
       </c>
       <c r="E2718" t="n">
-        <v>23.7999992370605</v>
+        <v>23.6000003814697</v>
       </c>
       <c r="F2718" t="n">
-        <v>23.2000007629395</v>
+        <v>23.6000003814697</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>540</v>
+        <v>28</v>
       </c>
       <c r="C2719" t="n">
-        <v>24</v>
+        <v>23.7999992370605</v>
       </c>
       <c r="D2719" t="n">
-        <v>23.6000003814697</v>
+        <v>23.2000007629395</v>
       </c>
       <c r="E2719" t="n">
-        <v>23.6000003814697</v>
+        <v>23.7999992370605</v>
       </c>
       <c r="F2719" t="n">
-        <v>24</v>
+        <v>23.2000007629395</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>156</v>
+        <v>540</v>
       </c>
       <c r="C2720" t="n">
-        <v>24.3999996185303</v>
+        <v>24</v>
       </c>
       <c r="D2720" t="n">
+        <v>23.6000003814697</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>23.6000003814697</v>
+      </c>
+      <c r="F2720" t="n">
         <v>24</v>
-      </c>
-      <c r="E2720" t="n">
-        <v>24</v>
-      </c>
-      <c r="F2720" t="n">
-        <v>24.3999996185303</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>208</v>
+        <v>156</v>
       </c>
       <c r="C2721" t="n">
-        <v>24.6000003814697</v>
+        <v>24.3999996185303</v>
       </c>
       <c r="D2721" t="n">
+        <v>24</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>24</v>
+      </c>
+      <c r="F2721" t="n">
         <v>24.3999996185303</v>
-      </c>
-      <c r="E2721" t="n">
-        <v>24.3999996185303</v>
-      </c>
-      <c r="F2721" t="n">
-        <v>24.6000003814697</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>408</v>
+        <v>208</v>
       </c>
       <c r="C2722" t="n">
         <v>24.6000003814697</v>
       </c>
       <c r="D2722" t="n">
-        <v>23.6000003814697</v>
+        <v>24.3999996185303</v>
       </c>
       <c r="E2722" t="n">
-        <v>24.2000007629395</v>
+        <v>24.3999996185303</v>
       </c>
       <c r="F2722" t="n">
         <v>24.6000003814697</v>
       </c>
       <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>164</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>24.6000003814697</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>24.2000007629395</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>24.6000003814697</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>24.6000003814697</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/TWL.MI.xlsx
+++ b/data/TWL.MI.xlsx
@@ -71225,6 +71225,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2726">
+      <c r="A2726" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B2726" t="n">
+        <v>560</v>
+      </c>
+      <c r="C2726" t="n">
+        <v>25</v>
+      </c>
+      <c r="D2726" t="n">
+        <v>23.7999992370605</v>
+      </c>
+      <c r="E2726" t="n">
+        <v>24.7999992370605</v>
+      </c>
+      <c r="F2726" t="n">
+        <v>25</v>
+      </c>
+      <c r="G2726" t="n">
+        <v>25</v>
+      </c>
+      <c r="H2726" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TWL.MI.xlsx
+++ b/data/TWL.MI.xlsx
@@ -63070,6 +63070,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2727">
+      <c r="A2727" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B2727" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2727" t="n">
+        <v>25</v>
+      </c>
+      <c r="D2727" t="n">
+        <v>25</v>
+      </c>
+      <c r="E2727" t="n">
+        <v>25</v>
+      </c>
+      <c r="F2727" t="n">
+        <v>25</v>
+      </c>
+      <c r="G2727" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TWL.MI.xlsx
+++ b/data/TWL.MI.xlsx
@@ -63139,6 +63139,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2730">
+      <c r="A2730" s="1" t="n">
+        <v>46293.2916666667</v>
+      </c>
+      <c r="B2730" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2730" t="n">
+        <v>24.2000007629395</v>
+      </c>
+      <c r="D2730" t="n">
+        <v>24.2000007629395</v>
+      </c>
+      <c r="E2730" t="n">
+        <v>24.2000007629395</v>
+      </c>
+      <c r="F2730" t="n">
+        <v>24.2000007629395</v>
+      </c>
+      <c r="G2730" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TWL.MI.xlsx
+++ b/data/TWL.MI.xlsx
@@ -63162,6 +63162,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2731">
+      <c r="A2731" s="1" t="n">
+        <v>46294.2916666667</v>
+      </c>
+      <c r="B2731" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2731" t="n">
+        <v>24.2000007629395</v>
+      </c>
+      <c r="D2731" t="n">
+        <v>24.2000007629395</v>
+      </c>
+      <c r="E2731" t="n">
+        <v>24.2000007629395</v>
+      </c>
+      <c r="F2731" t="n">
+        <v>24.2000007629395</v>
+      </c>
+      <c r="G2731" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TWL.MI.xlsx
+++ b/data/TWL.MI.xlsx
@@ -63185,6 +63185,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2732">
+      <c r="A2732" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B2732" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2732" t="n">
+        <v>24.2000007629395</v>
+      </c>
+      <c r="D2732" t="n">
+        <v>24.2000007629395</v>
+      </c>
+      <c r="E2732" t="n">
+        <v>24.2000007629395</v>
+      </c>
+      <c r="F2732" t="n">
+        <v>24.2000007629395</v>
+      </c>
+      <c r="G2732" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2733">
+      <c r="A2733" s="1" t="n">
+        <v>46296.2916666667</v>
+      </c>
+      <c r="B2733" t="n">
+        <v>764</v>
+      </c>
+      <c r="C2733" t="n">
+        <v>24.6000003814697</v>
+      </c>
+      <c r="D2733" t="n">
+        <v>22.2000007629395</v>
+      </c>
+      <c r="E2733" t="n">
+        <v>23.7999992370605</v>
+      </c>
+      <c r="F2733"/>
+      <c r="G2733" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TWL.MI.xlsx
+++ b/data/TWL.MI.xlsx
@@ -63270,7 +63270,9 @@
       <c r="E2735" t="n">
         <v>23.3999996185303</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>23.6000003814697</v>
+      </c>
       <c r="G2735" t="s">
         <v>7</v>
       </c>

--- a/data/TWL.MI.xlsx
+++ b/data/TWL.MI.xlsx
@@ -63277,6 +63277,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>23.6000003814697</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>23.6000003814697</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>23.6000003814697</v>
+      </c>
+      <c r="F2736" t="n">
+        <v>23.6000003814697</v>
+      </c>
+      <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>32</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>23.6000003814697</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>23.2000007629395</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>23.2000007629395</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TWL.MI.xlsx
+++ b/data/TWL.MI.xlsx
@@ -63316,7 +63316,9 @@
       <c r="E2737" t="n">
         <v>23.2000007629395</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>23.6000003814697</v>
+      </c>
       <c r="G2737" t="s">
         <v>7</v>
       </c>

--- a/data/TWL.MI.xlsx
+++ b/data/TWL.MI.xlsx
@@ -63323,6 +63323,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>23.6000003814697</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>23.6000003814697</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>23.6000003814697</v>
+      </c>
+      <c r="F2738" t="n">
+        <v>23.6000003814697</v>
+      </c>
+      <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>240</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>23.7999992370605</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>22.7999992370605</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>23.2000007629395</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TWL.MI.xlsx
+++ b/data/TWL.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>23.7999992370605</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>23.7999992370605</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>23.7999992370605</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>23.7999992370605</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TWL.MI.xlsx
+++ b/data/TWL.MI.xlsx
@@ -63438,6 +63438,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2743">
+      <c r="A2743" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2743" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2743" t="n">
+        <v>23.3999996185303</v>
+      </c>
+      <c r="D2743" t="n">
+        <v>23.3999996185303</v>
+      </c>
+      <c r="E2743" t="n">
+        <v>23.3999996185303</v>
+      </c>
+      <c r="F2743" t="n">
+        <v>23.3999996185303</v>
+      </c>
+      <c r="G2743" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TWL.MI.xlsx
+++ b/data/TWL.MI.xlsx
@@ -79954,6 +79954,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2745">
+      <c r="A2745" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2745" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C2745" t="n">
+        <v>23.3999996185303</v>
+      </c>
+      <c r="D2745" t="n">
+        <v>23.3999996185303</v>
+      </c>
+      <c r="E2745" t="n">
+        <v>23.3999996185303</v>
+      </c>
+      <c r="F2745" t="n">
+        <v>23.3999996185303</v>
+      </c>
+      <c r="G2745" t="n">
+        <v>23.3999996185303</v>
+      </c>
+      <c r="H2745" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2745" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2746">
+      <c r="A2746" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2746" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2746" t="n">
+        <v>22.7999992370605</v>
+      </c>
+      <c r="D2746" t="n">
+        <v>23.3999996185303</v>
+      </c>
+      <c r="E2746" t="n">
+        <v>22.3999996185303</v>
+      </c>
+      <c r="F2746" t="n">
+        <v>23.3999996185303</v>
+      </c>
+      <c r="G2746" t="n">
+        <v>23.3999996185303</v>
+      </c>
+      <c r="H2746" t="n">
+        <v>384</v>
+      </c>
+      <c r="I2746" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TWL.MI.xlsx
+++ b/data/TWL.MI.xlsx
@@ -80012,6 +80012,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2747">
+      <c r="A2747" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2747" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2747" t="n">
+        <v>22.7999992370605</v>
+      </c>
+      <c r="D2747" t="n">
+        <v>23.2000007629395</v>
+      </c>
+      <c r="E2747" t="n">
+        <v>22</v>
+      </c>
+      <c r="F2747" t="n">
+        <v>23.2000007629395</v>
+      </c>
+      <c r="G2747" t="n">
+        <v>23.2000007629395</v>
+      </c>
+      <c r="H2747" t="n">
+        <v>488</v>
+      </c>
+      <c r="I2747" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TWL.MI.xlsx
+++ b/data/TWL.MI.xlsx
@@ -427,7 +427,7 @@
         <v>23.8167095184326</v>
       </c>
       <c r="G2" t="n">
-        <v>22.284351348877</v>
+        <v>22.2843532562256</v>
       </c>
       <c r="H2" t="n">
         <v>379</v>
@@ -717,7 +717,7 @@
         <v>22.0058288574219</v>
       </c>
       <c r="G12" t="n">
-        <v>20.5899829864502</v>
+        <v>20.5899810791016</v>
       </c>
       <c r="H12" t="n">
         <v>396</v>
@@ -746,7 +746,7 @@
         <v>21.4408340454102</v>
       </c>
       <c r="G13" t="n">
-        <v>20.0613403320312</v>
+        <v>20.0613384246826</v>
       </c>
       <c r="H13" t="n">
         <v>345</v>
@@ -775,7 +775,7 @@
         <v>19.1229057312012</v>
       </c>
       <c r="G14" t="n">
-        <v>17.8925437927246</v>
+        <v>17.8925457000732</v>
       </c>
       <c r="H14" t="n">
         <v>983</v>
@@ -833,7 +833,7 @@
         <v>20.8613529205322</v>
       </c>
       <c r="G16" t="n">
-        <v>19.5191421508789</v>
+        <v>19.5191402435303</v>
       </c>
       <c r="H16" t="n">
         <v>172</v>
@@ -862,7 +862,7 @@
         <v>20.8613529205322</v>
       </c>
       <c r="G17" t="n">
-        <v>19.5191421508789</v>
+        <v>19.5191402435303</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
         <v>20.8613529205322</v>
       </c>
       <c r="G18" t="n">
-        <v>19.5191421508789</v>
+        <v>19.5191402435303</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
         <v>20.8613529205322</v>
       </c>
       <c r="G19" t="n">
-        <v>19.5191421508789</v>
+        <v>19.5191402435303</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -978,7 +978,7 @@
         <v>19.7023887634277</v>
       </c>
       <c r="G21" t="n">
-        <v>18.4347438812256</v>
+        <v>18.4347457885742</v>
       </c>
       <c r="H21" t="n">
         <v>293</v>
@@ -1007,7 +1007,7 @@
         <v>19.7023887634277</v>
       </c>
       <c r="G22" t="n">
-        <v>18.4347438812256</v>
+        <v>18.4347457885742</v>
       </c>
       <c r="H22" t="n">
         <v>276</v>
@@ -1036,7 +1036,7 @@
         <v>20.2239227294922</v>
       </c>
       <c r="G23" t="n">
-        <v>18.922721862793</v>
+        <v>18.9227237701416</v>
       </c>
       <c r="H23" t="n">
         <v>776</v>
@@ -1094,7 +1094,7 @@
         <v>19.6154651641846</v>
       </c>
       <c r="G25" t="n">
-        <v>18.3534145355225</v>
+        <v>18.3534126281738</v>
       </c>
       <c r="H25" t="n">
         <v>448</v>
@@ -1152,7 +1152,7 @@
         <v>19.1229057312012</v>
       </c>
       <c r="G27" t="n">
-        <v>17.8925437927246</v>
+        <v>17.8925457000732</v>
       </c>
       <c r="H27" t="n">
         <v>86</v>
@@ -1181,7 +1181,7 @@
         <v>18.282657623291</v>
       </c>
       <c r="G28" t="n">
-        <v>17.1063594818115</v>
+        <v>17.1063575744629</v>
       </c>
       <c r="H28" t="n">
         <v>86</v>
@@ -1210,7 +1210,7 @@
         <v>19.1229057312012</v>
       </c>
       <c r="G29" t="n">
-        <v>17.8925437927246</v>
+        <v>17.8925457000732</v>
       </c>
       <c r="H29" t="n">
         <v>2519</v>
@@ -1268,7 +1268,7 @@
         <v>18.0218906402588</v>
       </c>
       <c r="G31" t="n">
-        <v>16.8623676300049</v>
+        <v>16.8623695373535</v>
       </c>
       <c r="H31" t="n">
         <v>241</v>
@@ -1297,7 +1297,7 @@
         <v>18.8331642150879</v>
       </c>
       <c r="G32" t="n">
-        <v>17.6214466094971</v>
+        <v>17.6214447021484</v>
       </c>
       <c r="H32" t="n">
         <v>69</v>
@@ -1326,7 +1326,7 @@
         <v>18.8331642150879</v>
       </c>
       <c r="G33" t="n">
-        <v>17.6214466094971</v>
+        <v>17.6214447021484</v>
       </c>
       <c r="H33" t="n">
         <v>207</v>
@@ -1355,7 +1355,7 @@
         <v>18.5723972320557</v>
       </c>
       <c r="G34" t="n">
-        <v>17.3774547576904</v>
+        <v>17.3774566650391</v>
       </c>
       <c r="H34" t="n">
         <v>207</v>
@@ -1442,7 +1442,7 @@
         <v>19.1229057312012</v>
       </c>
       <c r="G37" t="n">
-        <v>17.8925437927246</v>
+        <v>17.8925457000732</v>
       </c>
       <c r="H37" t="n">
         <v>258</v>
@@ -1558,7 +1558,7 @@
         <v>20.5716114044189</v>
       </c>
       <c r="G41" t="n">
-        <v>19.2480430603027</v>
+        <v>19.2480411529541</v>
       </c>
       <c r="H41" t="n">
         <v>86</v>
@@ -1587,7 +1587,7 @@
         <v>20.5716114044189</v>
       </c>
       <c r="G42" t="n">
-        <v>19.2480430603027</v>
+        <v>19.2480411529541</v>
       </c>
       <c r="H42" t="n">
         <v>86</v>
@@ -1616,7 +1616,7 @@
         <v>20.5716114044189</v>
       </c>
       <c r="G43" t="n">
-        <v>19.2480430603027</v>
+        <v>19.2480411529541</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -1674,7 +1674,7 @@
         <v>20.5716114044189</v>
       </c>
       <c r="G45" t="n">
-        <v>19.2480430603027</v>
+        <v>19.2480411529541</v>
       </c>
       <c r="H45" t="n">
         <v>465</v>
@@ -1848,7 +1848,7 @@
         <v>21.8754444122314</v>
       </c>
       <c r="G51" t="n">
-        <v>20.4679851531982</v>
+        <v>20.4679870605469</v>
       </c>
       <c r="H51" t="n">
         <v>1069</v>
@@ -1964,7 +1964,7 @@
         <v>22.9764614105225</v>
       </c>
       <c r="G55" t="n">
-        <v>21.4981632232666</v>
+        <v>21.4981651306152</v>
       </c>
       <c r="H55" t="n">
         <v>224</v>
@@ -1993,7 +1993,7 @@
         <v>22.2231349945068</v>
       </c>
       <c r="G56" t="n">
-        <v>20.7933082580566</v>
+        <v>20.793306350708</v>
       </c>
       <c r="H56" t="n">
         <v>483</v>
@@ -2051,7 +2051,7 @@
         <v>21.6436538696289</v>
       </c>
       <c r="G58" t="n">
-        <v>20.2511100769043</v>
+        <v>20.2511081695557</v>
       </c>
       <c r="H58" t="n">
         <v>120</v>
@@ -2109,7 +2109,7 @@
         <v>23.1503067016602</v>
       </c>
       <c r="G60" t="n">
-        <v>21.6608257293701</v>
+        <v>21.6608238220215</v>
       </c>
       <c r="H60" t="n">
         <v>17</v>
@@ -2138,7 +2138,7 @@
         <v>23.1503067016602</v>
       </c>
       <c r="G61" t="n">
-        <v>21.6608257293701</v>
+        <v>21.6608238220215</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -2283,7 +2283,7 @@
         <v>21.7305755615234</v>
       </c>
       <c r="G66" t="n">
-        <v>20.3324375152588</v>
+        <v>20.3324394226074</v>
       </c>
       <c r="H66" t="n">
         <v>120</v>
@@ -2312,7 +2312,7 @@
         <v>21.4408340454102</v>
       </c>
       <c r="G67" t="n">
-        <v>20.0613403320312</v>
+        <v>20.0613384246826</v>
       </c>
       <c r="H67" t="n">
         <v>17</v>
@@ -2341,7 +2341,7 @@
         <v>22.0058288574219</v>
       </c>
       <c r="G68" t="n">
-        <v>20.5899829864502</v>
+        <v>20.5899810791016</v>
       </c>
       <c r="H68" t="n">
         <v>172</v>
@@ -2370,7 +2370,7 @@
         <v>22.0058288574219</v>
       </c>
       <c r="G69" t="n">
-        <v>20.5899829864502</v>
+        <v>20.5899810791016</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -2399,7 +2399,7 @@
         <v>20.8613529205322</v>
       </c>
       <c r="G70" t="n">
-        <v>19.5191421508789</v>
+        <v>19.5191402435303</v>
       </c>
       <c r="H70" t="n">
         <v>1173</v>
@@ -2428,7 +2428,7 @@
         <v>21.1800670623779</v>
       </c>
       <c r="G71" t="n">
-        <v>19.8173484802246</v>
+        <v>19.8173503875732</v>
       </c>
       <c r="H71" t="n">
         <v>103</v>
@@ -2486,7 +2486,7 @@
         <v>19.8327713012695</v>
       </c>
       <c r="G73" t="n">
-        <v>18.5567398071289</v>
+        <v>18.5567378997803</v>
       </c>
       <c r="H73" t="n">
         <v>241</v>
@@ -2515,7 +2515,7 @@
         <v>19.7023887634277</v>
       </c>
       <c r="G74" t="n">
-        <v>18.4347438812256</v>
+        <v>18.4347457885742</v>
       </c>
       <c r="H74" t="n">
         <v>431</v>
@@ -2544,7 +2544,7 @@
         <v>19.7023887634277</v>
       </c>
       <c r="G75" t="n">
-        <v>18.4347438812256</v>
+        <v>18.4347457885742</v>
       </c>
       <c r="H75" t="n">
         <v>120</v>
@@ -2631,7 +2631,7 @@
         <v>19.3257236480713</v>
       </c>
       <c r="G78" t="n">
-        <v>18.0823135375977</v>
+        <v>18.0823154449463</v>
       </c>
       <c r="H78" t="n">
         <v>345</v>
@@ -2660,7 +2660,7 @@
         <v>19.7023887634277</v>
       </c>
       <c r="G79" t="n">
-        <v>18.4347438812256</v>
+        <v>18.4347457885742</v>
       </c>
       <c r="H79" t="n">
         <v>69</v>
@@ -2689,7 +2689,7 @@
         <v>19.7023887634277</v>
       </c>
       <c r="G80" t="n">
-        <v>18.4347438812256</v>
+        <v>18.4347457885742</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -2747,7 +2747,7 @@
         <v>19.1229057312012</v>
       </c>
       <c r="G82" t="n">
-        <v>17.8925437927246</v>
+        <v>17.8925457000732</v>
       </c>
       <c r="H82" t="n">
         <v>345</v>
@@ -2776,7 +2776,7 @@
         <v>19.1229057312012</v>
       </c>
       <c r="G83" t="n">
-        <v>17.8925437927246</v>
+        <v>17.8925457000732</v>
       </c>
       <c r="H83" t="n">
         <v>638</v>
@@ -2950,7 +2950,7 @@
         <v>19.1229057312012</v>
       </c>
       <c r="G89" t="n">
-        <v>17.8925437927246</v>
+        <v>17.8925457000732</v>
       </c>
       <c r="H89" t="n">
         <v>138</v>
@@ -2979,7 +2979,7 @@
         <v>19.1229057312012</v>
       </c>
       <c r="G90" t="n">
-        <v>17.8925437927246</v>
+        <v>17.8925457000732</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -3066,7 +3066,7 @@
         <v>17.8770198822021</v>
       </c>
       <c r="G93" t="n">
-        <v>16.7268199920654</v>
+        <v>16.7268180847168</v>
       </c>
       <c r="H93" t="n">
         <v>241</v>
@@ -3124,7 +3124,7 @@
         <v>19.3257236480713</v>
       </c>
       <c r="G95" t="n">
-        <v>18.0823135375977</v>
+        <v>18.0823154449463</v>
       </c>
       <c r="H95" t="n">
         <v>517</v>
@@ -3182,7 +3182,7 @@
         <v>17.8770198822021</v>
       </c>
       <c r="G97" t="n">
-        <v>16.7268199920654</v>
+        <v>16.7268180847168</v>
       </c>
       <c r="H97" t="n">
         <v>17</v>
@@ -3211,7 +3211,7 @@
         <v>17.8770198822021</v>
       </c>
       <c r="G98" t="n">
-        <v>16.7268199920654</v>
+        <v>16.7268180847168</v>
       </c>
       <c r="H98" t="n">
         <v>138</v>
@@ -3269,7 +3269,7 @@
         <v>18.3261184692383</v>
       </c>
       <c r="G100" t="n">
-        <v>17.1470241546631</v>
+        <v>17.1470222473145</v>
       </c>
       <c r="H100" t="n">
         <v>34</v>
@@ -3443,7 +3443,7 @@
         <v>19.253288269043</v>
       </c>
       <c r="G106" t="n">
-        <v>18.0145397186279</v>
+        <v>18.0145378112793</v>
       </c>
       <c r="H106" t="n">
         <v>17</v>
@@ -3472,7 +3472,7 @@
         <v>19.253288269043</v>
       </c>
       <c r="G107" t="n">
-        <v>18.0145397186279</v>
+        <v>18.0145378112793</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -3588,7 +3588,7 @@
         <v>18.5723972320557</v>
       </c>
       <c r="G111" t="n">
-        <v>17.3774547576904</v>
+        <v>17.3774566650391</v>
       </c>
       <c r="H111" t="n">
         <v>172</v>
@@ -3617,7 +3617,7 @@
         <v>24.9322128295898</v>
       </c>
       <c r="G112" t="n">
-        <v>23.3280849456787</v>
+        <v>23.3280830383301</v>
       </c>
       <c r="H112" t="n">
         <v>2830</v>
@@ -3704,7 +3704,7 @@
         <v>31.436897277832</v>
       </c>
       <c r="G115" t="n">
-        <v>29.4142608642578</v>
+        <v>29.4142589569092</v>
       </c>
       <c r="H115" t="n">
         <v>7800</v>
@@ -3791,7 +3791,7 @@
         <v>25.2074661254883</v>
       </c>
       <c r="G118" t="n">
-        <v>23.5856266021729</v>
+        <v>23.5856285095215</v>
       </c>
       <c r="H118" t="n">
         <v>3002</v>
@@ -3820,7 +3820,7 @@
         <v>27.728214263916</v>
       </c>
       <c r="G119" t="n">
-        <v>25.9441928863525</v>
+        <v>25.9441909790039</v>
       </c>
       <c r="H119" t="n">
         <v>3796</v>
@@ -3907,7 +3907,7 @@
         <v>25.7145137786865</v>
       </c>
       <c r="G122" t="n">
-        <v>24.0600528717041</v>
+        <v>24.0600509643555</v>
       </c>
       <c r="H122" t="n">
         <v>673</v>
@@ -4052,7 +4052,7 @@
         <v>22.6432590484619</v>
       </c>
       <c r="G127" t="n">
-        <v>21.1863994598389</v>
+        <v>21.1864013671875</v>
       </c>
       <c r="H127" t="n">
         <v>396</v>
@@ -4081,7 +4081,7 @@
         <v>22.6142845153809</v>
       </c>
       <c r="G128" t="n">
-        <v>21.1592884063721</v>
+        <v>21.1592903137207</v>
       </c>
       <c r="H128" t="n">
         <v>120</v>
@@ -4110,7 +4110,7 @@
         <v>22.6142845153809</v>
       </c>
       <c r="G129" t="n">
-        <v>21.1592884063721</v>
+        <v>21.1592903137207</v>
       </c>
       <c r="H129" t="n">
         <v>431</v>
@@ -4139,7 +4139,7 @@
         <v>22.1362113952637</v>
       </c>
       <c r="G130" t="n">
-        <v>20.7119750976562</v>
+        <v>20.7119770050049</v>
       </c>
       <c r="H130" t="n">
         <v>189</v>
@@ -4226,7 +4226,7 @@
         <v>21.4408340454102</v>
       </c>
       <c r="G133" t="n">
-        <v>20.0613403320312</v>
+        <v>20.0613384246826</v>
       </c>
       <c r="H133" t="n">
         <v>120</v>
@@ -4429,7 +4429,7 @@
         <v>22.5418491363525</v>
       </c>
       <c r="G140" t="n">
-        <v>21.091516494751</v>
+        <v>21.0915145874023</v>
       </c>
       <c r="H140" t="n">
         <v>828</v>
@@ -4458,7 +4458,7 @@
         <v>22.454927444458</v>
       </c>
       <c r="G141" t="n">
-        <v>21.0101852416992</v>
+        <v>21.0101871490479</v>
       </c>
       <c r="H141" t="n">
         <v>34</v>
@@ -4545,7 +4545,7 @@
         <v>21.2235279083252</v>
       </c>
       <c r="G144" t="n">
-        <v>19.8580150604248</v>
+        <v>19.8580131530762</v>
       </c>
       <c r="H144" t="n">
         <v>500</v>
@@ -4835,7 +4835,7 @@
         <v>21.4408340454102</v>
       </c>
       <c r="G154" t="n">
-        <v>20.0613403320312</v>
+        <v>20.0613384246826</v>
       </c>
       <c r="H154" t="n">
         <v>155</v>
@@ -4864,7 +4864,7 @@
         <v>21.3249378204346</v>
       </c>
       <c r="G155" t="n">
-        <v>19.9528980255127</v>
+        <v>19.9528999328613</v>
       </c>
       <c r="H155" t="n">
         <v>120</v>
@@ -4980,7 +4980,7 @@
         <v>22.0782642364502</v>
       </c>
       <c r="G159" t="n">
-        <v>20.6577568054199</v>
+        <v>20.6577587127686</v>
       </c>
       <c r="H159" t="n">
         <v>103</v>
@@ -5009,7 +5009,7 @@
         <v>22.0782642364502</v>
       </c>
       <c r="G160" t="n">
-        <v>20.6577568054199</v>
+        <v>20.6577587127686</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -5299,7 +5299,7 @@
         <v>24.3961925506592</v>
       </c>
       <c r="G170" t="n">
-        <v>22.8265514373779</v>
+        <v>22.8265495300293</v>
       </c>
       <c r="H170" t="n">
         <v>327</v>
@@ -5502,7 +5502,7 @@
         <v>26.5547637939453</v>
       </c>
       <c r="G177" t="n">
-        <v>24.8462409973145</v>
+        <v>24.8462390899658</v>
       </c>
       <c r="H177" t="n">
         <v>293</v>
@@ -5531,7 +5531,7 @@
         <v>26.0766906738281</v>
       </c>
       <c r="G178" t="n">
-        <v>24.3989276885986</v>
+        <v>24.39892578125</v>
       </c>
       <c r="H178" t="n">
         <v>276</v>
@@ -5792,7 +5792,7 @@
         <v>25.4827213287354</v>
       </c>
       <c r="G187" t="n">
-        <v>23.8431739807129</v>
+        <v>23.8431720733643</v>
       </c>
       <c r="H187" t="n">
         <v>379</v>
@@ -5879,7 +5879,7 @@
         <v>27.2356548309326</v>
       </c>
       <c r="G190" t="n">
-        <v>25.4833221435547</v>
+        <v>25.4833240509033</v>
       </c>
       <c r="H190" t="n">
         <v>1156</v>
@@ -5908,7 +5908,7 @@
         <v>33.0304756164551</v>
       </c>
       <c r="G191" t="n">
-        <v>30.9053077697754</v>
+        <v>30.9053058624268</v>
       </c>
       <c r="H191" t="n">
         <v>5539</v>
@@ -6111,7 +6111,7 @@
         <v>27.9744930267334</v>
       </c>
       <c r="G198" t="n">
-        <v>26.1746234893799</v>
+        <v>26.1746253967285</v>
       </c>
       <c r="H198" t="n">
         <v>103</v>
@@ -6227,7 +6227,7 @@
         <v>28.0614166259766</v>
       </c>
       <c r="G202" t="n">
-        <v>26.2559566497803</v>
+        <v>26.2559547424316</v>
       </c>
       <c r="H202" t="n">
         <v>69</v>
@@ -6343,7 +6343,7 @@
         <v>27.8296222686768</v>
       </c>
       <c r="G206" t="n">
-        <v>26.0390739440918</v>
+        <v>26.0390758514404</v>
       </c>
       <c r="H206" t="n">
         <v>34</v>
@@ -6459,7 +6459,7 @@
         <v>28.0034675598145</v>
       </c>
       <c r="G210" t="n">
-        <v>26.2017345428467</v>
+        <v>26.2017364501953</v>
       </c>
       <c r="H210" t="n">
         <v>3468</v>
@@ -6488,7 +6488,7 @@
         <v>28.2787227630615</v>
       </c>
       <c r="G211" t="n">
-        <v>26.4592819213867</v>
+        <v>26.4592800140381</v>
       </c>
       <c r="H211" t="n">
         <v>759</v>
@@ -6633,7 +6633,7 @@
         <v>28.336669921875</v>
       </c>
       <c r="G216" t="n">
-        <v>26.5134983062744</v>
+        <v>26.513500213623</v>
       </c>
       <c r="H216" t="n">
         <v>120</v>
@@ -6662,7 +6662,7 @@
         <v>28.336669921875</v>
       </c>
       <c r="G217" t="n">
-        <v>26.5134983062744</v>
+        <v>26.513500213623</v>
       </c>
       <c r="H217" t="n">
         <v>51</v>
@@ -6691,7 +6691,7 @@
         <v>28.336669921875</v>
       </c>
       <c r="G218" t="n">
-        <v>26.5134983062744</v>
+        <v>26.513500213623</v>
       </c>
       <c r="H218" t="n">
         <v>0</v>
@@ -6720,7 +6720,7 @@
         <v>27.9600067138672</v>
       </c>
       <c r="G219" t="n">
-        <v>26.1610698699951</v>
+        <v>26.1610717773438</v>
       </c>
       <c r="H219" t="n">
         <v>172</v>
@@ -6807,7 +6807,7 @@
         <v>26.9169387817383</v>
       </c>
       <c r="G222" t="n">
-        <v>25.1851139068604</v>
+        <v>25.1851119995117</v>
       </c>
       <c r="H222" t="n">
         <v>189</v>
@@ -6836,7 +6836,7 @@
         <v>27.2356548309326</v>
       </c>
       <c r="G223" t="n">
-        <v>25.4833221435547</v>
+        <v>25.4833240509033</v>
       </c>
       <c r="H223" t="n">
         <v>258</v>
@@ -6952,7 +6952,7 @@
         <v>27.5109081268311</v>
       </c>
       <c r="G227" t="n">
-        <v>25.7408676147461</v>
+        <v>25.7408657073975</v>
       </c>
       <c r="H227" t="n">
         <v>448</v>
@@ -7068,7 +7068,7 @@
         <v>26.0766906738281</v>
       </c>
       <c r="G231" t="n">
-        <v>24.3989276885986</v>
+        <v>24.39892578125</v>
       </c>
       <c r="H231" t="n">
         <v>155</v>
@@ -7097,7 +7097,7 @@
         <v>26.0766906738281</v>
       </c>
       <c r="G232" t="n">
-        <v>24.3989276885986</v>
+        <v>24.39892578125</v>
       </c>
       <c r="H232" t="n">
         <v>0</v>
@@ -7126,7 +7126,7 @@
         <v>26.0766906738281</v>
       </c>
       <c r="G233" t="n">
-        <v>24.3989276885986</v>
+        <v>24.39892578125</v>
       </c>
       <c r="H233" t="n">
         <v>155</v>
@@ -7155,7 +7155,7 @@
         <v>25.2074661254883</v>
       </c>
       <c r="G234" t="n">
-        <v>23.5856266021729</v>
+        <v>23.5856285095215</v>
       </c>
       <c r="H234" t="n">
         <v>949</v>
@@ -7387,7 +7387,7 @@
         <v>27.2356548309326</v>
       </c>
       <c r="G242" t="n">
-        <v>25.4833221435547</v>
+        <v>25.4833240509033</v>
       </c>
       <c r="H242" t="n">
         <v>172</v>
@@ -7416,7 +7416,7 @@
         <v>27.2356548309326</v>
       </c>
       <c r="G243" t="n">
-        <v>25.4833221435547</v>
+        <v>25.4833240509033</v>
       </c>
       <c r="H243" t="n">
         <v>0</v>
@@ -7445,7 +7445,7 @@
         <v>27.2356548309326</v>
       </c>
       <c r="G244" t="n">
-        <v>25.4833221435547</v>
+        <v>25.4833240509033</v>
       </c>
       <c r="H244" t="n">
         <v>0</v>
@@ -7561,7 +7561,7 @@
         <v>26.265022277832</v>
       </c>
       <c r="G248" t="n">
-        <v>24.5751419067383</v>
+        <v>24.5751399993896</v>
       </c>
       <c r="H248" t="n">
         <v>310</v>
@@ -7590,7 +7590,7 @@
         <v>26.0766906738281</v>
       </c>
       <c r="G249" t="n">
-        <v>24.3989276885986</v>
+        <v>24.39892578125</v>
       </c>
       <c r="H249" t="n">
         <v>327</v>
@@ -7648,7 +7648,7 @@
         <v>26.1056632995605</v>
       </c>
       <c r="G251" t="n">
-        <v>24.4260368347168</v>
+        <v>24.4260349273682</v>
       </c>
       <c r="H251" t="n">
         <v>276</v>
@@ -7764,7 +7764,7 @@
         <v>26.9169387817383</v>
       </c>
       <c r="G255" t="n">
-        <v>25.1851139068604</v>
+        <v>25.1851119995117</v>
       </c>
       <c r="H255" t="n">
         <v>276</v>
@@ -7793,7 +7793,7 @@
         <v>26.9169387817383</v>
       </c>
       <c r="G256" t="n">
-        <v>25.1851139068604</v>
+        <v>25.1851119995117</v>
       </c>
       <c r="H256" t="n">
         <v>949</v>
@@ -7996,7 +7996,7 @@
         <v>27.2356548309326</v>
       </c>
       <c r="G263" t="n">
-        <v>25.4833221435547</v>
+        <v>25.4833240509033</v>
       </c>
       <c r="H263" t="n">
         <v>500</v>
@@ -8170,7 +8170,7 @@
         <v>27.7861614227295</v>
       </c>
       <c r="G269" t="n">
-        <v>25.9984092712402</v>
+        <v>25.9984111785889</v>
       </c>
       <c r="H269" t="n">
         <v>707</v>
@@ -8199,7 +8199,7 @@
         <v>28.5539741516113</v>
       </c>
       <c r="G270" t="n">
-        <v>26.7168216705322</v>
+        <v>26.7168235778809</v>
       </c>
       <c r="H270" t="n">
         <v>51</v>
@@ -8228,7 +8228,7 @@
         <v>28.5539741516113</v>
       </c>
       <c r="G271" t="n">
-        <v>26.7168216705322</v>
+        <v>26.7168235778809</v>
       </c>
       <c r="H271" t="n">
         <v>379</v>
@@ -8257,7 +8257,7 @@
         <v>29.6115303039551</v>
       </c>
       <c r="G272" t="n">
-        <v>27.7063369750977</v>
+        <v>27.706335067749</v>
       </c>
       <c r="H272" t="n">
         <v>1311</v>
@@ -8286,7 +8286,7 @@
         <v>32.2771453857422</v>
       </c>
       <c r="G273" t="n">
-        <v>30.2004451751709</v>
+        <v>30.2004470825195</v>
       </c>
       <c r="H273" t="n">
         <v>5142</v>
@@ -8373,7 +8373,7 @@
         <v>30.9153652191162</v>
       </c>
       <c r="G276" t="n">
-        <v>28.9262809753418</v>
+        <v>28.9262828826904</v>
       </c>
       <c r="H276" t="n">
         <v>8162</v>
@@ -8489,7 +8489,7 @@
         <v>31.5817699432373</v>
       </c>
       <c r="G280" t="n">
-        <v>29.5498123168945</v>
+        <v>29.5498104095459</v>
       </c>
       <c r="H280" t="n">
         <v>2381</v>
@@ -8576,7 +8576,7 @@
         <v>31.5817699432373</v>
       </c>
       <c r="G283" t="n">
-        <v>29.5498123168945</v>
+        <v>29.5498104095459</v>
       </c>
       <c r="H283" t="n">
         <v>120</v>
@@ -8692,7 +8692,7 @@
         <v>33.0304756164551</v>
       </c>
       <c r="G287" t="n">
-        <v>30.9053077697754</v>
+        <v>30.9053058624268</v>
       </c>
       <c r="H287" t="n">
         <v>621</v>
@@ -8721,7 +8721,7 @@
         <v>32.7407341003418</v>
       </c>
       <c r="G288" t="n">
-        <v>30.6342086791992</v>
+        <v>30.6342105865479</v>
       </c>
       <c r="H288" t="n">
         <v>310</v>
@@ -8808,7 +8808,7 @@
         <v>33.754825592041</v>
       </c>
       <c r="G291" t="n">
-        <v>31.5830516815186</v>
+        <v>31.5830535888672</v>
       </c>
       <c r="H291" t="n">
         <v>155</v>
@@ -9011,7 +9011,7 @@
         <v>32.7986793518066</v>
       </c>
       <c r="G298" t="n">
-        <v>30.6884250640869</v>
+        <v>30.6884269714355</v>
       </c>
       <c r="H298" t="n">
         <v>534</v>
@@ -9127,7 +9127,7 @@
         <v>33.0304756164551</v>
       </c>
       <c r="G302" t="n">
-        <v>30.9053077697754</v>
+        <v>30.9053058624268</v>
       </c>
       <c r="H302" t="n">
         <v>103</v>
@@ -9156,7 +9156,7 @@
         <v>32.7407341003418</v>
       </c>
       <c r="G303" t="n">
-        <v>30.6342086791992</v>
+        <v>30.6342105865479</v>
       </c>
       <c r="H303" t="n">
         <v>51</v>
@@ -9243,7 +9243,7 @@
         <v>33.6099548339844</v>
       </c>
       <c r="G306" t="n">
-        <v>31.4475021362305</v>
+        <v>31.4475040435791</v>
       </c>
       <c r="H306" t="n">
         <v>517</v>
@@ -9359,7 +9359,7 @@
         <v>33.6099548339844</v>
       </c>
       <c r="G310" t="n">
-        <v>31.4475021362305</v>
+        <v>31.4475040435791</v>
       </c>
       <c r="H310" t="n">
         <v>293</v>
@@ -9417,7 +9417,7 @@
         <v>33.9576454162598</v>
       </c>
       <c r="G312" t="n">
-        <v>31.7728233337402</v>
+        <v>31.7728252410889</v>
       </c>
       <c r="H312" t="n">
         <v>120</v>
@@ -9475,7 +9475,7 @@
         <v>34.1314888000488</v>
       </c>
       <c r="G314" t="n">
-        <v>31.9354801177979</v>
+        <v>31.9354820251465</v>
       </c>
       <c r="H314" t="n">
         <v>448</v>
@@ -9504,7 +9504,7 @@
         <v>34.1314888000488</v>
       </c>
       <c r="G315" t="n">
-        <v>31.9354801177979</v>
+        <v>31.9354820251465</v>
       </c>
       <c r="H315" t="n">
         <v>603</v>
@@ -9533,7 +9533,7 @@
         <v>34.1314888000488</v>
       </c>
       <c r="G316" t="n">
-        <v>31.9354801177979</v>
+        <v>31.9354820251465</v>
       </c>
       <c r="H316" t="n">
         <v>293</v>
@@ -9678,7 +9678,7 @@
         <v>38.2458114624023</v>
       </c>
       <c r="G321" t="n">
-        <v>35.7850875854492</v>
+        <v>35.7850914001465</v>
       </c>
       <c r="H321" t="n">
         <v>4762</v>
@@ -9794,7 +9794,7 @@
         <v>42.9106407165527</v>
       </c>
       <c r="G325" t="n">
-        <v>40.149787902832</v>
+        <v>40.1497840881348</v>
       </c>
       <c r="H325" t="n">
         <v>3969</v>
@@ -9910,7 +9910,7 @@
         <v>39.6655426025391</v>
       </c>
       <c r="G329" t="n">
-        <v>37.1134796142578</v>
+        <v>37.1134757995605</v>
       </c>
       <c r="H329" t="n">
         <v>742</v>
@@ -9939,7 +9939,7 @@
         <v>39.0281143188477</v>
       </c>
       <c r="G330" t="n">
-        <v>36.5170593261719</v>
+        <v>36.5170631408691</v>
       </c>
       <c r="H330" t="n">
         <v>638</v>
@@ -9997,7 +9997,7 @@
         <v>41.8965492248535</v>
       </c>
       <c r="G332" t="n">
-        <v>39.2009391784668</v>
+        <v>39.2009429931641</v>
       </c>
       <c r="H332" t="n">
         <v>1069</v>
@@ -10171,7 +10171,7 @@
         <v>52.1533813476562</v>
       </c>
       <c r="G338" t="n">
-        <v>48.7978553771973</v>
+        <v>48.7978515625</v>
       </c>
       <c r="H338" t="n">
         <v>17463</v>
@@ -10374,7 +10374,7 @@
         <v>75.3326644897461</v>
       </c>
       <c r="G345" t="n">
-        <v>70.4857940673828</v>
+        <v>70.4857864379883</v>
       </c>
       <c r="H345" t="n">
         <v>4434</v>
@@ -10432,7 +10432,7 @@
         <v>85.7633361816406</v>
       </c>
       <c r="G347" t="n">
-        <v>80.245361328125</v>
+        <v>80.2453536987305</v>
       </c>
       <c r="H347" t="n">
         <v>19879</v>
@@ -10461,7 +10461,7 @@
         <v>83.0397720336914</v>
       </c>
       <c r="G348" t="n">
-        <v>77.697021484375</v>
+        <v>77.6970291137695</v>
       </c>
       <c r="H348" t="n">
         <v>6454</v>
@@ -10519,7 +10519,7 @@
         <v>81.9387588500977</v>
       </c>
       <c r="G350" t="n">
-        <v>76.6668472290039</v>
+        <v>76.6668548583984</v>
       </c>
       <c r="H350" t="n">
         <v>4711</v>
@@ -10606,7 +10606,7 @@
         <v>84.5464248657227</v>
       </c>
       <c r="G353" t="n">
-        <v>79.1067352294922</v>
+        <v>79.1067428588867</v>
       </c>
       <c r="H353" t="n">
         <v>2916</v>
@@ -10751,7 +10751,7 @@
         <v>128.355270385742</v>
       </c>
       <c r="G358" t="n">
-        <v>120.096939086914</v>
+        <v>120.096946716309</v>
       </c>
       <c r="H358" t="n">
         <v>7437</v>
@@ -10838,7 +10838,7 @@
         <v>175.727920532227</v>
       </c>
       <c r="G361" t="n">
-        <v>164.421661376953</v>
+        <v>164.421646118164</v>
       </c>
       <c r="H361" t="n">
         <v>27421</v>
@@ -10896,7 +10896,7 @@
         <v>183.985534667969</v>
       </c>
       <c r="G363" t="n">
-        <v>172.147964477539</v>
+        <v>172.147979736328</v>
       </c>
       <c r="H363" t="n">
         <v>21001</v>
@@ -10925,7 +10925,7 @@
         <v>177.031753540039</v>
       </c>
       <c r="G364" t="n">
-        <v>165.6416015625</v>
+        <v>165.641586303711</v>
       </c>
       <c r="H364" t="n">
         <v>6609</v>
@@ -10954,7 +10954,7 @@
         <v>186.882949829102</v>
       </c>
       <c r="G365" t="n">
-        <v>174.858963012695</v>
+        <v>174.858978271484</v>
       </c>
       <c r="H365" t="n">
         <v>8196</v>
@@ -11012,7 +11012,7 @@
         <v>161.3857421875</v>
       </c>
       <c r="G367" t="n">
-        <v>151.002258300781</v>
+        <v>151.002243041992</v>
       </c>
       <c r="H367" t="n">
         <v>11648</v>
@@ -11099,7 +11099,7 @@
         <v>114.100006103516</v>
       </c>
       <c r="G370" t="n">
-        <v>106.758850097656</v>
+        <v>106.758857727051</v>
       </c>
       <c r="H370" t="n">
         <v>22778</v>
@@ -11157,7 +11157,7 @@
         <v>141.103866577148</v>
       </c>
       <c r="G372" t="n">
-        <v>132.025299072266</v>
+        <v>132.025283813477</v>
       </c>
       <c r="H372" t="n">
         <v>20121</v>
@@ -11186,7 +11186,7 @@
         <v>133.222915649414</v>
       </c>
       <c r="G373" t="n">
-        <v>124.651405334473</v>
+        <v>124.651397705078</v>
       </c>
       <c r="H373" t="n">
         <v>6436</v>
@@ -11215,7 +11215,7 @@
         <v>131.716262817383</v>
       </c>
       <c r="G374" t="n">
-        <v>123.241691589355</v>
+        <v>123.241683959961</v>
       </c>
       <c r="H374" t="n">
         <v>1415</v>
@@ -11331,7 +11331,7 @@
         <v>124.125045776367</v>
       </c>
       <c r="G378" t="n">
-        <v>116.138893127441</v>
+        <v>116.138885498047</v>
       </c>
       <c r="H378" t="n">
         <v>3503</v>
@@ -11447,7 +11447,7 @@
         <v>126.500923156738</v>
       </c>
       <c r="G382" t="n">
-        <v>118.361907958984</v>
+        <v>118.36190032959</v>
       </c>
       <c r="H382" t="n">
         <v>2260</v>
@@ -11505,7 +11505,7 @@
         <v>122.328651428223</v>
       </c>
       <c r="G384" t="n">
-        <v>114.458068847656</v>
+        <v>114.458076477051</v>
       </c>
       <c r="H384" t="n">
         <v>534</v>
@@ -11563,7 +11563,7 @@
         <v>116.939468383789</v>
       </c>
       <c r="G386" t="n">
-        <v>109.415634155273</v>
+        <v>109.415626525879</v>
       </c>
       <c r="H386" t="n">
         <v>983</v>
@@ -11621,7 +11621,7 @@
         <v>116.244087219238</v>
       </c>
       <c r="G388" t="n">
-        <v>108.764991760254</v>
+        <v>108.764984130859</v>
       </c>
       <c r="H388" t="n">
         <v>1863</v>
@@ -11650,7 +11650,7 @@
         <v>133.8603515625</v>
       </c>
       <c r="G389" t="n">
-        <v>125.247833251953</v>
+        <v>125.247825622559</v>
       </c>
       <c r="H389" t="n">
         <v>12424</v>
@@ -11679,7 +11679,7 @@
         <v>124.936317443848</v>
       </c>
       <c r="G390" t="n">
-        <v>116.897964477539</v>
+        <v>116.897956848145</v>
       </c>
       <c r="H390" t="n">
         <v>9128</v>
@@ -11766,7 +11766,7 @@
         <v>121.053787231445</v>
       </c>
       <c r="G393" t="n">
-        <v>113.265235900879</v>
+        <v>113.265228271484</v>
       </c>
       <c r="H393" t="n">
         <v>1156</v>
@@ -11795,7 +11795,7 @@
         <v>119.952774047852</v>
       </c>
       <c r="G394" t="n">
-        <v>112.235054016113</v>
+        <v>112.235061645508</v>
       </c>
       <c r="H394" t="n">
         <v>707</v>
@@ -11882,7 +11882,7 @@
         <v>117.692794799805</v>
       </c>
       <c r="G397" t="n">
-        <v>110.120491027832</v>
+        <v>110.120483398438</v>
       </c>
       <c r="H397" t="n">
         <v>811</v>
@@ -11940,7 +11940,7 @@
         <v>115.143074035645</v>
       </c>
       <c r="G399" t="n">
-        <v>107.734809875488</v>
+        <v>107.734817504883</v>
       </c>
       <c r="H399" t="n">
         <v>759</v>
@@ -80038,6 +80038,35 @@
         <v>488</v>
       </c>
       <c r="I2747" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2748">
+      <c r="A2748" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2748" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C2748" t="n">
+        <v>22.6000003814697</v>
+      </c>
+      <c r="D2748" t="n">
+        <v>23.2000007629395</v>
+      </c>
+      <c r="E2748" t="n">
+        <v>22.6000003814697</v>
+      </c>
+      <c r="F2748" t="n">
+        <v>23.2000007629395</v>
+      </c>
+      <c r="G2748" t="n">
+        <v>23.2000007629395</v>
+      </c>
+      <c r="H2748" t="n">
+        <v>72</v>
+      </c>
+      <c r="I2748" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TWL.MI.xlsx
+++ b/data/TWL.MI.xlsx
@@ -427,7 +427,7 @@
         <v>23.8167095184326</v>
       </c>
       <c r="G2" t="n">
-        <v>22.2843532562256</v>
+        <v>22.284351348877</v>
       </c>
       <c r="H2" t="n">
         <v>379</v>
@@ -717,7 +717,7 @@
         <v>22.0058288574219</v>
       </c>
       <c r="G12" t="n">
-        <v>20.5899810791016</v>
+        <v>20.5899829864502</v>
       </c>
       <c r="H12" t="n">
         <v>396</v>
@@ -746,7 +746,7 @@
         <v>21.4408340454102</v>
       </c>
       <c r="G13" t="n">
-        <v>20.0613384246826</v>
+        <v>20.0613403320312</v>
       </c>
       <c r="H13" t="n">
         <v>345</v>
@@ -775,7 +775,7 @@
         <v>19.1229057312012</v>
       </c>
       <c r="G14" t="n">
-        <v>17.8925457000732</v>
+        <v>17.8925437927246</v>
       </c>
       <c r="H14" t="n">
         <v>983</v>
@@ -833,7 +833,7 @@
         <v>20.8613529205322</v>
       </c>
       <c r="G16" t="n">
-        <v>19.5191402435303</v>
+        <v>19.5191421508789</v>
       </c>
       <c r="H16" t="n">
         <v>172</v>
@@ -862,7 +862,7 @@
         <v>20.8613529205322</v>
       </c>
       <c r="G17" t="n">
-        <v>19.5191402435303</v>
+        <v>19.5191421508789</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
         <v>20.8613529205322</v>
       </c>
       <c r="G18" t="n">
-        <v>19.5191402435303</v>
+        <v>19.5191421508789</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
         <v>20.8613529205322</v>
       </c>
       <c r="G19" t="n">
-        <v>19.5191402435303</v>
+        <v>19.5191421508789</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -978,7 +978,7 @@
         <v>19.7023887634277</v>
       </c>
       <c r="G21" t="n">
-        <v>18.4347457885742</v>
+        <v>18.4347438812256</v>
       </c>
       <c r="H21" t="n">
         <v>293</v>
@@ -1007,7 +1007,7 @@
         <v>19.7023887634277</v>
       </c>
       <c r="G22" t="n">
-        <v>18.4347457885742</v>
+        <v>18.4347438812256</v>
       </c>
       <c r="H22" t="n">
         <v>276</v>
@@ -1036,7 +1036,7 @@
         <v>20.2239227294922</v>
       </c>
       <c r="G23" t="n">
-        <v>18.9227237701416</v>
+        <v>18.922721862793</v>
       </c>
       <c r="H23" t="n">
         <v>776</v>
@@ -1094,7 +1094,7 @@
         <v>19.6154651641846</v>
       </c>
       <c r="G25" t="n">
-        <v>18.3534126281738</v>
+        <v>18.3534145355225</v>
       </c>
       <c r="H25" t="n">
         <v>448</v>
@@ -1152,7 +1152,7 @@
         <v>19.1229057312012</v>
       </c>
       <c r="G27" t="n">
-        <v>17.8925457000732</v>
+        <v>17.8925437927246</v>
       </c>
       <c r="H27" t="n">
         <v>86</v>
@@ -1181,7 +1181,7 @@
         <v>18.282657623291</v>
       </c>
       <c r="G28" t="n">
-        <v>17.1063575744629</v>
+        <v>17.1063594818115</v>
       </c>
       <c r="H28" t="n">
         <v>86</v>
@@ -1210,7 +1210,7 @@
         <v>19.1229057312012</v>
       </c>
       <c r="G29" t="n">
-        <v>17.8925457000732</v>
+        <v>17.8925437927246</v>
       </c>
       <c r="H29" t="n">
         <v>2519</v>
@@ -1268,7 +1268,7 @@
         <v>18.0218906402588</v>
       </c>
       <c r="G31" t="n">
-        <v>16.8623695373535</v>
+        <v>16.8623676300049</v>
       </c>
       <c r="H31" t="n">
         <v>241</v>
@@ -1297,7 +1297,7 @@
         <v>18.8331642150879</v>
       </c>
       <c r="G32" t="n">
-        <v>17.6214447021484</v>
+        <v>17.6214466094971</v>
       </c>
       <c r="H32" t="n">
         <v>69</v>
@@ -1326,7 +1326,7 @@
         <v>18.8331642150879</v>
       </c>
       <c r="G33" t="n">
-        <v>17.6214447021484</v>
+        <v>17.6214466094971</v>
       </c>
       <c r="H33" t="n">
         <v>207</v>
@@ -1355,7 +1355,7 @@
         <v>18.5723972320557</v>
       </c>
       <c r="G34" t="n">
-        <v>17.3774566650391</v>
+        <v>17.3774547576904</v>
       </c>
       <c r="H34" t="n">
         <v>207</v>
@@ -1442,7 +1442,7 @@
         <v>19.1229057312012</v>
       </c>
       <c r="G37" t="n">
-        <v>17.8925457000732</v>
+        <v>17.8925437927246</v>
       </c>
       <c r="H37" t="n">
         <v>258</v>
@@ -1558,7 +1558,7 @@
         <v>20.5716114044189</v>
       </c>
       <c r="G41" t="n">
-        <v>19.2480411529541</v>
+        <v>19.2480430603027</v>
       </c>
       <c r="H41" t="n">
         <v>86</v>
@@ -1587,7 +1587,7 @@
         <v>20.5716114044189</v>
       </c>
       <c r="G42" t="n">
-        <v>19.2480411529541</v>
+        <v>19.2480430603027</v>
       </c>
       <c r="H42" t="n">
         <v>86</v>
@@ -1616,7 +1616,7 @@
         <v>20.5716114044189</v>
       </c>
       <c r="G43" t="n">
-        <v>19.2480411529541</v>
+        <v>19.2480430603027</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -1674,7 +1674,7 @@
         <v>20.5716114044189</v>
       </c>
       <c r="G45" t="n">
-        <v>19.2480411529541</v>
+        <v>19.2480430603027</v>
       </c>
       <c r="H45" t="n">
         <v>465</v>
@@ -1848,7 +1848,7 @@
         <v>21.8754444122314</v>
       </c>
       <c r="G51" t="n">
-        <v>20.4679870605469</v>
+        <v>20.4679851531982</v>
       </c>
       <c r="H51" t="n">
         <v>1069</v>
@@ -1964,7 +1964,7 @@
         <v>22.9764614105225</v>
       </c>
       <c r="G55" t="n">
-        <v>21.4981651306152</v>
+        <v>21.4981632232666</v>
       </c>
       <c r="H55" t="n">
         <v>224</v>
@@ -1993,7 +1993,7 @@
         <v>22.2231349945068</v>
       </c>
       <c r="G56" t="n">
-        <v>20.793306350708</v>
+        <v>20.7933082580566</v>
       </c>
       <c r="H56" t="n">
         <v>483</v>
@@ -2051,7 +2051,7 @@
         <v>21.6436538696289</v>
       </c>
       <c r="G58" t="n">
-        <v>20.2511081695557</v>
+        <v>20.2511100769043</v>
       </c>
       <c r="H58" t="n">
         <v>120</v>
@@ -2109,7 +2109,7 @@
         <v>23.1503067016602</v>
       </c>
       <c r="G60" t="n">
-        <v>21.6608238220215</v>
+        <v>21.6608257293701</v>
       </c>
       <c r="H60" t="n">
         <v>17</v>
@@ -2138,7 +2138,7 @@
         <v>23.1503067016602</v>
       </c>
       <c r="G61" t="n">
-        <v>21.6608238220215</v>
+        <v>21.6608257293701</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -2283,7 +2283,7 @@
         <v>21.7305755615234</v>
       </c>
       <c r="G66" t="n">
-        <v>20.3324394226074</v>
+        <v>20.3324375152588</v>
       </c>
       <c r="H66" t="n">
         <v>120</v>
@@ -2312,7 +2312,7 @@
         <v>21.4408340454102</v>
       </c>
       <c r="G67" t="n">
-        <v>20.0613384246826</v>
+        <v>20.0613403320312</v>
       </c>
       <c r="H67" t="n">
         <v>17</v>
@@ -2341,7 +2341,7 @@
         <v>22.0058288574219</v>
       </c>
       <c r="G68" t="n">
-        <v>20.5899810791016</v>
+        <v>20.5899829864502</v>
       </c>
       <c r="H68" t="n">
         <v>172</v>
@@ -2370,7 +2370,7 @@
         <v>22.0058288574219</v>
       </c>
       <c r="G69" t="n">
-        <v>20.5899810791016</v>
+        <v>20.5899829864502</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -2399,7 +2399,7 @@
         <v>20.8613529205322</v>
       </c>
       <c r="G70" t="n">
-        <v>19.5191402435303</v>
+        <v>19.5191421508789</v>
       </c>
       <c r="H70" t="n">
         <v>1173</v>
@@ -2428,7 +2428,7 @@
         <v>21.1800670623779</v>
       </c>
       <c r="G71" t="n">
-        <v>19.8173503875732</v>
+        <v>19.8173484802246</v>
       </c>
       <c r="H71" t="n">
         <v>103</v>
@@ -2486,7 +2486,7 @@
         <v>19.8327713012695</v>
       </c>
       <c r="G73" t="n">
-        <v>18.5567378997803</v>
+        <v>18.5567398071289</v>
       </c>
       <c r="H73" t="n">
         <v>241</v>
@@ -2515,7 +2515,7 @@
         <v>19.7023887634277</v>
       </c>
       <c r="G74" t="n">
-        <v>18.4347457885742</v>
+        <v>18.4347438812256</v>
       </c>
       <c r="H74" t="n">
         <v>431</v>
@@ -2544,7 +2544,7 @@
         <v>19.7023887634277</v>
       </c>
       <c r="G75" t="n">
-        <v>18.4347457885742</v>
+        <v>18.4347438812256</v>
       </c>
       <c r="H75" t="n">
         <v>120</v>
@@ -2631,7 +2631,7 @@
         <v>19.3257236480713</v>
       </c>
       <c r="G78" t="n">
-        <v>18.0823154449463</v>
+        <v>18.0823135375977</v>
       </c>
       <c r="H78" t="n">
         <v>345</v>
@@ -2660,7 +2660,7 @@
         <v>19.7023887634277</v>
       </c>
       <c r="G79" t="n">
-        <v>18.4347457885742</v>
+        <v>18.4347438812256</v>
       </c>
       <c r="H79" t="n">
         <v>69</v>
@@ -2689,7 +2689,7 @@
         <v>19.7023887634277</v>
       </c>
       <c r="G80" t="n">
-        <v>18.4347457885742</v>
+        <v>18.4347438812256</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -2747,7 +2747,7 @@
         <v>19.1229057312012</v>
       </c>
       <c r="G82" t="n">
-        <v>17.8925457000732</v>
+        <v>17.8925437927246</v>
       </c>
       <c r="H82" t="n">
         <v>345</v>
@@ -2776,7 +2776,7 @@
         <v>19.1229057312012</v>
       </c>
       <c r="G83" t="n">
-        <v>17.8925457000732</v>
+        <v>17.8925437927246</v>
       </c>
       <c r="H83" t="n">
         <v>638</v>
@@ -2950,7 +2950,7 @@
         <v>19.1229057312012</v>
       </c>
       <c r="G89" t="n">
-        <v>17.8925457000732</v>
+        <v>17.8925437927246</v>
       </c>
       <c r="H89" t="n">
         <v>138</v>
@@ -2979,7 +2979,7 @@
         <v>19.1229057312012</v>
       </c>
       <c r="G90" t="n">
-        <v>17.8925457000732</v>
+        <v>17.8925437927246</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -3066,7 +3066,7 @@
         <v>17.8770198822021</v>
       </c>
       <c r="G93" t="n">
-        <v>16.7268180847168</v>
+        <v>16.7268199920654</v>
       </c>
       <c r="H93" t="n">
         <v>241</v>
@@ -3124,7 +3124,7 @@
         <v>19.3257236480713</v>
       </c>
       <c r="G95" t="n">
-        <v>18.0823154449463</v>
+        <v>18.0823135375977</v>
       </c>
       <c r="H95" t="n">
         <v>517</v>
@@ -3182,7 +3182,7 @@
         <v>17.8770198822021</v>
       </c>
       <c r="G97" t="n">
-        <v>16.7268180847168</v>
+        <v>16.7268199920654</v>
       </c>
       <c r="H97" t="n">
         <v>17</v>
@@ -3211,7 +3211,7 @@
         <v>17.8770198822021</v>
       </c>
       <c r="G98" t="n">
-        <v>16.7268180847168</v>
+        <v>16.7268199920654</v>
       </c>
       <c r="H98" t="n">
         <v>138</v>
@@ -3269,7 +3269,7 @@
         <v>18.3261184692383</v>
       </c>
       <c r="G100" t="n">
-        <v>17.1470222473145</v>
+        <v>17.1470241546631</v>
       </c>
       <c r="H100" t="n">
         <v>34</v>
@@ -3443,7 +3443,7 @@
         <v>19.253288269043</v>
       </c>
       <c r="G106" t="n">
-        <v>18.0145378112793</v>
+        <v>18.0145397186279</v>
       </c>
       <c r="H106" t="n">
         <v>17</v>
@@ -3472,7 +3472,7 @@
         <v>19.253288269043</v>
       </c>
       <c r="G107" t="n">
-        <v>18.0145378112793</v>
+        <v>18.0145397186279</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -3588,7 +3588,7 @@
         <v>18.5723972320557</v>
       </c>
       <c r="G111" t="n">
-        <v>17.3774566650391</v>
+        <v>17.3774547576904</v>
       </c>
       <c r="H111" t="n">
         <v>172</v>
@@ -3617,7 +3617,7 @@
         <v>24.9322128295898</v>
       </c>
       <c r="G112" t="n">
-        <v>23.3280830383301</v>
+        <v>23.3280849456787</v>
       </c>
       <c r="H112" t="n">
         <v>2830</v>
@@ -3704,7 +3704,7 @@
         <v>31.436897277832</v>
       </c>
       <c r="G115" t="n">
-        <v>29.4142589569092</v>
+        <v>29.4142608642578</v>
       </c>
       <c r="H115" t="n">
         <v>7800</v>
@@ -3791,7 +3791,7 @@
         <v>25.2074661254883</v>
       </c>
       <c r="G118" t="n">
-        <v>23.5856285095215</v>
+        <v>23.5856266021729</v>
       </c>
       <c r="H118" t="n">
         <v>3002</v>
@@ -3820,7 +3820,7 @@
         <v>27.728214263916</v>
       </c>
       <c r="G119" t="n">
-        <v>25.9441909790039</v>
+        <v>25.9441928863525</v>
       </c>
       <c r="H119" t="n">
         <v>3796</v>
@@ -3907,7 +3907,7 @@
         <v>25.7145137786865</v>
       </c>
       <c r="G122" t="n">
-        <v>24.0600509643555</v>
+        <v>24.0600528717041</v>
       </c>
       <c r="H122" t="n">
         <v>673</v>
@@ -4052,7 +4052,7 @@
         <v>22.6432590484619</v>
       </c>
       <c r="G127" t="n">
-        <v>21.1864013671875</v>
+        <v>21.1863994598389</v>
       </c>
       <c r="H127" t="n">
         <v>396</v>
@@ -4081,7 +4081,7 @@
         <v>22.6142845153809</v>
       </c>
       <c r="G128" t="n">
-        <v>21.1592903137207</v>
+        <v>21.1592884063721</v>
       </c>
       <c r="H128" t="n">
         <v>120</v>
@@ -4110,7 +4110,7 @@
         <v>22.6142845153809</v>
       </c>
       <c r="G129" t="n">
-        <v>21.1592903137207</v>
+        <v>21.1592884063721</v>
       </c>
       <c r="H129" t="n">
         <v>431</v>
@@ -4139,7 +4139,7 @@
         <v>22.1362113952637</v>
       </c>
       <c r="G130" t="n">
-        <v>20.7119770050049</v>
+        <v>20.7119750976562</v>
       </c>
       <c r="H130" t="n">
         <v>189</v>
@@ -4226,7 +4226,7 @@
         <v>21.4408340454102</v>
       </c>
       <c r="G133" t="n">
-        <v>20.0613384246826</v>
+        <v>20.0613403320312</v>
       </c>
       <c r="H133" t="n">
         <v>120</v>
@@ -4429,7 +4429,7 @@
         <v>22.5418491363525</v>
       </c>
       <c r="G140" t="n">
-        <v>21.0915145874023</v>
+        <v>21.091516494751</v>
       </c>
       <c r="H140" t="n">
         <v>828</v>
@@ -4458,7 +4458,7 @@
         <v>22.454927444458</v>
       </c>
       <c r="G141" t="n">
-        <v>21.0101871490479</v>
+        <v>21.0101852416992</v>
       </c>
       <c r="H141" t="n">
         <v>34</v>
@@ -4545,7 +4545,7 @@
         <v>21.2235279083252</v>
       </c>
       <c r="G144" t="n">
-        <v>19.8580131530762</v>
+        <v>19.8580150604248</v>
       </c>
       <c r="H144" t="n">
         <v>500</v>
@@ -4835,7 +4835,7 @@
         <v>21.4408340454102</v>
       </c>
       <c r="G154" t="n">
-        <v>20.0613384246826</v>
+        <v>20.0613403320312</v>
       </c>
       <c r="H154" t="n">
         <v>155</v>
@@ -4864,7 +4864,7 @@
         <v>21.3249378204346</v>
       </c>
       <c r="G155" t="n">
-        <v>19.9528999328613</v>
+        <v>19.9528980255127</v>
       </c>
       <c r="H155" t="n">
         <v>120</v>
@@ -4980,7 +4980,7 @@
         <v>22.0782642364502</v>
       </c>
       <c r="G159" t="n">
-        <v>20.6577587127686</v>
+        <v>20.6577568054199</v>
       </c>
       <c r="H159" t="n">
         <v>103</v>
@@ -5009,7 +5009,7 @@
         <v>22.0782642364502</v>
       </c>
       <c r="G160" t="n">
-        <v>20.6577587127686</v>
+        <v>20.6577568054199</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -5299,7 +5299,7 @@
         <v>24.3961925506592</v>
       </c>
       <c r="G170" t="n">
-        <v>22.8265495300293</v>
+        <v>22.8265514373779</v>
       </c>
       <c r="H170" t="n">
         <v>327</v>
@@ -5502,7 +5502,7 @@
         <v>26.5547637939453</v>
       </c>
       <c r="G177" t="n">
-        <v>24.8462390899658</v>
+        <v>24.8462409973145</v>
       </c>
       <c r="H177" t="n">
         <v>293</v>
@@ -5531,7 +5531,7 @@
         <v>26.0766906738281</v>
       </c>
       <c r="G178" t="n">
-        <v>24.39892578125</v>
+        <v>24.3989276885986</v>
       </c>
       <c r="H178" t="n">
         <v>276</v>
@@ -5792,7 +5792,7 @@
         <v>25.4827213287354</v>
       </c>
       <c r="G187" t="n">
-        <v>23.8431720733643</v>
+        <v>23.8431739807129</v>
       </c>
       <c r="H187" t="n">
         <v>379</v>
@@ -5879,7 +5879,7 @@
         <v>27.2356548309326</v>
       </c>
       <c r="G190" t="n">
-        <v>25.4833240509033</v>
+        <v>25.4833221435547</v>
       </c>
       <c r="H190" t="n">
         <v>1156</v>
@@ -5908,7 +5908,7 @@
         <v>33.0304756164551</v>
       </c>
       <c r="G191" t="n">
-        <v>30.9053058624268</v>
+        <v>30.9053077697754</v>
       </c>
       <c r="H191" t="n">
         <v>5539</v>
@@ -6111,7 +6111,7 @@
         <v>27.9744930267334</v>
       </c>
       <c r="G198" t="n">
-        <v>26.1746253967285</v>
+        <v>26.1746234893799</v>
       </c>
       <c r="H198" t="n">
         <v>103</v>
@@ -6227,7 +6227,7 @@
         <v>28.0614166259766</v>
       </c>
       <c r="G202" t="n">
-        <v>26.2559547424316</v>
+        <v>26.2559566497803</v>
       </c>
       <c r="H202" t="n">
         <v>69</v>
@@ -6343,7 +6343,7 @@
         <v>27.8296222686768</v>
       </c>
       <c r="G206" t="n">
-        <v>26.0390758514404</v>
+        <v>26.0390739440918</v>
       </c>
       <c r="H206" t="n">
         <v>34</v>
@@ -6459,7 +6459,7 @@
         <v>28.0034675598145</v>
       </c>
       <c r="G210" t="n">
-        <v>26.2017364501953</v>
+        <v>26.2017345428467</v>
       </c>
       <c r="H210" t="n">
         <v>3468</v>
@@ -6488,7 +6488,7 @@
         <v>28.2787227630615</v>
       </c>
       <c r="G211" t="n">
-        <v>26.4592800140381</v>
+        <v>26.4592819213867</v>
       </c>
       <c r="H211" t="n">
         <v>759</v>
@@ -6633,7 +6633,7 @@
         <v>28.336669921875</v>
       </c>
       <c r="G216" t="n">
-        <v>26.513500213623</v>
+        <v>26.5134983062744</v>
       </c>
       <c r="H216" t="n">
         <v>120</v>
@@ -6662,7 +6662,7 @@
         <v>28.336669921875</v>
       </c>
       <c r="G217" t="n">
-        <v>26.513500213623</v>
+        <v>26.5134983062744</v>
       </c>
       <c r="H217" t="n">
         <v>51</v>
@@ -6691,7 +6691,7 @@
         <v>28.336669921875</v>
       </c>
       <c r="G218" t="n">
-        <v>26.513500213623</v>
+        <v>26.5134983062744</v>
       </c>
       <c r="H218" t="n">
         <v>0</v>
@@ -6720,7 +6720,7 @@
         <v>27.9600067138672</v>
       </c>
       <c r="G219" t="n">
-        <v>26.1610717773438</v>
+        <v>26.1610698699951</v>
       </c>
       <c r="H219" t="n">
         <v>172</v>
@@ -6807,7 +6807,7 @@
         <v>26.9169387817383</v>
       </c>
       <c r="G222" t="n">
-        <v>25.1851119995117</v>
+        <v>25.1851139068604</v>
       </c>
       <c r="H222" t="n">
         <v>189</v>
@@ -6836,7 +6836,7 @@
         <v>27.2356548309326</v>
       </c>
       <c r="G223" t="n">
-        <v>25.4833240509033</v>
+        <v>25.4833221435547</v>
       </c>
       <c r="H223" t="n">
         <v>258</v>
@@ -6952,7 +6952,7 @@
         <v>27.5109081268311</v>
       </c>
       <c r="G227" t="n">
-        <v>25.7408657073975</v>
+        <v>25.7408676147461</v>
       </c>
       <c r="H227" t="n">
         <v>448</v>
@@ -7068,7 +7068,7 @@
         <v>26.0766906738281</v>
       </c>
       <c r="G231" t="n">
-        <v>24.39892578125</v>
+        <v>24.3989276885986</v>
       </c>
       <c r="H231" t="n">
         <v>155</v>
@@ -7097,7 +7097,7 @@
         <v>26.0766906738281</v>
       </c>
       <c r="G232" t="n">
-        <v>24.39892578125</v>
+        <v>24.3989276885986</v>
       </c>
       <c r="H232" t="n">
         <v>0</v>
@@ -7126,7 +7126,7 @@
         <v>26.0766906738281</v>
       </c>
       <c r="G233" t="n">
-        <v>24.39892578125</v>
+        <v>24.3989276885986</v>
       </c>
       <c r="H233" t="n">
         <v>155</v>
@@ -7155,7 +7155,7 @@
         <v>25.2074661254883</v>
       </c>
       <c r="G234" t="n">
-        <v>23.5856285095215</v>
+        <v>23.5856266021729</v>
       </c>
       <c r="H234" t="n">
         <v>949</v>
@@ -7387,7 +7387,7 @@
         <v>27.2356548309326</v>
       </c>
       <c r="G242" t="n">
-        <v>25.4833240509033</v>
+        <v>25.4833221435547</v>
       </c>
       <c r="H242" t="n">
         <v>172</v>
@@ -7416,7 +7416,7 @@
         <v>27.2356548309326</v>
       </c>
       <c r="G243" t="n">
-        <v>25.4833240509033</v>
+        <v>25.4833221435547</v>
       </c>
       <c r="H243" t="n">
         <v>0</v>
@@ -7445,7 +7445,7 @@
         <v>27.2356548309326</v>
       </c>
       <c r="G244" t="n">
-        <v>25.4833240509033</v>
+        <v>25.4833221435547</v>
       </c>
       <c r="H244" t="n">
         <v>0</v>
@@ -7561,7 +7561,7 @@
         <v>26.265022277832</v>
       </c>
       <c r="G248" t="n">
-        <v>24.5751399993896</v>
+        <v>24.5751419067383</v>
       </c>
       <c r="H248" t="n">
         <v>310</v>
@@ -7590,7 +7590,7 @@
         <v>26.0766906738281</v>
       </c>
       <c r="G249" t="n">
-        <v>24.39892578125</v>
+        <v>24.3989276885986</v>
       </c>
       <c r="H249" t="n">
         <v>327</v>
@@ -7648,7 +7648,7 @@
         <v>26.1056632995605</v>
       </c>
       <c r="G251" t="n">
-        <v>24.4260349273682</v>
+        <v>24.4260368347168</v>
       </c>
       <c r="H251" t="n">
         <v>276</v>
@@ -7764,7 +7764,7 @@
         <v>26.9169387817383</v>
       </c>
       <c r="G255" t="n">
-        <v>25.1851119995117</v>
+        <v>25.1851139068604</v>
       </c>
       <c r="H255" t="n">
         <v>276</v>
@@ -7793,7 +7793,7 @@
         <v>26.9169387817383</v>
       </c>
       <c r="G256" t="n">
-        <v>25.1851119995117</v>
+        <v>25.1851139068604</v>
       </c>
       <c r="H256" t="n">
         <v>949</v>
@@ -7996,7 +7996,7 @@
         <v>27.2356548309326</v>
       </c>
       <c r="G263" t="n">
-        <v>25.4833240509033</v>
+        <v>25.4833221435547</v>
       </c>
       <c r="H263" t="n">
         <v>500</v>
@@ -8170,7 +8170,7 @@
         <v>27.7861614227295</v>
       </c>
       <c r="G269" t="n">
-        <v>25.9984111785889</v>
+        <v>25.9984092712402</v>
       </c>
       <c r="H269" t="n">
         <v>707</v>
@@ -8199,7 +8199,7 @@
         <v>28.5539741516113</v>
       </c>
       <c r="G270" t="n">
-        <v>26.7168235778809</v>
+        <v>26.7168216705322</v>
       </c>
       <c r="H270" t="n">
         <v>51</v>
@@ -8228,7 +8228,7 @@
         <v>28.5539741516113</v>
       </c>
       <c r="G271" t="n">
-        <v>26.7168235778809</v>
+        <v>26.7168216705322</v>
       </c>
       <c r="H271" t="n">
         <v>379</v>
@@ -8257,7 +8257,7 @@
         <v>29.6115303039551</v>
       </c>
       <c r="G272" t="n">
-        <v>27.706335067749</v>
+        <v>27.7063369750977</v>
       </c>
       <c r="H272" t="n">
         <v>1311</v>
@@ -8286,7 +8286,7 @@
         <v>32.2771453857422</v>
       </c>
       <c r="G273" t="n">
-        <v>30.2004470825195</v>
+        <v>30.2004451751709</v>
       </c>
       <c r="H273" t="n">
         <v>5142</v>
@@ -8373,7 +8373,7 @@
         <v>30.9153652191162</v>
       </c>
       <c r="G276" t="n">
-        <v>28.9262828826904</v>
+        <v>28.9262809753418</v>
       </c>
       <c r="H276" t="n">
         <v>8162</v>
@@ -8489,7 +8489,7 @@
         <v>31.5817699432373</v>
       </c>
       <c r="G280" t="n">
-        <v>29.5498104095459</v>
+        <v>29.5498123168945</v>
       </c>
       <c r="H280" t="n">
         <v>2381</v>
@@ -8576,7 +8576,7 @@
         <v>31.5817699432373</v>
       </c>
       <c r="G283" t="n">
-        <v>29.5498104095459</v>
+        <v>29.5498123168945</v>
       </c>
       <c r="H283" t="n">
         <v>120</v>
@@ -8692,7 +8692,7 @@
         <v>33.0304756164551</v>
       </c>
       <c r="G287" t="n">
-        <v>30.9053058624268</v>
+        <v>30.9053077697754</v>
       </c>
       <c r="H287" t="n">
         <v>621</v>
@@ -8721,7 +8721,7 @@
         <v>32.7407341003418</v>
       </c>
       <c r="G288" t="n">
-        <v>30.6342105865479</v>
+        <v>30.6342086791992</v>
       </c>
       <c r="H288" t="n">
         <v>310</v>
@@ -8808,7 +8808,7 @@
         <v>33.754825592041</v>
       </c>
       <c r="G291" t="n">
-        <v>31.5830535888672</v>
+        <v>31.5830516815186</v>
       </c>
       <c r="H291" t="n">
         <v>155</v>
@@ -9011,7 +9011,7 @@
         <v>32.7986793518066</v>
       </c>
       <c r="G298" t="n">
-        <v>30.6884269714355</v>
+        <v>30.6884250640869</v>
       </c>
       <c r="H298" t="n">
         <v>534</v>
@@ -9127,7 +9127,7 @@
         <v>33.0304756164551</v>
       </c>
       <c r="G302" t="n">
-        <v>30.9053058624268</v>
+        <v>30.9053077697754</v>
       </c>
       <c r="H302" t="n">
         <v>103</v>
@@ -9156,7 +9156,7 @@
         <v>32.7407341003418</v>
       </c>
       <c r="G303" t="n">
-        <v>30.6342105865479</v>
+        <v>30.6342086791992</v>
       </c>
       <c r="H303" t="n">
         <v>51</v>
@@ -9243,7 +9243,7 @@
         <v>33.6099548339844</v>
       </c>
       <c r="G306" t="n">
-        <v>31.4475040435791</v>
+        <v>31.4475021362305</v>
       </c>
       <c r="H306" t="n">
         <v>517</v>
@@ -9359,7 +9359,7 @@
         <v>33.6099548339844</v>
       </c>
       <c r="G310" t="n">
-        <v>31.4475040435791</v>
+        <v>31.4475021362305</v>
       </c>
       <c r="H310" t="n">
         <v>293</v>
@@ -9417,7 +9417,7 @@
         <v>33.9576454162598</v>
       </c>
       <c r="G312" t="n">
-        <v>31.7728252410889</v>
+        <v>31.7728233337402</v>
       </c>
       <c r="H312" t="n">
         <v>120</v>
@@ -9475,7 +9475,7 @@
         <v>34.1314888000488</v>
       </c>
       <c r="G314" t="n">
-        <v>31.9354820251465</v>
+        <v>31.9354801177979</v>
       </c>
       <c r="H314" t="n">
         <v>448</v>
@@ -9504,7 +9504,7 @@
         <v>34.1314888000488</v>
       </c>
       <c r="G315" t="n">
-        <v>31.9354820251465</v>
+        <v>31.9354801177979</v>
       </c>
       <c r="H315" t="n">
         <v>603</v>
@@ -9533,7 +9533,7 @@
         <v>34.1314888000488</v>
       </c>
       <c r="G316" t="n">
-        <v>31.9354820251465</v>
+        <v>31.9354801177979</v>
       </c>
       <c r="H316" t="n">
         <v>293</v>
@@ -9678,7 +9678,7 @@
         <v>38.2458114624023</v>
       </c>
       <c r="G321" t="n">
-        <v>35.7850914001465</v>
+        <v>35.7850875854492</v>
       </c>
       <c r="H321" t="n">
         <v>4762</v>
@@ -9794,7 +9794,7 @@
         <v>42.9106407165527</v>
       </c>
       <c r="G325" t="n">
-        <v>40.1497840881348</v>
+        <v>40.149787902832</v>
       </c>
       <c r="H325" t="n">
         <v>3969</v>
@@ -9910,7 +9910,7 @@
         <v>39.6655426025391</v>
       </c>
       <c r="G329" t="n">
-        <v>37.1134757995605</v>
+        <v>37.1134796142578</v>
       </c>
       <c r="H329" t="n">
         <v>742</v>
@@ -9939,7 +9939,7 @@
         <v>39.0281143188477</v>
       </c>
       <c r="G330" t="n">
-        <v>36.5170631408691</v>
+        <v>36.5170593261719</v>
       </c>
       <c r="H330" t="n">
         <v>638</v>
@@ -9997,7 +9997,7 @@
         <v>41.8965492248535</v>
       </c>
       <c r="G332" t="n">
-        <v>39.2009429931641</v>
+        <v>39.2009391784668</v>
       </c>
       <c r="H332" t="n">
         <v>1069</v>
@@ -10171,7 +10171,7 @@
         <v>52.1533813476562</v>
       </c>
       <c r="G338" t="n">
-        <v>48.7978515625</v>
+        <v>48.7978553771973</v>
       </c>
       <c r="H338" t="n">
         <v>17463</v>
@@ -10374,7 +10374,7 @@
         <v>75.3326644897461</v>
       </c>
       <c r="G345" t="n">
-        <v>70.4857864379883</v>
+        <v>70.4857940673828</v>
       </c>
       <c r="H345" t="n">
         <v>4434</v>
@@ -10432,7 +10432,7 @@
         <v>85.7633361816406</v>
       </c>
       <c r="G347" t="n">
-        <v>80.2453536987305</v>
+        <v>80.245361328125</v>
       </c>
       <c r="H347" t="n">
         <v>19879</v>
@@ -10461,7 +10461,7 @@
         <v>83.0397720336914</v>
       </c>
       <c r="G348" t="n">
-        <v>77.6970291137695</v>
+        <v>77.697021484375</v>
       </c>
       <c r="H348" t="n">
         <v>6454</v>
@@ -10519,7 +10519,7 @@
         <v>81.9387588500977</v>
       </c>
       <c r="G350" t="n">
-        <v>76.6668548583984</v>
+        <v>76.6668472290039</v>
       </c>
       <c r="H350" t="n">
         <v>4711</v>
@@ -10606,7 +10606,7 @@
         <v>84.5464248657227</v>
       </c>
       <c r="G353" t="n">
-        <v>79.1067428588867</v>
+        <v>79.1067352294922</v>
       </c>
       <c r="H353" t="n">
         <v>2916</v>
@@ -10751,7 +10751,7 @@
         <v>128.355270385742</v>
       </c>
       <c r="G358" t="n">
-        <v>120.096946716309</v>
+        <v>120.096939086914</v>
       </c>
       <c r="H358" t="n">
         <v>7437</v>
@@ -10838,7 +10838,7 @@
         <v>175.727920532227</v>
       </c>
       <c r="G361" t="n">
-        <v>164.421646118164</v>
+        <v>164.421661376953</v>
       </c>
       <c r="H361" t="n">
         <v>27421</v>
@@ -10896,7 +10896,7 @@
         <v>183.985534667969</v>
       </c>
       <c r="G363" t="n">
-        <v>172.147979736328</v>
+        <v>172.147964477539</v>
       </c>
       <c r="H363" t="n">
         <v>21001</v>
@@ -10925,7 +10925,7 @@
         <v>177.031753540039</v>
       </c>
       <c r="G364" t="n">
-        <v>165.641586303711</v>
+        <v>165.6416015625</v>
       </c>
       <c r="H364" t="n">
         <v>6609</v>
@@ -10954,7 +10954,7 @@
         <v>186.882949829102</v>
       </c>
       <c r="G365" t="n">
-        <v>174.858978271484</v>
+        <v>174.858963012695</v>
       </c>
       <c r="H365" t="n">
         <v>8196</v>
@@ -11012,7 +11012,7 @@
         <v>161.3857421875</v>
       </c>
       <c r="G367" t="n">
-        <v>151.002243041992</v>
+        <v>151.002258300781</v>
       </c>
       <c r="H367" t="n">
         <v>11648</v>
@@ -11099,7 +11099,7 @@
         <v>114.100006103516</v>
       </c>
       <c r="G370" t="n">
-        <v>106.758857727051</v>
+        <v>106.758850097656</v>
       </c>
       <c r="H370" t="n">
         <v>22778</v>
@@ -11157,7 +11157,7 @@
         <v>141.103866577148</v>
       </c>
       <c r="G372" t="n">
-        <v>132.025283813477</v>
+        <v>132.025299072266</v>
       </c>
       <c r="H372" t="n">
         <v>20121</v>
@@ -11186,7 +11186,7 @@
         <v>133.222915649414</v>
       </c>
       <c r="G373" t="n">
-        <v>124.651397705078</v>
+        <v>124.651405334473</v>
       </c>
       <c r="H373" t="n">
         <v>6436</v>
@@ -11215,7 +11215,7 @@
         <v>131.716262817383</v>
       </c>
       <c r="G374" t="n">
-        <v>123.241683959961</v>
+        <v>123.241691589355</v>
       </c>
       <c r="H374" t="n">
         <v>1415</v>
@@ -11331,7 +11331,7 @@
         <v>124.125045776367</v>
       </c>
       <c r="G378" t="n">
-        <v>116.138885498047</v>
+        <v>116.138893127441</v>
       </c>
       <c r="H378" t="n">
         <v>3503</v>
@@ -11447,7 +11447,7 @@
         <v>126.500923156738</v>
       </c>
       <c r="G382" t="n">
-        <v>118.36190032959</v>
+        <v>118.361907958984</v>
       </c>
       <c r="H382" t="n">
         <v>2260</v>
@@ -11505,7 +11505,7 @@
         <v>122.328651428223</v>
       </c>
       <c r="G384" t="n">
-        <v>114.458076477051</v>
+        <v>114.458068847656</v>
       </c>
       <c r="H384" t="n">
         <v>534</v>
@@ -11563,7 +11563,7 @@
         <v>116.939468383789</v>
       </c>
       <c r="G386" t="n">
-        <v>109.415626525879</v>
+        <v>109.415634155273</v>
       </c>
       <c r="H386" t="n">
         <v>983</v>
@@ -11621,7 +11621,7 @@
         <v>116.244087219238</v>
       </c>
       <c r="G388" t="n">
-        <v>108.764984130859</v>
+        <v>108.764991760254</v>
       </c>
       <c r="H388" t="n">
         <v>1863</v>
@@ -11650,7 +11650,7 @@
         <v>133.8603515625</v>
       </c>
       <c r="G389" t="n">
-        <v>125.247825622559</v>
+        <v>125.247833251953</v>
       </c>
       <c r="H389" t="n">
         <v>12424</v>
@@ -11679,7 +11679,7 @@
         <v>124.936317443848</v>
       </c>
       <c r="G390" t="n">
-        <v>116.897956848145</v>
+        <v>116.897964477539</v>
       </c>
       <c r="H390" t="n">
         <v>9128</v>
@@ -11766,7 +11766,7 @@
         <v>121.053787231445</v>
       </c>
       <c r="G393" t="n">
-        <v>113.265228271484</v>
+        <v>113.265235900879</v>
       </c>
       <c r="H393" t="n">
         <v>1156</v>
@@ -11795,7 +11795,7 @@
         <v>119.952774047852</v>
       </c>
       <c r="G394" t="n">
-        <v>112.235061645508</v>
+        <v>112.235054016113</v>
       </c>
       <c r="H394" t="n">
         <v>707</v>
@@ -11882,7 +11882,7 @@
         <v>117.692794799805</v>
       </c>
       <c r="G397" t="n">
-        <v>110.120483398438</v>
+        <v>110.120491027832</v>
       </c>
       <c r="H397" t="n">
         <v>811</v>
@@ -11940,7 +11940,7 @@
         <v>115.143074035645</v>
       </c>
       <c r="G399" t="n">
-        <v>107.734817504883</v>
+        <v>107.734809875488</v>
       </c>
       <c r="H399" t="n">
         <v>759</v>
@@ -80067,6 +80067,35 @@
         <v>72</v>
       </c>
       <c r="I2748" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2749">
+      <c r="A2749" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2749" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2749" t="n">
+        <v>22.6000003814697</v>
+      </c>
+      <c r="D2749" t="n">
+        <v>23.2000007629395</v>
+      </c>
+      <c r="E2749" t="n">
+        <v>22.6000003814697</v>
+      </c>
+      <c r="F2749" t="n">
+        <v>23</v>
+      </c>
+      <c r="G2749" t="n">
+        <v>23</v>
+      </c>
+      <c r="H2749" t="n">
+        <v>4</v>
+      </c>
+      <c r="I2749" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TWL.MI.xlsx
+++ b/data/TWL.MI.xlsx
@@ -80078,13 +80078,13 @@
         <v>46318.2916666667</v>
       </c>
       <c r="C2749" t="n">
-        <v>22.6000003814697</v>
+        <v>23</v>
       </c>
       <c r="D2749" t="n">
-        <v>23.2000007629395</v>
+        <v>23</v>
       </c>
       <c r="E2749" t="n">
-        <v>22.6000003814697</v>
+        <v>23</v>
       </c>
       <c r="F2749" t="n">
         <v>23</v>

--- a/data/TWL.MI.xlsx
+++ b/data/TWL.MI.xlsx
@@ -427,7 +427,7 @@
         <v>23.8167095184326</v>
       </c>
       <c r="G2" t="n">
-        <v>22.284351348877</v>
+        <v>22.2843532562256</v>
       </c>
       <c r="H2" t="n">
         <v>379</v>
@@ -717,7 +717,7 @@
         <v>22.0058288574219</v>
       </c>
       <c r="G12" t="n">
-        <v>20.5899829864502</v>
+        <v>20.5899810791016</v>
       </c>
       <c r="H12" t="n">
         <v>396</v>
@@ -746,7 +746,7 @@
         <v>21.4408340454102</v>
       </c>
       <c r="G13" t="n">
-        <v>20.0613403320312</v>
+        <v>20.0613384246826</v>
       </c>
       <c r="H13" t="n">
         <v>345</v>
@@ -775,7 +775,7 @@
         <v>19.1229057312012</v>
       </c>
       <c r="G14" t="n">
-        <v>17.8925437927246</v>
+        <v>17.8925457000732</v>
       </c>
       <c r="H14" t="n">
         <v>983</v>
@@ -833,7 +833,7 @@
         <v>20.8613529205322</v>
       </c>
       <c r="G16" t="n">
-        <v>19.5191421508789</v>
+        <v>19.5191402435303</v>
       </c>
       <c r="H16" t="n">
         <v>172</v>
@@ -862,7 +862,7 @@
         <v>20.8613529205322</v>
       </c>
       <c r="G17" t="n">
-        <v>19.5191421508789</v>
+        <v>19.5191402435303</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
         <v>20.8613529205322</v>
       </c>
       <c r="G18" t="n">
-        <v>19.5191421508789</v>
+        <v>19.5191402435303</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
         <v>20.8613529205322</v>
       </c>
       <c r="G19" t="n">
-        <v>19.5191421508789</v>
+        <v>19.5191402435303</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -978,7 +978,7 @@
         <v>19.7023887634277</v>
       </c>
       <c r="G21" t="n">
-        <v>18.4347438812256</v>
+        <v>18.4347457885742</v>
       </c>
       <c r="H21" t="n">
         <v>293</v>
@@ -1007,7 +1007,7 @@
         <v>19.7023887634277</v>
       </c>
       <c r="G22" t="n">
-        <v>18.4347438812256</v>
+        <v>18.4347457885742</v>
       </c>
       <c r="H22" t="n">
         <v>276</v>
@@ -1036,7 +1036,7 @@
         <v>20.2239227294922</v>
       </c>
       <c r="G23" t="n">
-        <v>18.922721862793</v>
+        <v>18.9227237701416</v>
       </c>
       <c r="H23" t="n">
         <v>776</v>
@@ -1094,7 +1094,7 @@
         <v>19.6154651641846</v>
       </c>
       <c r="G25" t="n">
-        <v>18.3534145355225</v>
+        <v>18.3534126281738</v>
       </c>
       <c r="H25" t="n">
         <v>448</v>
@@ -1152,7 +1152,7 @@
         <v>19.1229057312012</v>
       </c>
       <c r="G27" t="n">
-        <v>17.8925437927246</v>
+        <v>17.8925457000732</v>
       </c>
       <c r="H27" t="n">
         <v>86</v>
@@ -1181,7 +1181,7 @@
         <v>18.282657623291</v>
       </c>
       <c r="G28" t="n">
-        <v>17.1063594818115</v>
+        <v>17.1063575744629</v>
       </c>
       <c r="H28" t="n">
         <v>86</v>
@@ -1210,7 +1210,7 @@
         <v>19.1229057312012</v>
       </c>
       <c r="G29" t="n">
-        <v>17.8925437927246</v>
+        <v>17.8925457000732</v>
       </c>
       <c r="H29" t="n">
         <v>2519</v>
@@ -1268,7 +1268,7 @@
         <v>18.0218906402588</v>
       </c>
       <c r="G31" t="n">
-        <v>16.8623676300049</v>
+        <v>16.8623695373535</v>
       </c>
       <c r="H31" t="n">
         <v>241</v>
@@ -1297,7 +1297,7 @@
         <v>18.8331642150879</v>
       </c>
       <c r="G32" t="n">
-        <v>17.6214466094971</v>
+        <v>17.6214447021484</v>
       </c>
       <c r="H32" t="n">
         <v>69</v>
@@ -1326,7 +1326,7 @@
         <v>18.8331642150879</v>
       </c>
       <c r="G33" t="n">
-        <v>17.6214466094971</v>
+        <v>17.6214447021484</v>
       </c>
       <c r="H33" t="n">
         <v>207</v>
@@ -1355,7 +1355,7 @@
         <v>18.5723972320557</v>
       </c>
       <c r="G34" t="n">
-        <v>17.3774547576904</v>
+        <v>17.3774566650391</v>
       </c>
       <c r="H34" t="n">
         <v>207</v>
@@ -1442,7 +1442,7 @@
         <v>19.1229057312012</v>
       </c>
       <c r="G37" t="n">
-        <v>17.8925437927246</v>
+        <v>17.8925457000732</v>
       </c>
       <c r="H37" t="n">
         <v>258</v>
@@ -1558,7 +1558,7 @@
         <v>20.5716114044189</v>
       </c>
       <c r="G41" t="n">
-        <v>19.2480430603027</v>
+        <v>19.2480411529541</v>
       </c>
       <c r="H41" t="n">
         <v>86</v>
@@ -1587,7 +1587,7 @@
         <v>20.5716114044189</v>
       </c>
       <c r="G42" t="n">
-        <v>19.2480430603027</v>
+        <v>19.2480411529541</v>
       </c>
       <c r="H42" t="n">
         <v>86</v>
@@ -1616,7 +1616,7 @@
         <v>20.5716114044189</v>
       </c>
       <c r="G43" t="n">
-        <v>19.2480430603027</v>
+        <v>19.2480411529541</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -1674,7 +1674,7 @@
         <v>20.5716114044189</v>
       </c>
       <c r="G45" t="n">
-        <v>19.2480430603027</v>
+        <v>19.2480411529541</v>
       </c>
       <c r="H45" t="n">
         <v>465</v>
@@ -1848,7 +1848,7 @@
         <v>21.8754444122314</v>
       </c>
       <c r="G51" t="n">
-        <v>20.4679851531982</v>
+        <v>20.4679870605469</v>
       </c>
       <c r="H51" t="n">
         <v>1069</v>
@@ -1964,7 +1964,7 @@
         <v>22.9764614105225</v>
       </c>
       <c r="G55" t="n">
-        <v>21.4981632232666</v>
+        <v>21.4981651306152</v>
       </c>
       <c r="H55" t="n">
         <v>224</v>
@@ -1993,7 +1993,7 @@
         <v>22.2231349945068</v>
       </c>
       <c r="G56" t="n">
-        <v>20.7933082580566</v>
+        <v>20.793306350708</v>
       </c>
       <c r="H56" t="n">
         <v>483</v>
@@ -2051,7 +2051,7 @@
         <v>21.6436538696289</v>
       </c>
       <c r="G58" t="n">
-        <v>20.2511100769043</v>
+        <v>20.2511081695557</v>
       </c>
       <c r="H58" t="n">
         <v>120</v>
@@ -2109,7 +2109,7 @@
         <v>23.1503067016602</v>
       </c>
       <c r="G60" t="n">
-        <v>21.6608257293701</v>
+        <v>21.6608238220215</v>
       </c>
       <c r="H60" t="n">
         <v>17</v>
@@ -2138,7 +2138,7 @@
         <v>23.1503067016602</v>
       </c>
       <c r="G61" t="n">
-        <v>21.6608257293701</v>
+        <v>21.6608238220215</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -2283,7 +2283,7 @@
         <v>21.7305755615234</v>
       </c>
       <c r="G66" t="n">
-        <v>20.3324375152588</v>
+        <v>20.3324394226074</v>
       </c>
       <c r="H66" t="n">
         <v>120</v>
@@ -2312,7 +2312,7 @@
         <v>21.4408340454102</v>
       </c>
       <c r="G67" t="n">
-        <v>20.0613403320312</v>
+        <v>20.0613384246826</v>
       </c>
       <c r="H67" t="n">
         <v>17</v>
@@ -2341,7 +2341,7 @@
         <v>22.0058288574219</v>
       </c>
       <c r="G68" t="n">
-        <v>20.5899829864502</v>
+        <v>20.5899810791016</v>
       </c>
       <c r="H68" t="n">
         <v>172</v>
@@ -2370,7 +2370,7 @@
         <v>22.0058288574219</v>
       </c>
       <c r="G69" t="n">
-        <v>20.5899829864502</v>
+        <v>20.5899810791016</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -2399,7 +2399,7 @@
         <v>20.8613529205322</v>
       </c>
       <c r="G70" t="n">
-        <v>19.5191421508789</v>
+        <v>19.5191402435303</v>
       </c>
       <c r="H70" t="n">
         <v>1173</v>
@@ -2428,7 +2428,7 @@
         <v>21.1800670623779</v>
       </c>
       <c r="G71" t="n">
-        <v>19.8173484802246</v>
+        <v>19.8173503875732</v>
       </c>
       <c r="H71" t="n">
         <v>103</v>
@@ -2486,7 +2486,7 @@
         <v>19.8327713012695</v>
       </c>
       <c r="G73" t="n">
-        <v>18.5567398071289</v>
+        <v>18.5567378997803</v>
       </c>
       <c r="H73" t="n">
         <v>241</v>
@@ -2515,7 +2515,7 @@
         <v>19.7023887634277</v>
       </c>
       <c r="G74" t="n">
-        <v>18.4347438812256</v>
+        <v>18.4347457885742</v>
       </c>
       <c r="H74" t="n">
         <v>431</v>
@@ -2544,7 +2544,7 @@
         <v>19.7023887634277</v>
       </c>
       <c r="G75" t="n">
-        <v>18.4347438812256</v>
+        <v>18.4347457885742</v>
       </c>
       <c r="H75" t="n">
         <v>120</v>
@@ -2631,7 +2631,7 @@
         <v>19.3257236480713</v>
       </c>
       <c r="G78" t="n">
-        <v>18.0823135375977</v>
+        <v>18.0823154449463</v>
       </c>
       <c r="H78" t="n">
         <v>345</v>
@@ -2660,7 +2660,7 @@
         <v>19.7023887634277</v>
       </c>
       <c r="G79" t="n">
-        <v>18.4347438812256</v>
+        <v>18.4347457885742</v>
       </c>
       <c r="H79" t="n">
         <v>69</v>
@@ -2689,7 +2689,7 @@
         <v>19.7023887634277</v>
       </c>
       <c r="G80" t="n">
-        <v>18.4347438812256</v>
+        <v>18.4347457885742</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -2747,7 +2747,7 @@
         <v>19.1229057312012</v>
       </c>
       <c r="G82" t="n">
-        <v>17.8925437927246</v>
+        <v>17.8925457000732</v>
       </c>
       <c r="H82" t="n">
         <v>345</v>
@@ -2776,7 +2776,7 @@
         <v>19.1229057312012</v>
       </c>
       <c r="G83" t="n">
-        <v>17.8925437927246</v>
+        <v>17.8925457000732</v>
       </c>
       <c r="H83" t="n">
         <v>638</v>
@@ -2950,7 +2950,7 @@
         <v>19.1229057312012</v>
       </c>
       <c r="G89" t="n">
-        <v>17.8925437927246</v>
+        <v>17.8925457000732</v>
       </c>
       <c r="H89" t="n">
         <v>138</v>
@@ -2979,7 +2979,7 @@
         <v>19.1229057312012</v>
       </c>
       <c r="G90" t="n">
-        <v>17.8925437927246</v>
+        <v>17.8925457000732</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -3066,7 +3066,7 @@
         <v>17.8770198822021</v>
       </c>
       <c r="G93" t="n">
-        <v>16.7268199920654</v>
+        <v>16.7268180847168</v>
       </c>
       <c r="H93" t="n">
         <v>241</v>
@@ -3124,7 +3124,7 @@
         <v>19.3257236480713</v>
       </c>
       <c r="G95" t="n">
-        <v>18.0823135375977</v>
+        <v>18.0823154449463</v>
       </c>
       <c r="H95" t="n">
         <v>517</v>
@@ -3182,7 +3182,7 @@
         <v>17.8770198822021</v>
       </c>
       <c r="G97" t="n">
-        <v>16.7268199920654</v>
+        <v>16.7268180847168</v>
       </c>
       <c r="H97" t="n">
         <v>17</v>
@@ -3211,7 +3211,7 @@
         <v>17.8770198822021</v>
       </c>
       <c r="G98" t="n">
-        <v>16.7268199920654</v>
+        <v>16.7268180847168</v>
       </c>
       <c r="H98" t="n">
         <v>138</v>
@@ -3269,7 +3269,7 @@
         <v>18.3261184692383</v>
       </c>
       <c r="G100" t="n">
-        <v>17.1470241546631</v>
+        <v>17.1470222473145</v>
       </c>
       <c r="H100" t="n">
         <v>34</v>
@@ -3443,7 +3443,7 @@
         <v>19.253288269043</v>
       </c>
       <c r="G106" t="n">
-        <v>18.0145397186279</v>
+        <v>18.0145378112793</v>
       </c>
       <c r="H106" t="n">
         <v>17</v>
@@ -3472,7 +3472,7 @@
         <v>19.253288269043</v>
       </c>
       <c r="G107" t="n">
-        <v>18.0145397186279</v>
+        <v>18.0145378112793</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -3588,7 +3588,7 @@
         <v>18.5723972320557</v>
       </c>
       <c r="G111" t="n">
-        <v>17.3774547576904</v>
+        <v>17.3774566650391</v>
       </c>
       <c r="H111" t="n">
         <v>172</v>
@@ -3617,7 +3617,7 @@
         <v>24.9322128295898</v>
       </c>
       <c r="G112" t="n">
-        <v>23.3280849456787</v>
+        <v>23.3280830383301</v>
       </c>
       <c r="H112" t="n">
         <v>2830</v>
@@ -3704,7 +3704,7 @@
         <v>31.436897277832</v>
       </c>
       <c r="G115" t="n">
-        <v>29.4142608642578</v>
+        <v>29.4142589569092</v>
       </c>
       <c r="H115" t="n">
         <v>7800</v>
@@ -3791,7 +3791,7 @@
         <v>25.2074661254883</v>
       </c>
       <c r="G118" t="n">
-        <v>23.5856266021729</v>
+        <v>23.5856285095215</v>
       </c>
       <c r="H118" t="n">
         <v>3002</v>
@@ -3820,7 +3820,7 @@
         <v>27.728214263916</v>
       </c>
       <c r="G119" t="n">
-        <v>25.9441928863525</v>
+        <v>25.9441909790039</v>
       </c>
       <c r="H119" t="n">
         <v>3796</v>
@@ -3907,7 +3907,7 @@
         <v>25.7145137786865</v>
       </c>
       <c r="G122" t="n">
-        <v>24.0600528717041</v>
+        <v>24.0600509643555</v>
       </c>
       <c r="H122" t="n">
         <v>673</v>
@@ -4052,7 +4052,7 @@
         <v>22.6432590484619</v>
       </c>
       <c r="G127" t="n">
-        <v>21.1863994598389</v>
+        <v>21.1864013671875</v>
       </c>
       <c r="H127" t="n">
         <v>396</v>
@@ -4081,7 +4081,7 @@
         <v>22.6142845153809</v>
       </c>
       <c r="G128" t="n">
-        <v>21.1592884063721</v>
+        <v>21.1592903137207</v>
       </c>
       <c r="H128" t="n">
         <v>120</v>
@@ -4110,7 +4110,7 @@
         <v>22.6142845153809</v>
       </c>
       <c r="G129" t="n">
-        <v>21.1592884063721</v>
+        <v>21.1592903137207</v>
       </c>
       <c r="H129" t="n">
         <v>431</v>
@@ -4139,7 +4139,7 @@
         <v>22.1362113952637</v>
       </c>
       <c r="G130" t="n">
-        <v>20.7119750976562</v>
+        <v>20.7119770050049</v>
       </c>
       <c r="H130" t="n">
         <v>189</v>
@@ -4226,7 +4226,7 @@
         <v>21.4408340454102</v>
       </c>
       <c r="G133" t="n">
-        <v>20.0613403320312</v>
+        <v>20.0613384246826</v>
       </c>
       <c r="H133" t="n">
         <v>120</v>
@@ -4429,7 +4429,7 @@
         <v>22.5418491363525</v>
       </c>
       <c r="G140" t="n">
-        <v>21.091516494751</v>
+        <v>21.0915145874023</v>
       </c>
       <c r="H140" t="n">
         <v>828</v>
@@ -4458,7 +4458,7 @@
         <v>22.454927444458</v>
       </c>
       <c r="G141" t="n">
-        <v>21.0101852416992</v>
+        <v>21.0101871490479</v>
       </c>
       <c r="H141" t="n">
         <v>34</v>
@@ -4545,7 +4545,7 @@
         <v>21.2235279083252</v>
       </c>
       <c r="G144" t="n">
-        <v>19.8580150604248</v>
+        <v>19.8580131530762</v>
       </c>
       <c r="H144" t="n">
         <v>500</v>
@@ -4835,7 +4835,7 @@
         <v>21.4408340454102</v>
       </c>
       <c r="G154" t="n">
-        <v>20.0613403320312</v>
+        <v>20.0613384246826</v>
       </c>
       <c r="H154" t="n">
         <v>155</v>
@@ -4864,7 +4864,7 @@
         <v>21.3249378204346</v>
       </c>
       <c r="G155" t="n">
-        <v>19.9528980255127</v>
+        <v>19.9528999328613</v>
       </c>
       <c r="H155" t="n">
         <v>120</v>
@@ -4980,7 +4980,7 @@
         <v>22.0782642364502</v>
       </c>
       <c r="G159" t="n">
-        <v>20.6577568054199</v>
+        <v>20.6577587127686</v>
       </c>
       <c r="H159" t="n">
         <v>103</v>
@@ -5009,7 +5009,7 @@
         <v>22.0782642364502</v>
       </c>
       <c r="G160" t="n">
-        <v>20.6577568054199</v>
+        <v>20.6577587127686</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -5299,7 +5299,7 @@
         <v>24.3961925506592</v>
       </c>
       <c r="G170" t="n">
-        <v>22.8265514373779</v>
+        <v>22.8265495300293</v>
       </c>
       <c r="H170" t="n">
         <v>327</v>
@@ -5502,7 +5502,7 @@
         <v>26.5547637939453</v>
       </c>
       <c r="G177" t="n">
-        <v>24.8462409973145</v>
+        <v>24.8462390899658</v>
       </c>
       <c r="H177" t="n">
         <v>293</v>
@@ -5531,7 +5531,7 @@
         <v>26.0766906738281</v>
       </c>
       <c r="G178" t="n">
-        <v>24.3989276885986</v>
+        <v>24.39892578125</v>
       </c>
       <c r="H178" t="n">
         <v>276</v>
@@ -5792,7 +5792,7 @@
         <v>25.4827213287354</v>
       </c>
       <c r="G187" t="n">
-        <v>23.8431739807129</v>
+        <v>23.8431720733643</v>
       </c>
       <c r="H187" t="n">
         <v>379</v>
@@ -5879,7 +5879,7 @@
         <v>27.2356548309326</v>
       </c>
       <c r="G190" t="n">
-        <v>25.4833221435547</v>
+        <v>25.4833240509033</v>
       </c>
       <c r="H190" t="n">
         <v>1156</v>
@@ -5908,7 +5908,7 @@
         <v>33.0304756164551</v>
       </c>
       <c r="G191" t="n">
-        <v>30.9053077697754</v>
+        <v>30.9053058624268</v>
       </c>
       <c r="H191" t="n">
         <v>5539</v>
@@ -6111,7 +6111,7 @@
         <v>27.9744930267334</v>
       </c>
       <c r="G198" t="n">
-        <v>26.1746234893799</v>
+        <v>26.1746253967285</v>
       </c>
       <c r="H198" t="n">
         <v>103</v>
@@ -6227,7 +6227,7 @@
         <v>28.0614166259766</v>
       </c>
       <c r="G202" t="n">
-        <v>26.2559566497803</v>
+        <v>26.2559547424316</v>
       </c>
       <c r="H202" t="n">
         <v>69</v>
@@ -6343,7 +6343,7 @@
         <v>27.8296222686768</v>
       </c>
       <c r="G206" t="n">
-        <v>26.0390739440918</v>
+        <v>26.0390758514404</v>
       </c>
       <c r="H206" t="n">
         <v>34</v>
@@ -6459,7 +6459,7 @@
         <v>28.0034675598145</v>
       </c>
       <c r="G210" t="n">
-        <v>26.2017345428467</v>
+        <v>26.2017364501953</v>
       </c>
       <c r="H210" t="n">
         <v>3468</v>
@@ -6488,7 +6488,7 @@
         <v>28.2787227630615</v>
       </c>
       <c r="G211" t="n">
-        <v>26.4592819213867</v>
+        <v>26.4592800140381</v>
       </c>
       <c r="H211" t="n">
         <v>759</v>
@@ -6633,7 +6633,7 @@
         <v>28.336669921875</v>
       </c>
       <c r="G216" t="n">
-        <v>26.5134983062744</v>
+        <v>26.513500213623</v>
       </c>
       <c r="H216" t="n">
         <v>120</v>
@@ -6662,7 +6662,7 @@
         <v>28.336669921875</v>
       </c>
       <c r="G217" t="n">
-        <v>26.5134983062744</v>
+        <v>26.513500213623</v>
       </c>
       <c r="H217" t="n">
         <v>51</v>
@@ -6691,7 +6691,7 @@
         <v>28.336669921875</v>
       </c>
       <c r="G218" t="n">
-        <v>26.5134983062744</v>
+        <v>26.513500213623</v>
       </c>
       <c r="H218" t="n">
         <v>0</v>
@@ -6720,7 +6720,7 @@
         <v>27.9600067138672</v>
       </c>
       <c r="G219" t="n">
-        <v>26.1610698699951</v>
+        <v>26.1610717773438</v>
       </c>
       <c r="H219" t="n">
         <v>172</v>
@@ -6807,7 +6807,7 @@
         <v>26.9169387817383</v>
       </c>
       <c r="G222" t="n">
-        <v>25.1851139068604</v>
+        <v>25.1851119995117</v>
       </c>
       <c r="H222" t="n">
         <v>189</v>
@@ -6836,7 +6836,7 @@
         <v>27.2356548309326</v>
       </c>
       <c r="G223" t="n">
-        <v>25.4833221435547</v>
+        <v>25.4833240509033</v>
       </c>
       <c r="H223" t="n">
         <v>258</v>
@@ -6952,7 +6952,7 @@
         <v>27.5109081268311</v>
       </c>
       <c r="G227" t="n">
-        <v>25.7408676147461</v>
+        <v>25.7408657073975</v>
       </c>
       <c r="H227" t="n">
         <v>448</v>
@@ -7068,7 +7068,7 @@
         <v>26.0766906738281</v>
       </c>
       <c r="G231" t="n">
-        <v>24.3989276885986</v>
+        <v>24.39892578125</v>
       </c>
       <c r="H231" t="n">
         <v>155</v>
@@ -7097,7 +7097,7 @@
         <v>26.0766906738281</v>
       </c>
       <c r="G232" t="n">
-        <v>24.3989276885986</v>
+        <v>24.39892578125</v>
       </c>
       <c r="H232" t="n">
         <v>0</v>
@@ -7126,7 +7126,7 @@
         <v>26.0766906738281</v>
       </c>
       <c r="G233" t="n">
-        <v>24.3989276885986</v>
+        <v>24.39892578125</v>
       </c>
       <c r="H233" t="n">
         <v>155</v>
@@ -7155,7 +7155,7 @@
         <v>25.2074661254883</v>
       </c>
       <c r="G234" t="n">
-        <v>23.5856266021729</v>
+        <v>23.5856285095215</v>
       </c>
       <c r="H234" t="n">
         <v>949</v>
@@ -7387,7 +7387,7 @@
         <v>27.2356548309326</v>
       </c>
       <c r="G242" t="n">
-        <v>25.4833221435547</v>
+        <v>25.4833240509033</v>
       </c>
       <c r="H242" t="n">
         <v>172</v>
@@ -7416,7 +7416,7 @@
         <v>27.2356548309326</v>
       </c>
       <c r="G243" t="n">
-        <v>25.4833221435547</v>
+        <v>25.4833240509033</v>
       </c>
       <c r="H243" t="n">
         <v>0</v>
@@ -7445,7 +7445,7 @@
         <v>27.2356548309326</v>
       </c>
       <c r="G244" t="n">
-        <v>25.4833221435547</v>
+        <v>25.4833240509033</v>
       </c>
       <c r="H244" t="n">
         <v>0</v>
@@ -7561,7 +7561,7 @@
         <v>26.265022277832</v>
       </c>
       <c r="G248" t="n">
-        <v>24.5751419067383</v>
+        <v>24.5751399993896</v>
       </c>
       <c r="H248" t="n">
         <v>310</v>
@@ -7590,7 +7590,7 @@
         <v>26.0766906738281</v>
       </c>
       <c r="G249" t="n">
-        <v>24.3989276885986</v>
+        <v>24.39892578125</v>
       </c>
       <c r="H249" t="n">
         <v>327</v>
@@ -7648,7 +7648,7 @@
         <v>26.1056632995605</v>
       </c>
       <c r="G251" t="n">
-        <v>24.4260368347168</v>
+        <v>24.4260349273682</v>
       </c>
       <c r="H251" t="n">
         <v>276</v>
@@ -7764,7 +7764,7 @@
         <v>26.9169387817383</v>
       </c>
       <c r="G255" t="n">
-        <v>25.1851139068604</v>
+        <v>25.1851119995117</v>
       </c>
       <c r="H255" t="n">
         <v>276</v>
@@ -7793,7 +7793,7 @@
         <v>26.9169387817383</v>
       </c>
       <c r="G256" t="n">
-        <v>25.1851139068604</v>
+        <v>25.1851119995117</v>
       </c>
       <c r="H256" t="n">
         <v>949</v>
@@ -7996,7 +7996,7 @@
         <v>27.2356548309326</v>
       </c>
       <c r="G263" t="n">
-        <v>25.4833221435547</v>
+        <v>25.4833240509033</v>
       </c>
       <c r="H263" t="n">
         <v>500</v>
@@ -8170,7 +8170,7 @@
         <v>27.7861614227295</v>
       </c>
       <c r="G269" t="n">
-        <v>25.9984092712402</v>
+        <v>25.9984111785889</v>
       </c>
       <c r="H269" t="n">
         <v>707</v>
@@ -8199,7 +8199,7 @@
         <v>28.5539741516113</v>
       </c>
       <c r="G270" t="n">
-        <v>26.7168216705322</v>
+        <v>26.7168235778809</v>
       </c>
       <c r="H270" t="n">
         <v>51</v>
@@ -8228,7 +8228,7 @@
         <v>28.5539741516113</v>
       </c>
       <c r="G271" t="n">
-        <v>26.7168216705322</v>
+        <v>26.7168235778809</v>
       </c>
       <c r="H271" t="n">
         <v>379</v>
@@ -8257,7 +8257,7 @@
         <v>29.6115303039551</v>
       </c>
       <c r="G272" t="n">
-        <v>27.7063369750977</v>
+        <v>27.706335067749</v>
       </c>
       <c r="H272" t="n">
         <v>1311</v>
@@ -8286,7 +8286,7 @@
         <v>32.2771453857422</v>
       </c>
       <c r="G273" t="n">
-        <v>30.2004451751709</v>
+        <v>30.2004470825195</v>
       </c>
       <c r="H273" t="n">
         <v>5142</v>
@@ -8373,7 +8373,7 @@
         <v>30.9153652191162</v>
       </c>
       <c r="G276" t="n">
-        <v>28.9262809753418</v>
+        <v>28.9262828826904</v>
       </c>
       <c r="H276" t="n">
         <v>8162</v>
@@ -8489,7 +8489,7 @@
         <v>31.5817699432373</v>
       </c>
       <c r="G280" t="n">
-        <v>29.5498123168945</v>
+        <v>29.5498104095459</v>
       </c>
       <c r="H280" t="n">
         <v>2381</v>
@@ -8576,7 +8576,7 @@
         <v>31.5817699432373</v>
       </c>
       <c r="G283" t="n">
-        <v>29.5498123168945</v>
+        <v>29.5498104095459</v>
       </c>
       <c r="H283" t="n">
         <v>120</v>
@@ -8692,7 +8692,7 @@
         <v>33.0304756164551</v>
       </c>
       <c r="G287" t="n">
-        <v>30.9053077697754</v>
+        <v>30.9053058624268</v>
       </c>
       <c r="H287" t="n">
         <v>621</v>
@@ -8721,7 +8721,7 @@
         <v>32.7407341003418</v>
       </c>
       <c r="G288" t="n">
-        <v>30.6342086791992</v>
+        <v>30.6342105865479</v>
       </c>
       <c r="H288" t="n">
         <v>310</v>
@@ -8808,7 +8808,7 @@
         <v>33.754825592041</v>
       </c>
       <c r="G291" t="n">
-        <v>31.5830516815186</v>
+        <v>31.5830535888672</v>
       </c>
       <c r="H291" t="n">
         <v>155</v>
@@ -9011,7 +9011,7 @@
         <v>32.7986793518066</v>
       </c>
       <c r="G298" t="n">
-        <v>30.6884250640869</v>
+        <v>30.6884269714355</v>
       </c>
       <c r="H298" t="n">
         <v>534</v>
@@ -9127,7 +9127,7 @@
         <v>33.0304756164551</v>
       </c>
       <c r="G302" t="n">
-        <v>30.9053077697754</v>
+        <v>30.9053058624268</v>
       </c>
       <c r="H302" t="n">
         <v>103</v>
@@ -9156,7 +9156,7 @@
         <v>32.7407341003418</v>
       </c>
       <c r="G303" t="n">
-        <v>30.6342086791992</v>
+        <v>30.6342105865479</v>
       </c>
       <c r="H303" t="n">
         <v>51</v>
@@ -9243,7 +9243,7 @@
         <v>33.6099548339844</v>
       </c>
       <c r="G306" t="n">
-        <v>31.4475021362305</v>
+        <v>31.4475040435791</v>
       </c>
       <c r="H306" t="n">
         <v>517</v>
@@ -9359,7 +9359,7 @@
         <v>33.6099548339844</v>
       </c>
       <c r="G310" t="n">
-        <v>31.4475021362305</v>
+        <v>31.4475040435791</v>
       </c>
       <c r="H310" t="n">
         <v>293</v>
@@ -9417,7 +9417,7 @@
         <v>33.9576454162598</v>
       </c>
       <c r="G312" t="n">
-        <v>31.7728233337402</v>
+        <v>31.7728252410889</v>
       </c>
       <c r="H312" t="n">
         <v>120</v>
@@ -9475,7 +9475,7 @@
         <v>34.1314888000488</v>
       </c>
       <c r="G314" t="n">
-        <v>31.9354801177979</v>
+        <v>31.9354820251465</v>
       </c>
       <c r="H314" t="n">
         <v>448</v>
@@ -9504,7 +9504,7 @@
         <v>34.1314888000488</v>
       </c>
       <c r="G315" t="n">
-        <v>31.9354801177979</v>
+        <v>31.9354820251465</v>
       </c>
       <c r="H315" t="n">
         <v>603</v>
@@ -9533,7 +9533,7 @@
         <v>34.1314888000488</v>
       </c>
       <c r="G316" t="n">
-        <v>31.9354801177979</v>
+        <v>31.9354820251465</v>
       </c>
       <c r="H316" t="n">
         <v>293</v>
@@ -9678,7 +9678,7 @@
         <v>38.2458114624023</v>
       </c>
       <c r="G321" t="n">
-        <v>35.7850875854492</v>
+        <v>35.7850914001465</v>
       </c>
       <c r="H321" t="n">
         <v>4762</v>
@@ -9794,7 +9794,7 @@
         <v>42.9106407165527</v>
       </c>
       <c r="G325" t="n">
-        <v>40.149787902832</v>
+        <v>40.1497840881348</v>
       </c>
       <c r="H325" t="n">
         <v>3969</v>
@@ -9910,7 +9910,7 @@
         <v>39.6655426025391</v>
       </c>
       <c r="G329" t="n">
-        <v>37.1134796142578</v>
+        <v>37.1134757995605</v>
       </c>
       <c r="H329" t="n">
         <v>742</v>
@@ -9939,7 +9939,7 @@
         <v>39.0281143188477</v>
       </c>
       <c r="G330" t="n">
-        <v>36.5170593261719</v>
+        <v>36.5170631408691</v>
       </c>
       <c r="H330" t="n">
         <v>638</v>
@@ -9997,7 +9997,7 @@
         <v>41.8965492248535</v>
       </c>
       <c r="G332" t="n">
-        <v>39.2009391784668</v>
+        <v>39.2009429931641</v>
       </c>
       <c r="H332" t="n">
         <v>1069</v>
@@ -10171,7 +10171,7 @@
         <v>52.1533813476562</v>
       </c>
       <c r="G338" t="n">
-        <v>48.7978553771973</v>
+        <v>48.7978515625</v>
       </c>
       <c r="H338" t="n">
         <v>17463</v>
@@ -10374,7 +10374,7 @@
         <v>75.3326644897461</v>
       </c>
       <c r="G345" t="n">
-        <v>70.4857940673828</v>
+        <v>70.4857864379883</v>
       </c>
       <c r="H345" t="n">
         <v>4434</v>
@@ -10432,7 +10432,7 @@
         <v>85.7633361816406</v>
       </c>
       <c r="G347" t="n">
-        <v>80.245361328125</v>
+        <v>80.2453536987305</v>
       </c>
       <c r="H347" t="n">
         <v>19879</v>
@@ -10461,7 +10461,7 @@
         <v>83.0397720336914</v>
       </c>
       <c r="G348" t="n">
-        <v>77.697021484375</v>
+        <v>77.6970291137695</v>
       </c>
       <c r="H348" t="n">
         <v>6454</v>
@@ -10519,7 +10519,7 @@
         <v>81.9387588500977</v>
       </c>
       <c r="G350" t="n">
-        <v>76.6668472290039</v>
+        <v>76.6668548583984</v>
       </c>
       <c r="H350" t="n">
         <v>4711</v>
@@ -10606,7 +10606,7 @@
         <v>84.5464248657227</v>
       </c>
       <c r="G353" t="n">
-        <v>79.1067352294922</v>
+        <v>79.1067428588867</v>
       </c>
       <c r="H353" t="n">
         <v>2916</v>
@@ -10751,7 +10751,7 @@
         <v>128.355270385742</v>
       </c>
       <c r="G358" t="n">
-        <v>120.096939086914</v>
+        <v>120.096946716309</v>
       </c>
       <c r="H358" t="n">
         <v>7437</v>
@@ -10838,7 +10838,7 @@
         <v>175.727920532227</v>
       </c>
       <c r="G361" t="n">
-        <v>164.421661376953</v>
+        <v>164.421646118164</v>
       </c>
       <c r="H361" t="n">
         <v>27421</v>
@@ -10896,7 +10896,7 @@
         <v>183.985534667969</v>
       </c>
       <c r="G363" t="n">
-        <v>172.147964477539</v>
+        <v>172.147979736328</v>
       </c>
       <c r="H363" t="n">
         <v>21001</v>
@@ -10925,7 +10925,7 @@
         <v>177.031753540039</v>
       </c>
       <c r="G364" t="n">
-        <v>165.6416015625</v>
+        <v>165.641586303711</v>
       </c>
       <c r="H364" t="n">
         <v>6609</v>
@@ -10954,7 +10954,7 @@
         <v>186.882949829102</v>
       </c>
       <c r="G365" t="n">
-        <v>174.858963012695</v>
+        <v>174.858978271484</v>
       </c>
       <c r="H365" t="n">
         <v>8196</v>
@@ -11012,7 +11012,7 @@
         <v>161.3857421875</v>
       </c>
       <c r="G367" t="n">
-        <v>151.002258300781</v>
+        <v>151.002243041992</v>
       </c>
       <c r="H367" t="n">
         <v>11648</v>
@@ -11099,7 +11099,7 @@
         <v>114.100006103516</v>
       </c>
       <c r="G370" t="n">
-        <v>106.758850097656</v>
+        <v>106.758857727051</v>
       </c>
       <c r="H370" t="n">
         <v>22778</v>
@@ -11157,7 +11157,7 @@
         <v>141.103866577148</v>
       </c>
       <c r="G372" t="n">
-        <v>132.025299072266</v>
+        <v>132.025283813477</v>
       </c>
       <c r="H372" t="n">
         <v>20121</v>
@@ -11186,7 +11186,7 @@
         <v>133.222915649414</v>
       </c>
       <c r="G373" t="n">
-        <v>124.651405334473</v>
+        <v>124.651397705078</v>
       </c>
       <c r="H373" t="n">
         <v>6436</v>
@@ -11215,7 +11215,7 @@
         <v>131.716262817383</v>
       </c>
       <c r="G374" t="n">
-        <v>123.241691589355</v>
+        <v>123.241683959961</v>
       </c>
       <c r="H374" t="n">
         <v>1415</v>
@@ -11331,7 +11331,7 @@
         <v>124.125045776367</v>
       </c>
       <c r="G378" t="n">
-        <v>116.138893127441</v>
+        <v>116.138885498047</v>
       </c>
       <c r="H378" t="n">
         <v>3503</v>
@@ -11447,7 +11447,7 @@
         <v>126.500923156738</v>
       </c>
       <c r="G382" t="n">
-        <v>118.361907958984</v>
+        <v>118.36190032959</v>
       </c>
       <c r="H382" t="n">
         <v>2260</v>
@@ -11505,7 +11505,7 @@
         <v>122.328651428223</v>
       </c>
       <c r="G384" t="n">
-        <v>114.458068847656</v>
+        <v>114.458076477051</v>
       </c>
       <c r="H384" t="n">
         <v>534</v>
@@ -11563,7 +11563,7 @@
         <v>116.939468383789</v>
       </c>
       <c r="G386" t="n">
-        <v>109.415634155273</v>
+        <v>109.415626525879</v>
       </c>
       <c r="H386" t="n">
         <v>983</v>
@@ -11621,7 +11621,7 @@
         <v>116.244087219238</v>
       </c>
       <c r="G388" t="n">
-        <v>108.764991760254</v>
+        <v>108.764984130859</v>
       </c>
       <c r="H388" t="n">
         <v>1863</v>
@@ -11650,7 +11650,7 @@
         <v>133.8603515625</v>
       </c>
       <c r="G389" t="n">
-        <v>125.247833251953</v>
+        <v>125.247825622559</v>
       </c>
       <c r="H389" t="n">
         <v>12424</v>
@@ -11679,7 +11679,7 @@
         <v>124.936317443848</v>
       </c>
       <c r="G390" t="n">
-        <v>116.897964477539</v>
+        <v>116.897956848145</v>
       </c>
       <c r="H390" t="n">
         <v>9128</v>
@@ -11766,7 +11766,7 @@
         <v>121.053787231445</v>
       </c>
       <c r="G393" t="n">
-        <v>113.265235900879</v>
+        <v>113.265228271484</v>
       </c>
       <c r="H393" t="n">
         <v>1156</v>
@@ -11795,7 +11795,7 @@
         <v>119.952774047852</v>
       </c>
       <c r="G394" t="n">
-        <v>112.235054016113</v>
+        <v>112.235061645508</v>
       </c>
       <c r="H394" t="n">
         <v>707</v>
@@ -11882,7 +11882,7 @@
         <v>117.692794799805</v>
       </c>
       <c r="G397" t="n">
-        <v>110.120491027832</v>
+        <v>110.120483398438</v>
       </c>
       <c r="H397" t="n">
         <v>811</v>
@@ -11940,7 +11940,7 @@
         <v>115.143074035645</v>
       </c>
       <c r="G399" t="n">
-        <v>107.734809875488</v>
+        <v>107.734817504883</v>
       </c>
       <c r="H399" t="n">
         <v>759</v>
@@ -80096,6 +80096,35 @@
         <v>4</v>
       </c>
       <c r="I2749" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2750">
+      <c r="A2750" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2750" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C2750" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2750" t="n">
+        <v>23</v>
+      </c>
+      <c r="E2750" t="n">
+        <v>23</v>
+      </c>
+      <c r="F2750" t="n">
+        <v>23</v>
+      </c>
+      <c r="G2750" t="n">
+        <v>23</v>
+      </c>
+      <c r="H2750" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2750" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TWL.MI.xlsx
+++ b/data/TWL.MI.xlsx
@@ -427,7 +427,7 @@
         <v>23.8167095184326</v>
       </c>
       <c r="G2" t="n">
-        <v>22.2843532562256</v>
+        <v>22.284351348877</v>
       </c>
       <c r="H2" t="n">
         <v>379</v>
@@ -717,7 +717,7 @@
         <v>22.0058288574219</v>
       </c>
       <c r="G12" t="n">
-        <v>20.5899810791016</v>
+        <v>20.5899829864502</v>
       </c>
       <c r="H12" t="n">
         <v>396</v>
@@ -746,7 +746,7 @@
         <v>21.4408340454102</v>
       </c>
       <c r="G13" t="n">
-        <v>20.0613384246826</v>
+        <v>20.0613403320312</v>
       </c>
       <c r="H13" t="n">
         <v>345</v>
@@ -775,7 +775,7 @@
         <v>19.1229057312012</v>
       </c>
       <c r="G14" t="n">
-        <v>17.8925457000732</v>
+        <v>17.8925437927246</v>
       </c>
       <c r="H14" t="n">
         <v>983</v>
@@ -833,7 +833,7 @@
         <v>20.8613529205322</v>
       </c>
       <c r="G16" t="n">
-        <v>19.5191402435303</v>
+        <v>19.5191421508789</v>
       </c>
       <c r="H16" t="n">
         <v>172</v>
@@ -862,7 +862,7 @@
         <v>20.8613529205322</v>
       </c>
       <c r="G17" t="n">
-        <v>19.5191402435303</v>
+        <v>19.5191421508789</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
         <v>20.8613529205322</v>
       </c>
       <c r="G18" t="n">
-        <v>19.5191402435303</v>
+        <v>19.5191421508789</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
         <v>20.8613529205322</v>
       </c>
       <c r="G19" t="n">
-        <v>19.5191402435303</v>
+        <v>19.5191421508789</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -978,7 +978,7 @@
         <v>19.7023887634277</v>
       </c>
       <c r="G21" t="n">
-        <v>18.4347457885742</v>
+        <v>18.4347438812256</v>
       </c>
       <c r="H21" t="n">
         <v>293</v>
@@ -1007,7 +1007,7 @@
         <v>19.7023887634277</v>
       </c>
       <c r="G22" t="n">
-        <v>18.4347457885742</v>
+        <v>18.4347438812256</v>
       </c>
       <c r="H22" t="n">
         <v>276</v>
@@ -1036,7 +1036,7 @@
         <v>20.2239227294922</v>
       </c>
       <c r="G23" t="n">
-        <v>18.9227237701416</v>
+        <v>18.922721862793</v>
       </c>
       <c r="H23" t="n">
         <v>776</v>
@@ -1094,7 +1094,7 @@
         <v>19.6154651641846</v>
       </c>
       <c r="G25" t="n">
-        <v>18.3534126281738</v>
+        <v>18.3534145355225</v>
       </c>
       <c r="H25" t="n">
         <v>448</v>
@@ -1152,7 +1152,7 @@
         <v>19.1229057312012</v>
       </c>
       <c r="G27" t="n">
-        <v>17.8925457000732</v>
+        <v>17.8925437927246</v>
       </c>
       <c r="H27" t="n">
         <v>86</v>
@@ -1181,7 +1181,7 @@
         <v>18.282657623291</v>
       </c>
       <c r="G28" t="n">
-        <v>17.1063575744629</v>
+        <v>17.1063594818115</v>
       </c>
       <c r="H28" t="n">
         <v>86</v>
@@ -1210,7 +1210,7 @@
         <v>19.1229057312012</v>
       </c>
       <c r="G29" t="n">
-        <v>17.8925457000732</v>
+        <v>17.8925437927246</v>
       </c>
       <c r="H29" t="n">
         <v>2519</v>
@@ -1268,7 +1268,7 @@
         <v>18.0218906402588</v>
       </c>
       <c r="G31" t="n">
-        <v>16.8623695373535</v>
+        <v>16.8623676300049</v>
       </c>
       <c r="H31" t="n">
         <v>241</v>
@@ -1297,7 +1297,7 @@
         <v>18.8331642150879</v>
       </c>
       <c r="G32" t="n">
-        <v>17.6214447021484</v>
+        <v>17.6214466094971</v>
       </c>
       <c r="H32" t="n">
         <v>69</v>
@@ -1326,7 +1326,7 @@
         <v>18.8331642150879</v>
       </c>
       <c r="G33" t="n">
-        <v>17.6214447021484</v>
+        <v>17.6214466094971</v>
       </c>
       <c r="H33" t="n">
         <v>207</v>
@@ -1355,7 +1355,7 @@
         <v>18.5723972320557</v>
       </c>
       <c r="G34" t="n">
-        <v>17.3774566650391</v>
+        <v>17.3774547576904</v>
       </c>
       <c r="H34" t="n">
         <v>207</v>
@@ -1442,7 +1442,7 @@
         <v>19.1229057312012</v>
       </c>
       <c r="G37" t="n">
-        <v>17.8925457000732</v>
+        <v>17.8925437927246</v>
       </c>
       <c r="H37" t="n">
         <v>258</v>
@@ -1558,7 +1558,7 @@
         <v>20.5716114044189</v>
       </c>
       <c r="G41" t="n">
-        <v>19.2480411529541</v>
+        <v>19.2480430603027</v>
       </c>
       <c r="H41" t="n">
         <v>86</v>
@@ -1587,7 +1587,7 @@
         <v>20.5716114044189</v>
       </c>
       <c r="G42" t="n">
-        <v>19.2480411529541</v>
+        <v>19.2480430603027</v>
       </c>
       <c r="H42" t="n">
         <v>86</v>
@@ -1616,7 +1616,7 @@
         <v>20.5716114044189</v>
       </c>
       <c r="G43" t="n">
-        <v>19.2480411529541</v>
+        <v>19.2480430603027</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -1674,7 +1674,7 @@
         <v>20.5716114044189</v>
       </c>
       <c r="G45" t="n">
-        <v>19.2480411529541</v>
+        <v>19.2480430603027</v>
       </c>
       <c r="H45" t="n">
         <v>465</v>
@@ -1848,7 +1848,7 @@
         <v>21.8754444122314</v>
       </c>
       <c r="G51" t="n">
-        <v>20.4679870605469</v>
+        <v>20.4679851531982</v>
       </c>
       <c r="H51" t="n">
         <v>1069</v>
@@ -1964,7 +1964,7 @@
         <v>22.9764614105225</v>
       </c>
       <c r="G55" t="n">
-        <v>21.4981651306152</v>
+        <v>21.4981632232666</v>
       </c>
       <c r="H55" t="n">
         <v>224</v>
@@ -1993,7 +1993,7 @@
         <v>22.2231349945068</v>
       </c>
       <c r="G56" t="n">
-        <v>20.793306350708</v>
+        <v>20.7933082580566</v>
       </c>
       <c r="H56" t="n">
         <v>483</v>
@@ -2051,7 +2051,7 @@
         <v>21.6436538696289</v>
       </c>
       <c r="G58" t="n">
-        <v>20.2511081695557</v>
+        <v>20.2511100769043</v>
       </c>
       <c r="H58" t="n">
         <v>120</v>
@@ -2109,7 +2109,7 @@
         <v>23.1503067016602</v>
       </c>
       <c r="G60" t="n">
-        <v>21.6608238220215</v>
+        <v>21.6608257293701</v>
       </c>
       <c r="H60" t="n">
         <v>17</v>
@@ -2138,7 +2138,7 @@
         <v>23.1503067016602</v>
       </c>
       <c r="G61" t="n">
-        <v>21.6608238220215</v>
+        <v>21.6608257293701</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -2283,7 +2283,7 @@
         <v>21.7305755615234</v>
       </c>
       <c r="G66" t="n">
-        <v>20.3324394226074</v>
+        <v>20.3324375152588</v>
       </c>
       <c r="H66" t="n">
         <v>120</v>
@@ -2312,7 +2312,7 @@
         <v>21.4408340454102</v>
       </c>
       <c r="G67" t="n">
-        <v>20.0613384246826</v>
+        <v>20.0613403320312</v>
       </c>
       <c r="H67" t="n">
         <v>17</v>
@@ -2341,7 +2341,7 @@
         <v>22.0058288574219</v>
       </c>
       <c r="G68" t="n">
-        <v>20.5899810791016</v>
+        <v>20.5899829864502</v>
       </c>
       <c r="H68" t="n">
         <v>172</v>
@@ -2370,7 +2370,7 @@
         <v>22.0058288574219</v>
       </c>
       <c r="G69" t="n">
-        <v>20.5899810791016</v>
+        <v>20.5899829864502</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -2399,7 +2399,7 @@
         <v>20.8613529205322</v>
       </c>
       <c r="G70" t="n">
-        <v>19.5191402435303</v>
+        <v>19.5191421508789</v>
       </c>
       <c r="H70" t="n">
         <v>1173</v>
@@ -2428,7 +2428,7 @@
         <v>21.1800670623779</v>
       </c>
       <c r="G71" t="n">
-        <v>19.8173503875732</v>
+        <v>19.8173484802246</v>
       </c>
       <c r="H71" t="n">
         <v>103</v>
@@ -2486,7 +2486,7 @@
         <v>19.8327713012695</v>
       </c>
       <c r="G73" t="n">
-        <v>18.5567378997803</v>
+        <v>18.5567398071289</v>
       </c>
       <c r="H73" t="n">
         <v>241</v>
@@ -2515,7 +2515,7 @@
         <v>19.7023887634277</v>
       </c>
       <c r="G74" t="n">
-        <v>18.4347457885742</v>
+        <v>18.4347438812256</v>
       </c>
       <c r="H74" t="n">
         <v>431</v>
@@ -2544,7 +2544,7 @@
         <v>19.7023887634277</v>
       </c>
       <c r="G75" t="n">
-        <v>18.4347457885742</v>
+        <v>18.4347438812256</v>
       </c>
       <c r="H75" t="n">
         <v>120</v>
@@ -2631,7 +2631,7 @@
         <v>19.3257236480713</v>
       </c>
       <c r="G78" t="n">
-        <v>18.0823154449463</v>
+        <v>18.0823135375977</v>
       </c>
       <c r="H78" t="n">
         <v>345</v>
@@ -2660,7 +2660,7 @@
         <v>19.7023887634277</v>
       </c>
       <c r="G79" t="n">
-        <v>18.4347457885742</v>
+        <v>18.4347438812256</v>
       </c>
       <c r="H79" t="n">
         <v>69</v>
@@ -2689,7 +2689,7 @@
         <v>19.7023887634277</v>
       </c>
       <c r="G80" t="n">
-        <v>18.4347457885742</v>
+        <v>18.4347438812256</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -2747,7 +2747,7 @@
         <v>19.1229057312012</v>
       </c>
       <c r="G82" t="n">
-        <v>17.8925457000732</v>
+        <v>17.8925437927246</v>
       </c>
       <c r="H82" t="n">
         <v>345</v>
@@ -2776,7 +2776,7 @@
         <v>19.1229057312012</v>
       </c>
       <c r="G83" t="n">
-        <v>17.8925457000732</v>
+        <v>17.8925437927246</v>
       </c>
       <c r="H83" t="n">
         <v>638</v>
@@ -2950,7 +2950,7 @@
         <v>19.1229057312012</v>
       </c>
       <c r="G89" t="n">
-        <v>17.8925457000732</v>
+        <v>17.8925437927246</v>
       </c>
       <c r="H89" t="n">
         <v>138</v>
@@ -2979,7 +2979,7 @@
         <v>19.1229057312012</v>
       </c>
       <c r="G90" t="n">
-        <v>17.8925457000732</v>
+        <v>17.8925437927246</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -3066,7 +3066,7 @@
         <v>17.8770198822021</v>
       </c>
       <c r="G93" t="n">
-        <v>16.7268180847168</v>
+        <v>16.7268199920654</v>
       </c>
       <c r="H93" t="n">
         <v>241</v>
@@ -3124,7 +3124,7 @@
         <v>19.3257236480713</v>
       </c>
       <c r="G95" t="n">
-        <v>18.0823154449463</v>
+        <v>18.0823135375977</v>
       </c>
       <c r="H95" t="n">
         <v>517</v>
@@ -3182,7 +3182,7 @@
         <v>17.8770198822021</v>
       </c>
       <c r="G97" t="n">
-        <v>16.7268180847168</v>
+        <v>16.7268199920654</v>
       </c>
       <c r="H97" t="n">
         <v>17</v>
@@ -3211,7 +3211,7 @@
         <v>17.8770198822021</v>
       </c>
       <c r="G98" t="n">
-        <v>16.7268180847168</v>
+        <v>16.7268199920654</v>
       </c>
       <c r="H98" t="n">
         <v>138</v>
@@ -3269,7 +3269,7 @@
         <v>18.3261184692383</v>
       </c>
       <c r="G100" t="n">
-        <v>17.1470222473145</v>
+        <v>17.1470241546631</v>
       </c>
       <c r="H100" t="n">
         <v>34</v>
@@ -3443,7 +3443,7 @@
         <v>19.253288269043</v>
       </c>
       <c r="G106" t="n">
-        <v>18.0145378112793</v>
+        <v>18.0145397186279</v>
       </c>
       <c r="H106" t="n">
         <v>17</v>
@@ -3472,7 +3472,7 @@
         <v>19.253288269043</v>
       </c>
       <c r="G107" t="n">
-        <v>18.0145378112793</v>
+        <v>18.0145397186279</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -3588,7 +3588,7 @@
         <v>18.5723972320557</v>
       </c>
       <c r="G111" t="n">
-        <v>17.3774566650391</v>
+        <v>17.3774547576904</v>
       </c>
       <c r="H111" t="n">
         <v>172</v>
@@ -3617,7 +3617,7 @@
         <v>24.9322128295898</v>
       </c>
       <c r="G112" t="n">
-        <v>23.3280830383301</v>
+        <v>23.3280849456787</v>
       </c>
       <c r="H112" t="n">
         <v>2830</v>
@@ -3704,7 +3704,7 @@
         <v>31.436897277832</v>
       </c>
       <c r="G115" t="n">
-        <v>29.4142589569092</v>
+        <v>29.4142608642578</v>
       </c>
       <c r="H115" t="n">
         <v>7800</v>
@@ -3791,7 +3791,7 @@
         <v>25.2074661254883</v>
       </c>
       <c r="G118" t="n">
-        <v>23.5856285095215</v>
+        <v>23.5856266021729</v>
       </c>
       <c r="H118" t="n">
         <v>3002</v>
@@ -3820,7 +3820,7 @@
         <v>27.728214263916</v>
       </c>
       <c r="G119" t="n">
-        <v>25.9441909790039</v>
+        <v>25.9441928863525</v>
       </c>
       <c r="H119" t="n">
         <v>3796</v>
@@ -3907,7 +3907,7 @@
         <v>25.7145137786865</v>
       </c>
       <c r="G122" t="n">
-        <v>24.0600509643555</v>
+        <v>24.0600528717041</v>
       </c>
       <c r="H122" t="n">
         <v>673</v>
@@ -4052,7 +4052,7 @@
         <v>22.6432590484619</v>
       </c>
       <c r="G127" t="n">
-        <v>21.1864013671875</v>
+        <v>21.1863994598389</v>
       </c>
       <c r="H127" t="n">
         <v>396</v>
@@ -4081,7 +4081,7 @@
         <v>22.6142845153809</v>
       </c>
       <c r="G128" t="n">
-        <v>21.1592903137207</v>
+        <v>21.1592884063721</v>
       </c>
       <c r="H128" t="n">
         <v>120</v>
@@ -4110,7 +4110,7 @@
         <v>22.6142845153809</v>
       </c>
       <c r="G129" t="n">
-        <v>21.1592903137207</v>
+        <v>21.1592884063721</v>
       </c>
       <c r="H129" t="n">
         <v>431</v>
@@ -4139,7 +4139,7 @@
         <v>22.1362113952637</v>
       </c>
       <c r="G130" t="n">
-        <v>20.7119770050049</v>
+        <v>20.7119750976562</v>
       </c>
       <c r="H130" t="n">
         <v>189</v>
@@ -4226,7 +4226,7 @@
         <v>21.4408340454102</v>
       </c>
       <c r="G133" t="n">
-        <v>20.0613384246826</v>
+        <v>20.0613403320312</v>
       </c>
       <c r="H133" t="n">
         <v>120</v>
@@ -4429,7 +4429,7 @@
         <v>22.5418491363525</v>
       </c>
       <c r="G140" t="n">
-        <v>21.0915145874023</v>
+        <v>21.091516494751</v>
       </c>
       <c r="H140" t="n">
         <v>828</v>
@@ -4458,7 +4458,7 @@
         <v>22.454927444458</v>
       </c>
       <c r="G141" t="n">
-        <v>21.0101871490479</v>
+        <v>21.0101852416992</v>
       </c>
       <c r="H141" t="n">
         <v>34</v>
@@ -4545,7 +4545,7 @@
         <v>21.2235279083252</v>
       </c>
       <c r="G144" t="n">
-        <v>19.8580131530762</v>
+        <v>19.8580150604248</v>
       </c>
       <c r="H144" t="n">
         <v>500</v>
@@ -4835,7 +4835,7 @@
         <v>21.4408340454102</v>
       </c>
       <c r="G154" t="n">
-        <v>20.0613384246826</v>
+        <v>20.0613403320312</v>
       </c>
       <c r="H154" t="n">
         <v>155</v>
@@ -4864,7 +4864,7 @@
         <v>21.3249378204346</v>
       </c>
       <c r="G155" t="n">
-        <v>19.9528999328613</v>
+        <v>19.9528980255127</v>
       </c>
       <c r="H155" t="n">
         <v>120</v>
@@ -4980,7 +4980,7 @@
         <v>22.0782642364502</v>
       </c>
       <c r="G159" t="n">
-        <v>20.6577587127686</v>
+        <v>20.6577568054199</v>
       </c>
       <c r="H159" t="n">
         <v>103</v>
@@ -5009,7 +5009,7 @@
         <v>22.0782642364502</v>
       </c>
       <c r="G160" t="n">
-        <v>20.6577587127686</v>
+        <v>20.6577568054199</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -5299,7 +5299,7 @@
         <v>24.3961925506592</v>
       </c>
       <c r="G170" t="n">
-        <v>22.8265495300293</v>
+        <v>22.8265514373779</v>
       </c>
       <c r="H170" t="n">
         <v>327</v>
@@ -5502,7 +5502,7 @@
         <v>26.5547637939453</v>
       </c>
       <c r="G177" t="n">
-        <v>24.8462390899658</v>
+        <v>24.8462409973145</v>
       </c>
       <c r="H177" t="n">
         <v>293</v>
@@ -5531,7 +5531,7 @@
         <v>26.0766906738281</v>
       </c>
       <c r="G178" t="n">
-        <v>24.39892578125</v>
+        <v>24.3989276885986</v>
       </c>
       <c r="H178" t="n">
         <v>276</v>
@@ -5792,7 +5792,7 @@
         <v>25.4827213287354</v>
       </c>
       <c r="G187" t="n">
-        <v>23.8431720733643</v>
+        <v>23.8431739807129</v>
       </c>
       <c r="H187" t="n">
         <v>379</v>
@@ -5879,7 +5879,7 @@
         <v>27.2356548309326</v>
       </c>
       <c r="G190" t="n">
-        <v>25.4833240509033</v>
+        <v>25.4833221435547</v>
       </c>
       <c r="H190" t="n">
         <v>1156</v>
@@ -5908,7 +5908,7 @@
         <v>33.0304756164551</v>
       </c>
       <c r="G191" t="n">
-        <v>30.9053058624268</v>
+        <v>30.9053077697754</v>
       </c>
       <c r="H191" t="n">
         <v>5539</v>
@@ -6111,7 +6111,7 @@
         <v>27.9744930267334</v>
       </c>
       <c r="G198" t="n">
-        <v>26.1746253967285</v>
+        <v>26.1746234893799</v>
       </c>
       <c r="H198" t="n">
         <v>103</v>
@@ -6227,7 +6227,7 @@
         <v>28.0614166259766</v>
       </c>
       <c r="G202" t="n">
-        <v>26.2559547424316</v>
+        <v>26.2559566497803</v>
       </c>
       <c r="H202" t="n">
         <v>69</v>
@@ -6343,7 +6343,7 @@
         <v>27.8296222686768</v>
       </c>
       <c r="G206" t="n">
-        <v>26.0390758514404</v>
+        <v>26.0390739440918</v>
       </c>
       <c r="H206" t="n">
         <v>34</v>
@@ -6459,7 +6459,7 @@
         <v>28.0034675598145</v>
       </c>
       <c r="G210" t="n">
-        <v>26.2017364501953</v>
+        <v>26.2017345428467</v>
       </c>
       <c r="H210" t="n">
         <v>3468</v>
@@ -6488,7 +6488,7 @@
         <v>28.2787227630615</v>
       </c>
       <c r="G211" t="n">
-        <v>26.4592800140381</v>
+        <v>26.4592819213867</v>
       </c>
       <c r="H211" t="n">
         <v>759</v>
@@ -6633,7 +6633,7 @@
         <v>28.336669921875</v>
       </c>
       <c r="G216" t="n">
-        <v>26.513500213623</v>
+        <v>26.5134983062744</v>
       </c>
       <c r="H216" t="n">
         <v>120</v>
@@ -6662,7 +6662,7 @@
         <v>28.336669921875</v>
       </c>
       <c r="G217" t="n">
-        <v>26.513500213623</v>
+        <v>26.5134983062744</v>
       </c>
       <c r="H217" t="n">
         <v>51</v>
@@ -6691,7 +6691,7 @@
         <v>28.336669921875</v>
       </c>
       <c r="G218" t="n">
-        <v>26.513500213623</v>
+        <v>26.5134983062744</v>
       </c>
       <c r="H218" t="n">
         <v>0</v>
@@ -6720,7 +6720,7 @@
         <v>27.9600067138672</v>
       </c>
       <c r="G219" t="n">
-        <v>26.1610717773438</v>
+        <v>26.1610698699951</v>
       </c>
       <c r="H219" t="n">
         <v>172</v>
@@ -6807,7 +6807,7 @@
         <v>26.9169387817383</v>
       </c>
       <c r="G222" t="n">
-        <v>25.1851119995117</v>
+        <v>25.1851139068604</v>
       </c>
       <c r="H222" t="n">
         <v>189</v>
@@ -6836,7 +6836,7 @@
         <v>27.2356548309326</v>
       </c>
       <c r="G223" t="n">
-        <v>25.4833240509033</v>
+        <v>25.4833221435547</v>
       </c>
       <c r="H223" t="n">
         <v>258</v>
@@ -6952,7 +6952,7 @@
         <v>27.5109081268311</v>
       </c>
       <c r="G227" t="n">
-        <v>25.7408657073975</v>
+        <v>25.7408676147461</v>
       </c>
       <c r="H227" t="n">
         <v>448</v>
@@ -7068,7 +7068,7 @@
         <v>26.0766906738281</v>
       </c>
       <c r="G231" t="n">
-        <v>24.39892578125</v>
+        <v>24.3989276885986</v>
       </c>
       <c r="H231" t="n">
         <v>155</v>
@@ -7097,7 +7097,7 @@
         <v>26.0766906738281</v>
       </c>
       <c r="G232" t="n">
-        <v>24.39892578125</v>
+        <v>24.3989276885986</v>
       </c>
       <c r="H232" t="n">
         <v>0</v>
@@ -7126,7 +7126,7 @@
         <v>26.0766906738281</v>
       </c>
       <c r="G233" t="n">
-        <v>24.39892578125</v>
+        <v>24.3989276885986</v>
       </c>
       <c r="H233" t="n">
         <v>155</v>
@@ -7155,7 +7155,7 @@
         <v>25.2074661254883</v>
       </c>
       <c r="G234" t="n">
-        <v>23.5856285095215</v>
+        <v>23.5856266021729</v>
       </c>
       <c r="H234" t="n">
         <v>949</v>
@@ -7387,7 +7387,7 @@
         <v>27.2356548309326</v>
       </c>
       <c r="G242" t="n">
-        <v>25.4833240509033</v>
+        <v>25.4833221435547</v>
       </c>
       <c r="H242" t="n">
         <v>172</v>
@@ -7416,7 +7416,7 @@
         <v>27.2356548309326</v>
       </c>
       <c r="G243" t="n">
-        <v>25.4833240509033</v>
+        <v>25.4833221435547</v>
       </c>
       <c r="H243" t="n">
         <v>0</v>
@@ -7445,7 +7445,7 @@
         <v>27.2356548309326</v>
       </c>
       <c r="G244" t="n">
-        <v>25.4833240509033</v>
+        <v>25.4833221435547</v>
       </c>
       <c r="H244" t="n">
         <v>0</v>
@@ -7561,7 +7561,7 @@
         <v>26.265022277832</v>
       </c>
       <c r="G248" t="n">
-        <v>24.5751399993896</v>
+        <v>24.5751419067383</v>
       </c>
       <c r="H248" t="n">
         <v>310</v>
@@ -7590,7 +7590,7 @@
         <v>26.0766906738281</v>
       </c>
       <c r="G249" t="n">
-        <v>24.39892578125</v>
+        <v>24.3989276885986</v>
       </c>
       <c r="H249" t="n">
         <v>327</v>
@@ -7648,7 +7648,7 @@
         <v>26.1056632995605</v>
       </c>
       <c r="G251" t="n">
-        <v>24.4260349273682</v>
+        <v>24.4260368347168</v>
       </c>
       <c r="H251" t="n">
         <v>276</v>
@@ -7764,7 +7764,7 @@
         <v>26.9169387817383</v>
       </c>
       <c r="G255" t="n">
-        <v>25.1851119995117</v>
+        <v>25.1851139068604</v>
       </c>
       <c r="H255" t="n">
         <v>276</v>
@@ -7793,7 +7793,7 @@
         <v>26.9169387817383</v>
       </c>
       <c r="G256" t="n">
-        <v>25.1851119995117</v>
+        <v>25.1851139068604</v>
       </c>
       <c r="H256" t="n">
         <v>949</v>
@@ -7996,7 +7996,7 @@
         <v>27.2356548309326</v>
       </c>
       <c r="G263" t="n">
-        <v>25.4833240509033</v>
+        <v>25.4833221435547</v>
       </c>
       <c r="H263" t="n">
         <v>500</v>
@@ -8170,7 +8170,7 @@
         <v>27.7861614227295</v>
       </c>
       <c r="G269" t="n">
-        <v>25.9984111785889</v>
+        <v>25.9984092712402</v>
       </c>
       <c r="H269" t="n">
         <v>707</v>
@@ -8199,7 +8199,7 @@
         <v>28.5539741516113</v>
       </c>
       <c r="G270" t="n">
-        <v>26.7168235778809</v>
+        <v>26.7168216705322</v>
       </c>
       <c r="H270" t="n">
         <v>51</v>
@@ -8228,7 +8228,7 @@
         <v>28.5539741516113</v>
       </c>
       <c r="G271" t="n">
-        <v>26.7168235778809</v>
+        <v>26.7168216705322</v>
       </c>
       <c r="H271" t="n">
         <v>379</v>
@@ -8257,7 +8257,7 @@
         <v>29.6115303039551</v>
       </c>
       <c r="G272" t="n">
-        <v>27.706335067749</v>
+        <v>27.7063369750977</v>
       </c>
       <c r="H272" t="n">
         <v>1311</v>
@@ -8286,7 +8286,7 @@
         <v>32.2771453857422</v>
       </c>
       <c r="G273" t="n">
-        <v>30.2004470825195</v>
+        <v>30.2004451751709</v>
       </c>
       <c r="H273" t="n">
         <v>5142</v>
@@ -8373,7 +8373,7 @@
         <v>30.9153652191162</v>
       </c>
       <c r="G276" t="n">
-        <v>28.9262828826904</v>
+        <v>28.9262809753418</v>
       </c>
       <c r="H276" t="n">
         <v>8162</v>
@@ -8489,7 +8489,7 @@
         <v>31.5817699432373</v>
       </c>
       <c r="G280" t="n">
-        <v>29.5498104095459</v>
+        <v>29.5498123168945</v>
       </c>
       <c r="H280" t="n">
         <v>2381</v>
@@ -8576,7 +8576,7 @@
         <v>31.5817699432373</v>
       </c>
       <c r="G283" t="n">
-        <v>29.5498104095459</v>
+        <v>29.5498123168945</v>
       </c>
       <c r="H283" t="n">
         <v>120</v>
@@ -8692,7 +8692,7 @@
         <v>33.0304756164551</v>
       </c>
       <c r="G287" t="n">
-        <v>30.9053058624268</v>
+        <v>30.9053077697754</v>
       </c>
       <c r="H287" t="n">
         <v>621</v>
@@ -8721,7 +8721,7 @@
         <v>32.7407341003418</v>
       </c>
       <c r="G288" t="n">
-        <v>30.6342105865479</v>
+        <v>30.6342086791992</v>
       </c>
       <c r="H288" t="n">
         <v>310</v>
@@ -8808,7 +8808,7 @@
         <v>33.754825592041</v>
       </c>
       <c r="G291" t="n">
-        <v>31.5830535888672</v>
+        <v>31.5830516815186</v>
       </c>
       <c r="H291" t="n">
         <v>155</v>
@@ -9011,7 +9011,7 @@
         <v>32.7986793518066</v>
       </c>
       <c r="G298" t="n">
-        <v>30.6884269714355</v>
+        <v>30.6884250640869</v>
       </c>
       <c r="H298" t="n">
         <v>534</v>
@@ -9127,7 +9127,7 @@
         <v>33.0304756164551</v>
       </c>
       <c r="G302" t="n">
-        <v>30.9053058624268</v>
+        <v>30.9053077697754</v>
       </c>
       <c r="H302" t="n">
         <v>103</v>
@@ -9156,7 +9156,7 @@
         <v>32.7407341003418</v>
       </c>
       <c r="G303" t="n">
-        <v>30.6342105865479</v>
+        <v>30.6342086791992</v>
       </c>
       <c r="H303" t="n">
         <v>51</v>
@@ -9243,7 +9243,7 @@
         <v>33.6099548339844</v>
       </c>
       <c r="G306" t="n">
-        <v>31.4475040435791</v>
+        <v>31.4475021362305</v>
       </c>
       <c r="H306" t="n">
         <v>517</v>
@@ -9359,7 +9359,7 @@
         <v>33.6099548339844</v>
       </c>
       <c r="G310" t="n">
-        <v>31.4475040435791</v>
+        <v>31.4475021362305</v>
       </c>
       <c r="H310" t="n">
         <v>293</v>
@@ -9417,7 +9417,7 @@
         <v>33.9576454162598</v>
       </c>
       <c r="G312" t="n">
-        <v>31.7728252410889</v>
+        <v>31.7728233337402</v>
       </c>
       <c r="H312" t="n">
         <v>120</v>
@@ -9475,7 +9475,7 @@
         <v>34.1314888000488</v>
       </c>
       <c r="G314" t="n">
-        <v>31.9354820251465</v>
+        <v>31.9354801177979</v>
       </c>
       <c r="H314" t="n">
         <v>448</v>
@@ -9504,7 +9504,7 @@
         <v>34.1314888000488</v>
       </c>
       <c r="G315" t="n">
-        <v>31.9354820251465</v>
+        <v>31.9354801177979</v>
       </c>
       <c r="H315" t="n">
         <v>603</v>
@@ -9533,7 +9533,7 @@
         <v>34.1314888000488</v>
       </c>
       <c r="G316" t="n">
-        <v>31.9354820251465</v>
+        <v>31.9354801177979</v>
       </c>
       <c r="H316" t="n">
         <v>293</v>
@@ -9678,7 +9678,7 @@
         <v>38.2458114624023</v>
       </c>
       <c r="G321" t="n">
-        <v>35.7850914001465</v>
+        <v>35.7850875854492</v>
       </c>
       <c r="H321" t="n">
         <v>4762</v>
@@ -9794,7 +9794,7 @@
         <v>42.9106407165527</v>
       </c>
       <c r="G325" t="n">
-        <v>40.1497840881348</v>
+        <v>40.149787902832</v>
       </c>
       <c r="H325" t="n">
         <v>3969</v>
@@ -9910,7 +9910,7 @@
         <v>39.6655426025391</v>
       </c>
       <c r="G329" t="n">
-        <v>37.1134757995605</v>
+        <v>37.1134796142578</v>
       </c>
       <c r="H329" t="n">
         <v>742</v>
@@ -9939,7 +9939,7 @@
         <v>39.0281143188477</v>
       </c>
       <c r="G330" t="n">
-        <v>36.5170631408691</v>
+        <v>36.5170593261719</v>
       </c>
       <c r="H330" t="n">
         <v>638</v>
@@ -9997,7 +9997,7 @@
         <v>41.8965492248535</v>
       </c>
       <c r="G332" t="n">
-        <v>39.2009429931641</v>
+        <v>39.2009391784668</v>
       </c>
       <c r="H332" t="n">
         <v>1069</v>
@@ -10171,7 +10171,7 @@
         <v>52.1533813476562</v>
       </c>
       <c r="G338" t="n">
-        <v>48.7978515625</v>
+        <v>48.7978553771973</v>
       </c>
       <c r="H338" t="n">
         <v>17463</v>
@@ -10374,7 +10374,7 @@
         <v>75.3326644897461</v>
       </c>
       <c r="G345" t="n">
-        <v>70.4857864379883</v>
+        <v>70.4857940673828</v>
       </c>
       <c r="H345" t="n">
         <v>4434</v>
@@ -10432,7 +10432,7 @@
         <v>85.7633361816406</v>
       </c>
       <c r="G347" t="n">
-        <v>80.2453536987305</v>
+        <v>80.245361328125</v>
       </c>
       <c r="H347" t="n">
         <v>19879</v>
@@ -10461,7 +10461,7 @@
         <v>83.0397720336914</v>
       </c>
       <c r="G348" t="n">
-        <v>77.6970291137695</v>
+        <v>77.697021484375</v>
       </c>
       <c r="H348" t="n">
         <v>6454</v>
@@ -10519,7 +10519,7 @@
         <v>81.9387588500977</v>
       </c>
       <c r="G350" t="n">
-        <v>76.6668548583984</v>
+        <v>76.6668472290039</v>
       </c>
       <c r="H350" t="n">
         <v>4711</v>
@@ -10606,7 +10606,7 @@
         <v>84.5464248657227</v>
       </c>
       <c r="G353" t="n">
-        <v>79.1067428588867</v>
+        <v>79.1067352294922</v>
       </c>
       <c r="H353" t="n">
         <v>2916</v>
@@ -10751,7 +10751,7 @@
         <v>128.355270385742</v>
       </c>
       <c r="G358" t="n">
-        <v>120.096946716309</v>
+        <v>120.096939086914</v>
       </c>
       <c r="H358" t="n">
         <v>7437</v>
@@ -10838,7 +10838,7 @@
         <v>175.727920532227</v>
       </c>
       <c r="G361" t="n">
-        <v>164.421646118164</v>
+        <v>164.421661376953</v>
       </c>
       <c r="H361" t="n">
         <v>27421</v>
@@ -10896,7 +10896,7 @@
         <v>183.985534667969</v>
       </c>
       <c r="G363" t="n">
-        <v>172.147979736328</v>
+        <v>172.147964477539</v>
       </c>
       <c r="H363" t="n">
         <v>21001</v>
@@ -10925,7 +10925,7 @@
         <v>177.031753540039</v>
       </c>
       <c r="G364" t="n">
-        <v>165.641586303711</v>
+        <v>165.6416015625</v>
       </c>
       <c r="H364" t="n">
         <v>6609</v>
@@ -10954,7 +10954,7 @@
         <v>186.882949829102</v>
       </c>
       <c r="G365" t="n">
-        <v>174.858978271484</v>
+        <v>174.858963012695</v>
       </c>
       <c r="H365" t="n">
         <v>8196</v>
@@ -11012,7 +11012,7 @@
         <v>161.3857421875</v>
       </c>
       <c r="G367" t="n">
-        <v>151.002243041992</v>
+        <v>151.002258300781</v>
       </c>
       <c r="H367" t="n">
         <v>11648</v>
@@ -11099,7 +11099,7 @@
         <v>114.100006103516</v>
       </c>
       <c r="G370" t="n">
-        <v>106.758857727051</v>
+        <v>106.758850097656</v>
       </c>
       <c r="H370" t="n">
         <v>22778</v>
@@ -11157,7 +11157,7 @@
         <v>141.103866577148</v>
       </c>
       <c r="G372" t="n">
-        <v>132.025283813477</v>
+        <v>132.025299072266</v>
       </c>
       <c r="H372" t="n">
         <v>20121</v>
@@ -11186,7 +11186,7 @@
         <v>133.222915649414</v>
       </c>
       <c r="G373" t="n">
-        <v>124.651397705078</v>
+        <v>124.651405334473</v>
       </c>
       <c r="H373" t="n">
         <v>6436</v>
@@ -11215,7 +11215,7 @@
         <v>131.716262817383</v>
       </c>
       <c r="G374" t="n">
-        <v>123.241683959961</v>
+        <v>123.241691589355</v>
       </c>
       <c r="H374" t="n">
         <v>1415</v>
@@ -11331,7 +11331,7 @@
         <v>124.125045776367</v>
       </c>
       <c r="G378" t="n">
-        <v>116.138885498047</v>
+        <v>116.138893127441</v>
       </c>
       <c r="H378" t="n">
         <v>3503</v>
@@ -11447,7 +11447,7 @@
         <v>126.500923156738</v>
       </c>
       <c r="G382" t="n">
-        <v>118.36190032959</v>
+        <v>118.361907958984</v>
       </c>
       <c r="H382" t="n">
         <v>2260</v>
@@ -11505,7 +11505,7 @@
         <v>122.328651428223</v>
       </c>
       <c r="G384" t="n">
-        <v>114.458076477051</v>
+        <v>114.458068847656</v>
       </c>
       <c r="H384" t="n">
         <v>534</v>
@@ -11563,7 +11563,7 @@
         <v>116.939468383789</v>
       </c>
       <c r="G386" t="n">
-        <v>109.415626525879</v>
+        <v>109.415634155273</v>
       </c>
       <c r="H386" t="n">
         <v>983</v>
@@ -11621,7 +11621,7 @@
         <v>116.244087219238</v>
       </c>
       <c r="G388" t="n">
-        <v>108.764984130859</v>
+        <v>108.764991760254</v>
       </c>
       <c r="H388" t="n">
         <v>1863</v>
@@ -11650,7 +11650,7 @@
         <v>133.8603515625</v>
       </c>
       <c r="G389" t="n">
-        <v>125.247825622559</v>
+        <v>125.247833251953</v>
       </c>
       <c r="H389" t="n">
         <v>12424</v>
@@ -11679,7 +11679,7 @@
         <v>124.936317443848</v>
       </c>
       <c r="G390" t="n">
-        <v>116.897956848145</v>
+        <v>116.897964477539</v>
       </c>
       <c r="H390" t="n">
         <v>9128</v>
@@ -11766,7 +11766,7 @@
         <v>121.053787231445</v>
       </c>
       <c r="G393" t="n">
-        <v>113.265228271484</v>
+        <v>113.265235900879</v>
       </c>
       <c r="H393" t="n">
         <v>1156</v>
@@ -11795,7 +11795,7 @@
         <v>119.952774047852</v>
       </c>
       <c r="G394" t="n">
-        <v>112.235061645508</v>
+        <v>112.235054016113</v>
       </c>
       <c r="H394" t="n">
         <v>707</v>
@@ -11882,7 +11882,7 @@
         <v>117.692794799805</v>
       </c>
       <c r="G397" t="n">
-        <v>110.120483398438</v>
+        <v>110.120491027832</v>
       </c>
       <c r="H397" t="n">
         <v>811</v>
@@ -11940,7 +11940,7 @@
         <v>115.143074035645</v>
       </c>
       <c r="G399" t="n">
-        <v>107.734817504883</v>
+        <v>107.734809875488</v>
       </c>
       <c r="H399" t="n">
         <v>759</v>
@@ -80125,6 +80125,35 @@
         <v>0</v>
       </c>
       <c r="I2750" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2751">
+      <c r="A2751" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2751" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C2751" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2751" t="n">
+        <v>23</v>
+      </c>
+      <c r="E2751" t="n">
+        <v>23</v>
+      </c>
+      <c r="F2751" t="n">
+        <v>23</v>
+      </c>
+      <c r="G2751" t="n">
+        <v>23</v>
+      </c>
+      <c r="H2751" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2751" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TWL.MI.xlsx
+++ b/data/TWL.MI.xlsx
@@ -427,7 +427,7 @@
         <v>23.8167095184326</v>
       </c>
       <c r="G2" t="n">
-        <v>22.284351348877</v>
+        <v>22.2843532562256</v>
       </c>
       <c r="H2" t="n">
         <v>379</v>
@@ -717,7 +717,7 @@
         <v>22.0058288574219</v>
       </c>
       <c r="G12" t="n">
-        <v>20.5899829864502</v>
+        <v>20.5899810791016</v>
       </c>
       <c r="H12" t="n">
         <v>396</v>
@@ -746,7 +746,7 @@
         <v>21.4408340454102</v>
       </c>
       <c r="G13" t="n">
-        <v>20.0613403320312</v>
+        <v>20.0613384246826</v>
       </c>
       <c r="H13" t="n">
         <v>345</v>
@@ -775,7 +775,7 @@
         <v>19.1229057312012</v>
       </c>
       <c r="G14" t="n">
-        <v>17.8925437927246</v>
+        <v>17.8925457000732</v>
       </c>
       <c r="H14" t="n">
         <v>983</v>
@@ -833,7 +833,7 @@
         <v>20.8613529205322</v>
       </c>
       <c r="G16" t="n">
-        <v>19.5191421508789</v>
+        <v>19.5191402435303</v>
       </c>
       <c r="H16" t="n">
         <v>172</v>
@@ -862,7 +862,7 @@
         <v>20.8613529205322</v>
       </c>
       <c r="G17" t="n">
-        <v>19.5191421508789</v>
+        <v>19.5191402435303</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
         <v>20.8613529205322</v>
       </c>
       <c r="G18" t="n">
-        <v>19.5191421508789</v>
+        <v>19.5191402435303</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
         <v>20.8613529205322</v>
       </c>
       <c r="G19" t="n">
-        <v>19.5191421508789</v>
+        <v>19.5191402435303</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -978,7 +978,7 @@
         <v>19.7023887634277</v>
       </c>
       <c r="G21" t="n">
-        <v>18.4347438812256</v>
+        <v>18.4347457885742</v>
       </c>
       <c r="H21" t="n">
         <v>293</v>
@@ -1007,7 +1007,7 @@
         <v>19.7023887634277</v>
       </c>
       <c r="G22" t="n">
-        <v>18.4347438812256</v>
+        <v>18.4347457885742</v>
       </c>
       <c r="H22" t="n">
         <v>276</v>
@@ -1036,7 +1036,7 @@
         <v>20.2239227294922</v>
       </c>
       <c r="G23" t="n">
-        <v>18.922721862793</v>
+        <v>18.9227237701416</v>
       </c>
       <c r="H23" t="n">
         <v>776</v>
@@ -1094,7 +1094,7 @@
         <v>19.6154651641846</v>
       </c>
       <c r="G25" t="n">
-        <v>18.3534145355225</v>
+        <v>18.3534126281738</v>
       </c>
       <c r="H25" t="n">
         <v>448</v>
@@ -1152,7 +1152,7 @@
         <v>19.1229057312012</v>
       </c>
       <c r="G27" t="n">
-        <v>17.8925437927246</v>
+        <v>17.8925457000732</v>
       </c>
       <c r="H27" t="n">
         <v>86</v>
@@ -1181,7 +1181,7 @@
         <v>18.282657623291</v>
       </c>
       <c r="G28" t="n">
-        <v>17.1063594818115</v>
+        <v>17.1063575744629</v>
       </c>
       <c r="H28" t="n">
         <v>86</v>
@@ -1210,7 +1210,7 @@
         <v>19.1229057312012</v>
       </c>
       <c r="G29" t="n">
-        <v>17.8925437927246</v>
+        <v>17.8925457000732</v>
       </c>
       <c r="H29" t="n">
         <v>2519</v>
@@ -1268,7 +1268,7 @@
         <v>18.0218906402588</v>
       </c>
       <c r="G31" t="n">
-        <v>16.8623676300049</v>
+        <v>16.8623695373535</v>
       </c>
       <c r="H31" t="n">
         <v>241</v>
@@ -1297,7 +1297,7 @@
         <v>18.8331642150879</v>
       </c>
       <c r="G32" t="n">
-        <v>17.6214466094971</v>
+        <v>17.6214447021484</v>
       </c>
       <c r="H32" t="n">
         <v>69</v>
@@ -1326,7 +1326,7 @@
         <v>18.8331642150879</v>
       </c>
       <c r="G33" t="n">
-        <v>17.6214466094971</v>
+        <v>17.6214447021484</v>
       </c>
       <c r="H33" t="n">
         <v>207</v>
@@ -1355,7 +1355,7 @@
         <v>18.5723972320557</v>
       </c>
       <c r="G34" t="n">
-        <v>17.3774547576904</v>
+        <v>17.3774566650391</v>
       </c>
       <c r="H34" t="n">
         <v>207</v>
@@ -1442,7 +1442,7 @@
         <v>19.1229057312012</v>
       </c>
       <c r="G37" t="n">
-        <v>17.8925437927246</v>
+        <v>17.8925457000732</v>
       </c>
       <c r="H37" t="n">
         <v>258</v>
@@ -1558,7 +1558,7 @@
         <v>20.5716114044189</v>
       </c>
       <c r="G41" t="n">
-        <v>19.2480430603027</v>
+        <v>19.2480411529541</v>
       </c>
       <c r="H41" t="n">
         <v>86</v>
@@ -1587,7 +1587,7 @@
         <v>20.5716114044189</v>
       </c>
       <c r="G42" t="n">
-        <v>19.2480430603027</v>
+        <v>19.2480411529541</v>
       </c>
       <c r="H42" t="n">
         <v>86</v>
@@ -1616,7 +1616,7 @@
         <v>20.5716114044189</v>
       </c>
       <c r="G43" t="n">
-        <v>19.2480430603027</v>
+        <v>19.2480411529541</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -1674,7 +1674,7 @@
         <v>20.5716114044189</v>
       </c>
       <c r="G45" t="n">
-        <v>19.2480430603027</v>
+        <v>19.2480411529541</v>
       </c>
       <c r="H45" t="n">
         <v>465</v>
@@ -1848,7 +1848,7 @@
         <v>21.8754444122314</v>
       </c>
       <c r="G51" t="n">
-        <v>20.4679851531982</v>
+        <v>20.4679870605469</v>
       </c>
       <c r="H51" t="n">
         <v>1069</v>
@@ -1964,7 +1964,7 @@
         <v>22.9764614105225</v>
       </c>
       <c r="G55" t="n">
-        <v>21.4981632232666</v>
+        <v>21.4981651306152</v>
       </c>
       <c r="H55" t="n">
         <v>224</v>
@@ -1993,7 +1993,7 @@
         <v>22.2231349945068</v>
       </c>
       <c r="G56" t="n">
-        <v>20.7933082580566</v>
+        <v>20.793306350708</v>
       </c>
       <c r="H56" t="n">
         <v>483</v>
@@ -2051,7 +2051,7 @@
         <v>21.6436538696289</v>
       </c>
       <c r="G58" t="n">
-        <v>20.2511100769043</v>
+        <v>20.2511081695557</v>
       </c>
       <c r="H58" t="n">
         <v>120</v>
@@ -2109,7 +2109,7 @@
         <v>23.1503067016602</v>
       </c>
       <c r="G60" t="n">
-        <v>21.6608257293701</v>
+        <v>21.6608238220215</v>
       </c>
       <c r="H60" t="n">
         <v>17</v>
@@ -2138,7 +2138,7 @@
         <v>23.1503067016602</v>
       </c>
       <c r="G61" t="n">
-        <v>21.6608257293701</v>
+        <v>21.6608238220215</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -2283,7 +2283,7 @@
         <v>21.7305755615234</v>
       </c>
       <c r="G66" t="n">
-        <v>20.3324375152588</v>
+        <v>20.3324394226074</v>
       </c>
       <c r="H66" t="n">
         <v>120</v>
@@ -2312,7 +2312,7 @@
         <v>21.4408340454102</v>
       </c>
       <c r="G67" t="n">
-        <v>20.0613403320312</v>
+        <v>20.0613384246826</v>
       </c>
       <c r="H67" t="n">
         <v>17</v>
@@ -2341,7 +2341,7 @@
         <v>22.0058288574219</v>
       </c>
       <c r="G68" t="n">
-        <v>20.5899829864502</v>
+        <v>20.5899810791016</v>
       </c>
       <c r="H68" t="n">
         <v>172</v>
@@ -2370,7 +2370,7 @@
         <v>22.0058288574219</v>
       </c>
       <c r="G69" t="n">
-        <v>20.5899829864502</v>
+        <v>20.5899810791016</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -2399,7 +2399,7 @@
         <v>20.8613529205322</v>
       </c>
       <c r="G70" t="n">
-        <v>19.5191421508789</v>
+        <v>19.5191402435303</v>
       </c>
       <c r="H70" t="n">
         <v>1173</v>
@@ -2428,7 +2428,7 @@
         <v>21.1800670623779</v>
       </c>
       <c r="G71" t="n">
-        <v>19.8173484802246</v>
+        <v>19.8173503875732</v>
       </c>
       <c r="H71" t="n">
         <v>103</v>
@@ -2486,7 +2486,7 @@
         <v>19.8327713012695</v>
       </c>
       <c r="G73" t="n">
-        <v>18.5567398071289</v>
+        <v>18.5567378997803</v>
       </c>
       <c r="H73" t="n">
         <v>241</v>
@@ -2515,7 +2515,7 @@
         <v>19.7023887634277</v>
       </c>
       <c r="G74" t="n">
-        <v>18.4347438812256</v>
+        <v>18.4347457885742</v>
       </c>
       <c r="H74" t="n">
         <v>431</v>
@@ -2544,7 +2544,7 @@
         <v>19.7023887634277</v>
       </c>
       <c r="G75" t="n">
-        <v>18.4347438812256</v>
+        <v>18.4347457885742</v>
       </c>
       <c r="H75" t="n">
         <v>120</v>
@@ -2631,7 +2631,7 @@
         <v>19.3257236480713</v>
       </c>
       <c r="G78" t="n">
-        <v>18.0823135375977</v>
+        <v>18.0823154449463</v>
       </c>
       <c r="H78" t="n">
         <v>345</v>
@@ -2660,7 +2660,7 @@
         <v>19.7023887634277</v>
       </c>
       <c r="G79" t="n">
-        <v>18.4347438812256</v>
+        <v>18.4347457885742</v>
       </c>
       <c r="H79" t="n">
         <v>69</v>
@@ -2689,7 +2689,7 @@
         <v>19.7023887634277</v>
       </c>
       <c r="G80" t="n">
-        <v>18.4347438812256</v>
+        <v>18.4347457885742</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -2747,7 +2747,7 @@
         <v>19.1229057312012</v>
       </c>
       <c r="G82" t="n">
-        <v>17.8925437927246</v>
+        <v>17.8925457000732</v>
       </c>
       <c r="H82" t="n">
         <v>345</v>
@@ -2776,7 +2776,7 @@
         <v>19.1229057312012</v>
       </c>
       <c r="G83" t="n">
-        <v>17.8925437927246</v>
+        <v>17.8925457000732</v>
       </c>
       <c r="H83" t="n">
         <v>638</v>
@@ -2950,7 +2950,7 @@
         <v>19.1229057312012</v>
       </c>
       <c r="G89" t="n">
-        <v>17.8925437927246</v>
+        <v>17.8925457000732</v>
       </c>
       <c r="H89" t="n">
         <v>138</v>
@@ -2979,7 +2979,7 @@
         <v>19.1229057312012</v>
       </c>
       <c r="G90" t="n">
-        <v>17.8925437927246</v>
+        <v>17.8925457000732</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -3066,7 +3066,7 @@
         <v>17.8770198822021</v>
       </c>
       <c r="G93" t="n">
-        <v>16.7268199920654</v>
+        <v>16.7268180847168</v>
       </c>
       <c r="H93" t="n">
         <v>241</v>
@@ -3124,7 +3124,7 @@
         <v>19.3257236480713</v>
       </c>
       <c r="G95" t="n">
-        <v>18.0823135375977</v>
+        <v>18.0823154449463</v>
       </c>
       <c r="H95" t="n">
         <v>517</v>
@@ -3182,7 +3182,7 @@
         <v>17.8770198822021</v>
       </c>
       <c r="G97" t="n">
-        <v>16.7268199920654</v>
+        <v>16.7268180847168</v>
       </c>
       <c r="H97" t="n">
         <v>17</v>
@@ -3211,7 +3211,7 @@
         <v>17.8770198822021</v>
       </c>
       <c r="G98" t="n">
-        <v>16.7268199920654</v>
+        <v>16.7268180847168</v>
       </c>
       <c r="H98" t="n">
         <v>138</v>
@@ -3269,7 +3269,7 @@
         <v>18.3261184692383</v>
       </c>
       <c r="G100" t="n">
-        <v>17.1470241546631</v>
+        <v>17.1470222473145</v>
       </c>
       <c r="H100" t="n">
         <v>34</v>
@@ -3443,7 +3443,7 @@
         <v>19.253288269043</v>
       </c>
       <c r="G106" t="n">
-        <v>18.0145397186279</v>
+        <v>18.0145378112793</v>
       </c>
       <c r="H106" t="n">
         <v>17</v>
@@ -3472,7 +3472,7 @@
         <v>19.253288269043</v>
       </c>
       <c r="G107" t="n">
-        <v>18.0145397186279</v>
+        <v>18.0145378112793</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -3588,7 +3588,7 @@
         <v>18.5723972320557</v>
       </c>
       <c r="G111" t="n">
-        <v>17.3774547576904</v>
+        <v>17.3774566650391</v>
       </c>
       <c r="H111" t="n">
         <v>172</v>
@@ -3617,7 +3617,7 @@
         <v>24.9322128295898</v>
       </c>
       <c r="G112" t="n">
-        <v>23.3280849456787</v>
+        <v>23.3280830383301</v>
       </c>
       <c r="H112" t="n">
         <v>2830</v>
@@ -3704,7 +3704,7 @@
         <v>31.436897277832</v>
       </c>
       <c r="G115" t="n">
-        <v>29.4142608642578</v>
+        <v>29.4142589569092</v>
       </c>
       <c r="H115" t="n">
         <v>7800</v>
@@ -3791,7 +3791,7 @@
         <v>25.2074661254883</v>
       </c>
       <c r="G118" t="n">
-        <v>23.5856266021729</v>
+        <v>23.5856285095215</v>
       </c>
       <c r="H118" t="n">
         <v>3002</v>
@@ -3820,7 +3820,7 @@
         <v>27.728214263916</v>
       </c>
       <c r="G119" t="n">
-        <v>25.9441928863525</v>
+        <v>25.9441909790039</v>
       </c>
       <c r="H119" t="n">
         <v>3796</v>
@@ -3907,7 +3907,7 @@
         <v>25.7145137786865</v>
       </c>
       <c r="G122" t="n">
-        <v>24.0600528717041</v>
+        <v>24.0600509643555</v>
       </c>
       <c r="H122" t="n">
         <v>673</v>
@@ -4052,7 +4052,7 @@
         <v>22.6432590484619</v>
       </c>
       <c r="G127" t="n">
-        <v>21.1863994598389</v>
+        <v>21.1864013671875</v>
       </c>
       <c r="H127" t="n">
         <v>396</v>
@@ -4081,7 +4081,7 @@
         <v>22.6142845153809</v>
       </c>
       <c r="G128" t="n">
-        <v>21.1592884063721</v>
+        <v>21.1592903137207</v>
       </c>
       <c r="H128" t="n">
         <v>120</v>
@@ -4110,7 +4110,7 @@
         <v>22.6142845153809</v>
       </c>
       <c r="G129" t="n">
-        <v>21.1592884063721</v>
+        <v>21.1592903137207</v>
       </c>
       <c r="H129" t="n">
         <v>431</v>
@@ -4139,7 +4139,7 @@
         <v>22.1362113952637</v>
       </c>
       <c r="G130" t="n">
-        <v>20.7119750976562</v>
+        <v>20.7119770050049</v>
       </c>
       <c r="H130" t="n">
         <v>189</v>
@@ -4226,7 +4226,7 @@
         <v>21.4408340454102</v>
       </c>
       <c r="G133" t="n">
-        <v>20.0613403320312</v>
+        <v>20.0613384246826</v>
       </c>
       <c r="H133" t="n">
         <v>120</v>
@@ -4429,7 +4429,7 @@
         <v>22.5418491363525</v>
       </c>
       <c r="G140" t="n">
-        <v>21.091516494751</v>
+        <v>21.0915145874023</v>
       </c>
       <c r="H140" t="n">
         <v>828</v>
@@ -4458,7 +4458,7 @@
         <v>22.454927444458</v>
       </c>
       <c r="G141" t="n">
-        <v>21.0101852416992</v>
+        <v>21.0101871490479</v>
       </c>
       <c r="H141" t="n">
         <v>34</v>
@@ -4545,7 +4545,7 @@
         <v>21.2235279083252</v>
       </c>
       <c r="G144" t="n">
-        <v>19.8580150604248</v>
+        <v>19.8580131530762</v>
       </c>
       <c r="H144" t="n">
         <v>500</v>
@@ -4835,7 +4835,7 @@
         <v>21.4408340454102</v>
       </c>
       <c r="G154" t="n">
-        <v>20.0613403320312</v>
+        <v>20.0613384246826</v>
       </c>
       <c r="H154" t="n">
         <v>155</v>
@@ -4864,7 +4864,7 @@
         <v>21.3249378204346</v>
       </c>
       <c r="G155" t="n">
-        <v>19.9528980255127</v>
+        <v>19.9528999328613</v>
       </c>
       <c r="H155" t="n">
         <v>120</v>
@@ -4980,7 +4980,7 @@
         <v>22.0782642364502</v>
       </c>
       <c r="G159" t="n">
-        <v>20.6577568054199</v>
+        <v>20.6577587127686</v>
       </c>
       <c r="H159" t="n">
         <v>103</v>
@@ -5009,7 +5009,7 @@
         <v>22.0782642364502</v>
       </c>
       <c r="G160" t="n">
-        <v>20.6577568054199</v>
+        <v>20.6577587127686</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -5299,7 +5299,7 @@
         <v>24.3961925506592</v>
       </c>
       <c r="G170" t="n">
-        <v>22.8265514373779</v>
+        <v>22.8265495300293</v>
       </c>
       <c r="H170" t="n">
         <v>327</v>
@@ -5502,7 +5502,7 @@
         <v>26.5547637939453</v>
       </c>
       <c r="G177" t="n">
-        <v>24.8462409973145</v>
+        <v>24.8462390899658</v>
       </c>
       <c r="H177" t="n">
         <v>293</v>
@@ -5531,7 +5531,7 @@
         <v>26.0766906738281</v>
       </c>
       <c r="G178" t="n">
-        <v>24.3989276885986</v>
+        <v>24.39892578125</v>
       </c>
       <c r="H178" t="n">
         <v>276</v>
@@ -5792,7 +5792,7 @@
         <v>25.4827213287354</v>
       </c>
       <c r="G187" t="n">
-        <v>23.8431739807129</v>
+        <v>23.8431720733643</v>
       </c>
       <c r="H187" t="n">
         <v>379</v>
@@ -5879,7 +5879,7 @@
         <v>27.2356548309326</v>
       </c>
       <c r="G190" t="n">
-        <v>25.4833221435547</v>
+        <v>25.4833240509033</v>
       </c>
       <c r="H190" t="n">
         <v>1156</v>
@@ -5908,7 +5908,7 @@
         <v>33.0304756164551</v>
       </c>
       <c r="G191" t="n">
-        <v>30.9053077697754</v>
+        <v>30.9053058624268</v>
       </c>
       <c r="H191" t="n">
         <v>5539</v>
@@ -6111,7 +6111,7 @@
         <v>27.9744930267334</v>
       </c>
       <c r="G198" t="n">
-        <v>26.1746234893799</v>
+        <v>26.1746253967285</v>
       </c>
       <c r="H198" t="n">
         <v>103</v>
@@ -6227,7 +6227,7 @@
         <v>28.0614166259766</v>
       </c>
       <c r="G202" t="n">
-        <v>26.2559566497803</v>
+        <v>26.2559547424316</v>
       </c>
       <c r="H202" t="n">
         <v>69</v>
@@ -6343,7 +6343,7 @@
         <v>27.8296222686768</v>
       </c>
       <c r="G206" t="n">
-        <v>26.0390739440918</v>
+        <v>26.0390758514404</v>
       </c>
       <c r="H206" t="n">
         <v>34</v>
@@ -6459,7 +6459,7 @@
         <v>28.0034675598145</v>
       </c>
       <c r="G210" t="n">
-        <v>26.2017345428467</v>
+        <v>26.2017364501953</v>
       </c>
       <c r="H210" t="n">
         <v>3468</v>
@@ -6488,7 +6488,7 @@
         <v>28.2787227630615</v>
       </c>
       <c r="G211" t="n">
-        <v>26.4592819213867</v>
+        <v>26.4592800140381</v>
       </c>
       <c r="H211" t="n">
         <v>759</v>
@@ -6633,7 +6633,7 @@
         <v>28.336669921875</v>
       </c>
       <c r="G216" t="n">
-        <v>26.5134983062744</v>
+        <v>26.513500213623</v>
       </c>
       <c r="H216" t="n">
         <v>120</v>
@@ -6662,7 +6662,7 @@
         <v>28.336669921875</v>
       </c>
       <c r="G217" t="n">
-        <v>26.5134983062744</v>
+        <v>26.513500213623</v>
       </c>
       <c r="H217" t="n">
         <v>51</v>
@@ -6691,7 +6691,7 @@
         <v>28.336669921875</v>
       </c>
       <c r="G218" t="n">
-        <v>26.5134983062744</v>
+        <v>26.513500213623</v>
       </c>
       <c r="H218" t="n">
         <v>0</v>
@@ -6720,7 +6720,7 @@
         <v>27.9600067138672</v>
       </c>
       <c r="G219" t="n">
-        <v>26.1610698699951</v>
+        <v>26.1610717773438</v>
       </c>
       <c r="H219" t="n">
         <v>172</v>
@@ -6807,7 +6807,7 @@
         <v>26.9169387817383</v>
       </c>
       <c r="G222" t="n">
-        <v>25.1851139068604</v>
+        <v>25.1851119995117</v>
       </c>
       <c r="H222" t="n">
         <v>189</v>
@@ -6836,7 +6836,7 @@
         <v>27.2356548309326</v>
       </c>
       <c r="G223" t="n">
-        <v>25.4833221435547</v>
+        <v>25.4833240509033</v>
       </c>
       <c r="H223" t="n">
         <v>258</v>
@@ -6952,7 +6952,7 @@
         <v>27.5109081268311</v>
       </c>
       <c r="G227" t="n">
-        <v>25.7408676147461</v>
+        <v>25.7408657073975</v>
       </c>
       <c r="H227" t="n">
         <v>448</v>
@@ -7068,7 +7068,7 @@
         <v>26.0766906738281</v>
       </c>
       <c r="G231" t="n">
-        <v>24.3989276885986</v>
+        <v>24.39892578125</v>
       </c>
       <c r="H231" t="n">
         <v>155</v>
@@ -7097,7 +7097,7 @@
         <v>26.0766906738281</v>
       </c>
       <c r="G232" t="n">
-        <v>24.3989276885986</v>
+        <v>24.39892578125</v>
       </c>
       <c r="H232" t="n">
         <v>0</v>
@@ -7126,7 +7126,7 @@
         <v>26.0766906738281</v>
       </c>
       <c r="G233" t="n">
-        <v>24.3989276885986</v>
+        <v>24.39892578125</v>
       </c>
       <c r="H233" t="n">
         <v>155</v>
@@ -7155,7 +7155,7 @@
         <v>25.2074661254883</v>
       </c>
       <c r="G234" t="n">
-        <v>23.5856266021729</v>
+        <v>23.5856285095215</v>
       </c>
       <c r="H234" t="n">
         <v>949</v>
@@ -7387,7 +7387,7 @@
         <v>27.2356548309326</v>
       </c>
       <c r="G242" t="n">
-        <v>25.4833221435547</v>
+        <v>25.4833240509033</v>
       </c>
       <c r="H242" t="n">
         <v>172</v>
@@ -7416,7 +7416,7 @@
         <v>27.2356548309326</v>
       </c>
       <c r="G243" t="n">
-        <v>25.4833221435547</v>
+        <v>25.4833240509033</v>
       </c>
       <c r="H243" t="n">
         <v>0</v>
@@ -7445,7 +7445,7 @@
         <v>27.2356548309326</v>
       </c>
       <c r="G244" t="n">
-        <v>25.4833221435547</v>
+        <v>25.4833240509033</v>
       </c>
       <c r="H244" t="n">
         <v>0</v>
@@ -7561,7 +7561,7 @@
         <v>26.265022277832</v>
       </c>
       <c r="G248" t="n">
-        <v>24.5751419067383</v>
+        <v>24.5751399993896</v>
       </c>
       <c r="H248" t="n">
         <v>310</v>
@@ -7590,7 +7590,7 @@
         <v>26.0766906738281</v>
       </c>
       <c r="G249" t="n">
-        <v>24.3989276885986</v>
+        <v>24.39892578125</v>
       </c>
       <c r="H249" t="n">
         <v>327</v>
@@ -7648,7 +7648,7 @@
         <v>26.1056632995605</v>
       </c>
       <c r="G251" t="n">
-        <v>24.4260368347168</v>
+        <v>24.4260349273682</v>
       </c>
       <c r="H251" t="n">
         <v>276</v>
@@ -7764,7 +7764,7 @@
         <v>26.9169387817383</v>
       </c>
       <c r="G255" t="n">
-        <v>25.1851139068604</v>
+        <v>25.1851119995117</v>
       </c>
       <c r="H255" t="n">
         <v>276</v>
@@ -7793,7 +7793,7 @@
         <v>26.9169387817383</v>
       </c>
       <c r="G256" t="n">
-        <v>25.1851139068604</v>
+        <v>25.1851119995117</v>
       </c>
       <c r="H256" t="n">
         <v>949</v>
@@ -7996,7 +7996,7 @@
         <v>27.2356548309326</v>
       </c>
       <c r="G263" t="n">
-        <v>25.4833221435547</v>
+        <v>25.4833240509033</v>
       </c>
       <c r="H263" t="n">
         <v>500</v>
@@ -8170,7 +8170,7 @@
         <v>27.7861614227295</v>
       </c>
       <c r="G269" t="n">
-        <v>25.9984092712402</v>
+        <v>25.9984111785889</v>
       </c>
       <c r="H269" t="n">
         <v>707</v>
@@ -8199,7 +8199,7 @@
         <v>28.5539741516113</v>
       </c>
       <c r="G270" t="n">
-        <v>26.7168216705322</v>
+        <v>26.7168235778809</v>
       </c>
       <c r="H270" t="n">
         <v>51</v>
@@ -8228,7 +8228,7 @@
         <v>28.5539741516113</v>
       </c>
       <c r="G271" t="n">
-        <v>26.7168216705322</v>
+        <v>26.7168235778809</v>
       </c>
       <c r="H271" t="n">
         <v>379</v>
@@ -8257,7 +8257,7 @@
         <v>29.6115303039551</v>
       </c>
       <c r="G272" t="n">
-        <v>27.7063369750977</v>
+        <v>27.706335067749</v>
       </c>
       <c r="H272" t="n">
         <v>1311</v>
@@ -8286,7 +8286,7 @@
         <v>32.2771453857422</v>
       </c>
       <c r="G273" t="n">
-        <v>30.2004451751709</v>
+        <v>30.2004470825195</v>
       </c>
       <c r="H273" t="n">
         <v>5142</v>
@@ -8373,7 +8373,7 @@
         <v>30.9153652191162</v>
       </c>
       <c r="G276" t="n">
-        <v>28.9262809753418</v>
+        <v>28.9262828826904</v>
       </c>
       <c r="H276" t="n">
         <v>8162</v>
@@ -8489,7 +8489,7 @@
         <v>31.5817699432373</v>
       </c>
       <c r="G280" t="n">
-        <v>29.5498123168945</v>
+        <v>29.5498104095459</v>
       </c>
       <c r="H280" t="n">
         <v>2381</v>
@@ -8576,7 +8576,7 @@
         <v>31.5817699432373</v>
       </c>
       <c r="G283" t="n">
-        <v>29.5498123168945</v>
+        <v>29.5498104095459</v>
       </c>
       <c r="H283" t="n">
         <v>120</v>
@@ -8692,7 +8692,7 @@
         <v>33.0304756164551</v>
       </c>
       <c r="G287" t="n">
-        <v>30.9053077697754</v>
+        <v>30.9053058624268</v>
       </c>
       <c r="H287" t="n">
         <v>621</v>
@@ -8721,7 +8721,7 @@
         <v>32.7407341003418</v>
       </c>
       <c r="G288" t="n">
-        <v>30.6342086791992</v>
+        <v>30.6342105865479</v>
       </c>
       <c r="H288" t="n">
         <v>310</v>
@@ -8808,7 +8808,7 @@
         <v>33.754825592041</v>
       </c>
       <c r="G291" t="n">
-        <v>31.5830516815186</v>
+        <v>31.5830535888672</v>
       </c>
       <c r="H291" t="n">
         <v>155</v>
@@ -9011,7 +9011,7 @@
         <v>32.7986793518066</v>
       </c>
       <c r="G298" t="n">
-        <v>30.6884250640869</v>
+        <v>30.6884269714355</v>
       </c>
       <c r="H298" t="n">
         <v>534</v>
@@ -9127,7 +9127,7 @@
         <v>33.0304756164551</v>
       </c>
       <c r="G302" t="n">
-        <v>30.9053077697754</v>
+        <v>30.9053058624268</v>
       </c>
       <c r="H302" t="n">
         <v>103</v>
@@ -9156,7 +9156,7 @@
         <v>32.7407341003418</v>
       </c>
       <c r="G303" t="n">
-        <v>30.6342086791992</v>
+        <v>30.6342105865479</v>
       </c>
       <c r="H303" t="n">
         <v>51</v>
@@ -9243,7 +9243,7 @@
         <v>33.6099548339844</v>
       </c>
       <c r="G306" t="n">
-        <v>31.4475021362305</v>
+        <v>31.4475040435791</v>
       </c>
       <c r="H306" t="n">
         <v>517</v>
@@ -9359,7 +9359,7 @@
         <v>33.6099548339844</v>
       </c>
       <c r="G310" t="n">
-        <v>31.4475021362305</v>
+        <v>31.4475040435791</v>
       </c>
       <c r="H310" t="n">
         <v>293</v>
@@ -9417,7 +9417,7 @@
         <v>33.9576454162598</v>
       </c>
       <c r="G312" t="n">
-        <v>31.7728233337402</v>
+        <v>31.7728252410889</v>
       </c>
       <c r="H312" t="n">
         <v>120</v>
@@ -9475,7 +9475,7 @@
         <v>34.1314888000488</v>
       </c>
       <c r="G314" t="n">
-        <v>31.9354801177979</v>
+        <v>31.9354820251465</v>
       </c>
       <c r="H314" t="n">
         <v>448</v>
@@ -9504,7 +9504,7 @@
         <v>34.1314888000488</v>
       </c>
       <c r="G315" t="n">
-        <v>31.9354801177979</v>
+        <v>31.9354820251465</v>
       </c>
       <c r="H315" t="n">
         <v>603</v>
@@ -9533,7 +9533,7 @@
         <v>34.1314888000488</v>
       </c>
       <c r="G316" t="n">
-        <v>31.9354801177979</v>
+        <v>31.9354820251465</v>
       </c>
       <c r="H316" t="n">
         <v>293</v>
@@ -9678,7 +9678,7 @@
         <v>38.2458114624023</v>
       </c>
       <c r="G321" t="n">
-        <v>35.7850875854492</v>
+        <v>35.7850914001465</v>
       </c>
       <c r="H321" t="n">
         <v>4762</v>
@@ -9794,7 +9794,7 @@
         <v>42.9106407165527</v>
       </c>
       <c r="G325" t="n">
-        <v>40.149787902832</v>
+        <v>40.1497840881348</v>
       </c>
       <c r="H325" t="n">
         <v>3969</v>
@@ -9910,7 +9910,7 @@
         <v>39.6655426025391</v>
       </c>
       <c r="G329" t="n">
-        <v>37.1134796142578</v>
+        <v>37.1134757995605</v>
       </c>
       <c r="H329" t="n">
         <v>742</v>
@@ -9939,7 +9939,7 @@
         <v>39.0281143188477</v>
       </c>
       <c r="G330" t="n">
-        <v>36.5170593261719</v>
+        <v>36.5170631408691</v>
       </c>
       <c r="H330" t="n">
         <v>638</v>
@@ -9997,7 +9997,7 @@
         <v>41.8965492248535</v>
       </c>
       <c r="G332" t="n">
-        <v>39.2009391784668</v>
+        <v>39.2009429931641</v>
       </c>
       <c r="H332" t="n">
         <v>1069</v>
@@ -10171,7 +10171,7 @@
         <v>52.1533813476562</v>
       </c>
       <c r="G338" t="n">
-        <v>48.7978553771973</v>
+        <v>48.7978515625</v>
       </c>
       <c r="H338" t="n">
         <v>17463</v>
@@ -10374,7 +10374,7 @@
         <v>75.3326644897461</v>
       </c>
       <c r="G345" t="n">
-        <v>70.4857940673828</v>
+        <v>70.4857864379883</v>
       </c>
       <c r="H345" t="n">
         <v>4434</v>
@@ -10432,7 +10432,7 @@
         <v>85.7633361816406</v>
       </c>
       <c r="G347" t="n">
-        <v>80.245361328125</v>
+        <v>80.2453536987305</v>
       </c>
       <c r="H347" t="n">
         <v>19879</v>
@@ -10461,7 +10461,7 @@
         <v>83.0397720336914</v>
       </c>
       <c r="G348" t="n">
-        <v>77.697021484375</v>
+        <v>77.6970291137695</v>
       </c>
       <c r="H348" t="n">
         <v>6454</v>
@@ -10519,7 +10519,7 @@
         <v>81.9387588500977</v>
       </c>
       <c r="G350" t="n">
-        <v>76.6668472290039</v>
+        <v>76.6668548583984</v>
       </c>
       <c r="H350" t="n">
         <v>4711</v>
@@ -10606,7 +10606,7 @@
         <v>84.5464248657227</v>
       </c>
       <c r="G353" t="n">
-        <v>79.1067352294922</v>
+        <v>79.1067428588867</v>
       </c>
       <c r="H353" t="n">
         <v>2916</v>
@@ -10751,7 +10751,7 @@
         <v>128.355270385742</v>
       </c>
       <c r="G358" t="n">
-        <v>120.096939086914</v>
+        <v>120.096946716309</v>
       </c>
       <c r="H358" t="n">
         <v>7437</v>
@@ -10838,7 +10838,7 @@
         <v>175.727920532227</v>
       </c>
       <c r="G361" t="n">
-        <v>164.421661376953</v>
+        <v>164.421646118164</v>
       </c>
       <c r="H361" t="n">
         <v>27421</v>
@@ -10896,7 +10896,7 @@
         <v>183.985534667969</v>
       </c>
       <c r="G363" t="n">
-        <v>172.147964477539</v>
+        <v>172.147979736328</v>
       </c>
       <c r="H363" t="n">
         <v>21001</v>
@@ -10925,7 +10925,7 @@
         <v>177.031753540039</v>
       </c>
       <c r="G364" t="n">
-        <v>165.6416015625</v>
+        <v>165.641586303711</v>
       </c>
       <c r="H364" t="n">
         <v>6609</v>
@@ -10954,7 +10954,7 @@
         <v>186.882949829102</v>
       </c>
       <c r="G365" t="n">
-        <v>174.858963012695</v>
+        <v>174.858978271484</v>
       </c>
       <c r="H365" t="n">
         <v>8196</v>
@@ -11012,7 +11012,7 @@
         <v>161.3857421875</v>
       </c>
       <c r="G367" t="n">
-        <v>151.002258300781</v>
+        <v>151.002243041992</v>
       </c>
       <c r="H367" t="n">
         <v>11648</v>
@@ -11099,7 +11099,7 @@
         <v>114.100006103516</v>
       </c>
       <c r="G370" t="n">
-        <v>106.758850097656</v>
+        <v>106.758857727051</v>
       </c>
       <c r="H370" t="n">
         <v>22778</v>
@@ -11157,7 +11157,7 @@
         <v>141.103866577148</v>
       </c>
       <c r="G372" t="n">
-        <v>132.025299072266</v>
+        <v>132.025283813477</v>
       </c>
       <c r="H372" t="n">
         <v>20121</v>
@@ -11186,7 +11186,7 @@
         <v>133.222915649414</v>
       </c>
       <c r="G373" t="n">
-        <v>124.651405334473</v>
+        <v>124.651397705078</v>
       </c>
       <c r="H373" t="n">
         <v>6436</v>
@@ -11215,7 +11215,7 @@
         <v>131.716262817383</v>
       </c>
       <c r="G374" t="n">
-        <v>123.241691589355</v>
+        <v>123.241683959961</v>
       </c>
       <c r="H374" t="n">
         <v>1415</v>
@@ -11331,7 +11331,7 @@
         <v>124.125045776367</v>
       </c>
       <c r="G378" t="n">
-        <v>116.138893127441</v>
+        <v>116.138885498047</v>
       </c>
       <c r="H378" t="n">
         <v>3503</v>
@@ -11447,7 +11447,7 @@
         <v>126.500923156738</v>
       </c>
       <c r="G382" t="n">
-        <v>118.361907958984</v>
+        <v>118.36190032959</v>
       </c>
       <c r="H382" t="n">
         <v>2260</v>
@@ -11505,7 +11505,7 @@
         <v>122.328651428223</v>
       </c>
       <c r="G384" t="n">
-        <v>114.458068847656</v>
+        <v>114.458076477051</v>
       </c>
       <c r="H384" t="n">
         <v>534</v>
@@ -11563,7 +11563,7 @@
         <v>116.939468383789</v>
       </c>
       <c r="G386" t="n">
-        <v>109.415634155273</v>
+        <v>109.415626525879</v>
       </c>
       <c r="H386" t="n">
         <v>983</v>
@@ -11621,7 +11621,7 @@
         <v>116.244087219238</v>
       </c>
       <c r="G388" t="n">
-        <v>108.764991760254</v>
+        <v>108.764984130859</v>
       </c>
       <c r="H388" t="n">
         <v>1863</v>
@@ -11650,7 +11650,7 @@
         <v>133.8603515625</v>
       </c>
       <c r="G389" t="n">
-        <v>125.247833251953</v>
+        <v>125.247825622559</v>
       </c>
       <c r="H389" t="n">
         <v>12424</v>
@@ -11679,7 +11679,7 @@
         <v>124.936317443848</v>
       </c>
       <c r="G390" t="n">
-        <v>116.897964477539</v>
+        <v>116.897956848145</v>
       </c>
       <c r="H390" t="n">
         <v>9128</v>
@@ -11766,7 +11766,7 @@
         <v>121.053787231445</v>
       </c>
       <c r="G393" t="n">
-        <v>113.265235900879</v>
+        <v>113.265228271484</v>
       </c>
       <c r="H393" t="n">
         <v>1156</v>
@@ -11795,7 +11795,7 @@
         <v>119.952774047852</v>
       </c>
       <c r="G394" t="n">
-        <v>112.235054016113</v>
+        <v>112.235061645508</v>
       </c>
       <c r="H394" t="n">
         <v>707</v>
@@ -11882,7 +11882,7 @@
         <v>117.692794799805</v>
       </c>
       <c r="G397" t="n">
-        <v>110.120491027832</v>
+        <v>110.120483398438</v>
       </c>
       <c r="H397" t="n">
         <v>811</v>
@@ -11940,7 +11940,7 @@
         <v>115.143074035645</v>
       </c>
       <c r="G399" t="n">
-        <v>107.734809875488</v>
+        <v>107.734817504883</v>
       </c>
       <c r="H399" t="n">
         <v>759</v>
@@ -80154,6 +80154,64 @@
         <v>0</v>
       </c>
       <c r="I2751" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2752">
+      <c r="A2752" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2752" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C2752" t="n">
+        <v>23</v>
+      </c>
+      <c r="D2752" t="n">
+        <v>23</v>
+      </c>
+      <c r="E2752" t="n">
+        <v>23</v>
+      </c>
+      <c r="F2752" t="n">
+        <v>23</v>
+      </c>
+      <c r="G2752" t="n">
+        <v>23</v>
+      </c>
+      <c r="H2752" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2752" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2753">
+      <c r="A2753" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2753" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C2753" t="n">
+        <v>22.3999996185303</v>
+      </c>
+      <c r="D2753" t="n">
+        <v>22.3999996185303</v>
+      </c>
+      <c r="E2753" t="n">
+        <v>22.3999996185303</v>
+      </c>
+      <c r="F2753" t="n">
+        <v>22.7999992370605</v>
+      </c>
+      <c r="G2753" t="n">
+        <v>22.7999992370605</v>
+      </c>
+      <c r="H2753" t="n">
+        <v>8</v>
+      </c>
+      <c r="I2753" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TWL.MI.xlsx
+++ b/data/TWL.MI.xlsx
@@ -80197,7 +80197,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="D2753" t="n">
-        <v>22.3999996185303</v>
+        <v>22.7999992370605</v>
       </c>
       <c r="E2753" t="n">
         <v>22.3999996185303</v>
